--- a/downloads/indicadores/EMOE/EMOE_datos.xlsx
+++ b/downloads/indicadores/EMOE/EMOE_datos.xlsx
@@ -508,7 +508,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401 · Fecha de publicación: 3 de agosto de 2026</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf · Fecha de publicación: 3 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L82" s="4" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L103" s="7" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L105" s="7" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L106" s="4" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K107" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L107" s="7" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=682416#D701401</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
         </is>
       </c>
       <c r="L108" s="4" t="inlineStr">

--- a/downloads/indicadores/EMOE/EMOE_datos.xlsx
+++ b/downloads/indicadores/EMOE/EMOE_datos.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4232,10 +4232,10 @@
         <v>46204</v>
       </c>
       <c r="C108" s="6" t="n">
-        <v>48.241225</v>
+        <v>48.203612</v>
       </c>
       <c r="D108" s="6" t="n">
-        <v>0.08425199999999999</v>
+        <v>0.046638</v>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
@@ -4253,6 +4253,42 @@
         </is>
       </c>
       <c r="H108" s="7" t="inlineStr">
+        <is>
+          <t>3 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>Ago 26</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C109" s="8" t="n">
+        <v>48.232912</v>
+      </c>
+      <c r="D109" s="8" t="n">
+        <v>0.029301</v>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="G109" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="H109" s="9" t="inlineStr">
         <is>
           <t>3 de agosto de 2026</t>
         </is>

--- a/downloads/indicadores/EMOE/EMOE_datos.xlsx
+++ b/downloads/indicadores/EMOE/EMOE_datos.xlsx
@@ -504,7 +504,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf · Fecha de publicación: 3 de agosto de 2026</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf · Fecha de publicación: 1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -649,12 +649,12 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -685,12 +685,12 @@
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1549,12 +1549,12 @@
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1621,12 +1621,12 @@
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1657,12 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1693,12 +1693,12 @@
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1801,12 +1801,12 @@
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1837,12 +1837,12 @@
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1909,12 +1909,12 @@
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2017,12 +2017,12 @@
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2053,12 +2053,12 @@
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H47" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2125,12 +2125,12 @@
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2161,12 +2161,12 @@
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2197,12 +2197,12 @@
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2305,12 +2305,12 @@
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2341,12 +2341,12 @@
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H55" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2377,12 +2377,12 @@
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2413,12 +2413,12 @@
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2485,12 +2485,12 @@
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H59" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2521,12 +2521,12 @@
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2593,12 +2593,12 @@
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2629,12 +2629,12 @@
       </c>
       <c r="G63" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H63" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2701,12 +2701,12 @@
       </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H65" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2773,12 +2773,12 @@
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H67" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2809,12 +2809,12 @@
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2845,12 +2845,12 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H69" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2881,12 +2881,12 @@
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2917,12 +2917,12 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H71" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2953,12 +2953,12 @@
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -2989,12 +2989,12 @@
       </c>
       <c r="G73" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H73" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3025,12 +3025,12 @@
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3061,12 +3061,12 @@
       </c>
       <c r="G75" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H75" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3097,12 +3097,12 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H77" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3169,12 +3169,12 @@
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H79" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3241,12 +3241,12 @@
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3277,12 +3277,12 @@
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H81" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3313,12 +3313,12 @@
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3349,12 +3349,12 @@
       </c>
       <c r="G83" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H83" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3385,12 +3385,12 @@
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3421,12 +3421,12 @@
       </c>
       <c r="G85" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H85" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3493,12 +3493,12 @@
       </c>
       <c r="G87" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H87" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3529,12 +3529,12 @@
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3565,12 +3565,12 @@
       </c>
       <c r="G89" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H89" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3637,12 +3637,12 @@
       </c>
       <c r="G91" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H91" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3673,12 +3673,12 @@
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="G93" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H93" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3745,12 +3745,12 @@
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="G95" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H95" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3817,12 +3817,12 @@
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3853,12 +3853,12 @@
       </c>
       <c r="G97" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H97" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="G99" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H99" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3961,12 +3961,12 @@
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="G101" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H101" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -4033,12 +4033,12 @@
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -4069,12 +4069,12 @@
       </c>
       <c r="G103" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H103" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -4105,12 +4105,12 @@
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="G105" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H105" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -4177,12 +4177,12 @@
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -4213,12 +4213,12 @@
       </c>
       <c r="G107" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H107" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -4285,12 +4285,12 @@
       </c>
       <c r="G109" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
         </is>
       </c>
       <c r="H109" s="9" t="inlineStr">
         <is>
-          <t>3 de agosto de 2026</t>
+          <t>1 de septiembre de 2026</t>
         </is>
       </c>
     </row>

--- a/downloads/indicadores/EMOE/EMOE_datos.xlsx
+++ b/downloads/indicadores/EMOE/EMOE_datos.xlsx
@@ -474,37 +474,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:M109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="55" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Confianza empresarial (EMOE)</t>
+          <t>Encuesta Mensual de Opinión Empresarial</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Puntos</t>
+          <t>Fuente: INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE) · Frecuencia: Mensual · Unidad: Puntos</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf · Fecha de publicación: 1 de septiembre de 2026</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf · Fecha de publicación: 1 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -521,30 +526,55 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Confianza empresarial (puntos)</t>
+          <t>IGOEC</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Var. mensual (puntos)</t>
+          <t>Cambio mensual IGOEC (puntos)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Cambio anual IGOEC (puntos)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Manufacturas</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Comercio</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Servicios privados no financieros</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
           <t>Carácter del dato</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>URL del boletín</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Fecha de publicación</t>
         </is>
@@ -565,22 +595,27 @@
       <c r="D6" s="6" t="n">
         <v>-0.848</v>
       </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -601,22 +636,27 @@
       <c r="D7" s="8" t="n">
         <v>0.122</v>
       </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M7" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -637,22 +677,27 @@
       <c r="D8" s="6" t="n">
         <v>0.92</v>
       </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -673,22 +718,27 @@
       <c r="D9" s="8" t="n">
         <v>0.003</v>
       </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="8" t="n"/>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -709,22 +759,27 @@
       <c r="D10" s="6" t="n">
         <v>-0.855</v>
       </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -745,22 +800,27 @@
       <c r="D11" s="8" t="n">
         <v>-0.778</v>
       </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -781,22 +841,27 @@
       <c r="D12" s="6" t="n">
         <v>4.354</v>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -817,22 +882,27 @@
       <c r="D13" s="8" t="n">
         <v>0.654</v>
       </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M13" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -853,22 +923,27 @@
       <c r="D14" s="6" t="n">
         <v>-1.141</v>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -889,22 +964,27 @@
       <c r="D15" s="8" t="n">
         <v>-0.496</v>
       </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M15" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -925,22 +1005,27 @@
       <c r="D16" s="6" t="n">
         <v>-1.464</v>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -961,22 +1046,27 @@
       <c r="D17" s="8" t="n">
         <v>0.555</v>
       </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M17" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -997,22 +1087,29 @@
       <c r="D18" s="6" t="n">
         <v>1.412</v>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="E18" s="6" t="n">
+        <v>3.286</v>
+      </c>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1033,22 +1130,29 @@
       <c r="D19" s="8" t="n">
         <v>0.504</v>
       </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="E19" s="8" t="n">
+        <v>3.668</v>
+      </c>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M19" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1069,22 +1173,29 @@
       <c r="D20" s="6" t="n">
         <v>0.171</v>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="E20" s="6" t="n">
+        <v>2.919</v>
+      </c>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1105,22 +1216,29 @@
       <c r="D21" s="8" t="n">
         <v>0.02</v>
       </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="E21" s="8" t="n">
+        <v>2.936</v>
+      </c>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="8" t="n"/>
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="8" t="n"/>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1141,22 +1259,29 @@
       <c r="D22" s="6" t="n">
         <v>-1.413</v>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="E22" s="6" t="n">
+        <v>2.378</v>
+      </c>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1177,22 +1302,29 @@
       <c r="D23" s="8" t="n">
         <v>-0.892</v>
       </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="E23" s="8" t="n">
+        <v>2.264</v>
+      </c>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="8" t="n"/>
+      <c r="H23" s="8" t="n"/>
+      <c r="I23" s="8" t="n"/>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M23" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1213,22 +1345,29 @@
       <c r="D24" s="6" t="n">
         <v>-0.993</v>
       </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="E24" s="6" t="n">
+        <v>-3.083</v>
+      </c>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M24" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1249,22 +1388,29 @@
       <c r="D25" s="8" t="n">
         <v>-0.524</v>
       </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="E25" s="8" t="n">
+        <v>-4.261</v>
+      </c>
+      <c r="F25" s="8" t="n"/>
+      <c r="G25" s="8" t="n"/>
+      <c r="H25" s="8" t="n"/>
+      <c r="I25" s="8" t="n"/>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M25" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1285,22 +1431,29 @@
       <c r="D26" s="6" t="n">
         <v>0.842</v>
       </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="E26" s="6" t="n">
+        <v>-2.278</v>
+      </c>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M26" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1321,22 +1474,29 @@
       <c r="D27" s="8" t="n">
         <v>-1.299</v>
       </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="E27" s="8" t="n">
+        <v>-3.081</v>
+      </c>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="8" t="n"/>
+      <c r="H27" s="8" t="n"/>
+      <c r="I27" s="8" t="n"/>
+      <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M27" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1357,22 +1517,29 @@
       <c r="D28" s="6" t="n">
         <v>-0.759</v>
       </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="E28" s="6" t="n">
+        <v>-2.376</v>
+      </c>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1393,22 +1560,29 @@
       <c r="D29" s="8" t="n">
         <v>0.424</v>
       </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="E29" s="8" t="n">
+        <v>-2.507</v>
+      </c>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="8" t="n"/>
+      <c r="H29" s="8" t="n"/>
+      <c r="I29" s="8" t="n"/>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M29" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1429,22 +1603,29 @@
       <c r="D30" s="6" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="E30" s="6" t="n">
+        <v>-4.859</v>
+      </c>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="n"/>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1465,22 +1646,29 @@
       <c r="D31" s="8" t="n">
         <v>1.071</v>
       </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H31" s="9" t="inlineStr">
+      <c r="E31" s="8" t="n">
+        <v>-4.292</v>
+      </c>
+      <c r="F31" s="8" t="n"/>
+      <c r="G31" s="8" t="n"/>
+      <c r="H31" s="8" t="n"/>
+      <c r="I31" s="8" t="n"/>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M31" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1501,22 +1689,29 @@
       <c r="D32" s="6" t="n">
         <v>-4.384</v>
       </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="E32" s="6" t="n">
+        <v>-8.847</v>
+      </c>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="n"/>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M32" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1537,22 +1732,29 @@
       <c r="D33" s="8" t="n">
         <v>-8.247</v>
       </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="E33" s="8" t="n">
+        <v>-17.114</v>
+      </c>
+      <c r="F33" s="8" t="n"/>
+      <c r="G33" s="8" t="n"/>
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="8" t="n"/>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M33" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1573,22 +1775,29 @@
       <c r="D34" s="6" t="n">
         <v>-1.76</v>
       </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="E34" s="6" t="n">
+        <v>-17.461</v>
+      </c>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="6" t="n"/>
+      <c r="I34" s="6" t="n"/>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K34" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M34" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1609,22 +1818,29 @@
       <c r="D35" s="8" t="n">
         <v>2.509</v>
       </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="E35" s="8" t="n">
+        <v>-14.06</v>
+      </c>
+      <c r="F35" s="8" t="n"/>
+      <c r="G35" s="8" t="n"/>
+      <c r="H35" s="8" t="n"/>
+      <c r="I35" s="8" t="n"/>
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L35" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M35" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1645,22 +1861,29 @@
       <c r="D36" s="6" t="n">
         <v>2.131</v>
       </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="E36" s="6" t="n">
+        <v>-10.936</v>
+      </c>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="6" t="n"/>
+      <c r="I36" s="6" t="n"/>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M36" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1681,22 +1904,29 @@
       <c r="D37" s="8" t="n">
         <v>-0.617</v>
       </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="E37" s="8" t="n">
+        <v>-11.029</v>
+      </c>
+      <c r="F37" s="8" t="n"/>
+      <c r="G37" s="8" t="n"/>
+      <c r="H37" s="8" t="n"/>
+      <c r="I37" s="8" t="n"/>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L37" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M37" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1717,22 +1947,29 @@
       <c r="D38" s="6" t="n">
         <v>0.898</v>
       </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
+      <c r="E38" s="6" t="n">
+        <v>-10.973</v>
+      </c>
+      <c r="F38" s="6" t="n"/>
+      <c r="G38" s="6" t="n"/>
+      <c r="H38" s="6" t="n"/>
+      <c r="I38" s="6" t="n"/>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M38" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1753,22 +1990,29 @@
       <c r="D39" s="8" t="n">
         <v>1.245</v>
       </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G39" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H39" s="9" t="inlineStr">
+      <c r="E39" s="8" t="n">
+        <v>-8.429</v>
+      </c>
+      <c r="F39" s="8" t="n"/>
+      <c r="G39" s="8" t="n"/>
+      <c r="H39" s="8" t="n"/>
+      <c r="I39" s="8" t="n"/>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M39" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1789,22 +2033,29 @@
       <c r="D40" s="6" t="n">
         <v>-0.164</v>
       </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
+      <c r="E40" s="6" t="n">
+        <v>-7.834</v>
+      </c>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="6" t="n"/>
+      <c r="I40" s="6" t="n"/>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M40" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1825,22 +2076,29 @@
       <c r="D41" s="8" t="n">
         <v>1.172</v>
       </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H41" s="9" t="inlineStr">
+      <c r="E41" s="8" t="n">
+        <v>-7.086</v>
+      </c>
+      <c r="F41" s="8" t="n"/>
+      <c r="G41" s="8" t="n"/>
+      <c r="H41" s="8" t="n"/>
+      <c r="I41" s="8" t="n"/>
+      <c r="J41" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K41" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L41" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M41" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1861,22 +2119,29 @@
       <c r="D42" s="6" t="n">
         <v>-0.108</v>
       </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H42" s="7" t="inlineStr">
+      <c r="E42" s="6" t="n">
+        <v>-6.254</v>
+      </c>
+      <c r="F42" s="6" t="n"/>
+      <c r="G42" s="6" t="n"/>
+      <c r="H42" s="6" t="n"/>
+      <c r="I42" s="6" t="n"/>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M42" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1897,22 +2162,29 @@
       <c r="D43" s="8" t="n">
         <v>1.201</v>
       </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G43" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H43" s="9" t="inlineStr">
+      <c r="E43" s="8" t="n">
+        <v>-6.124</v>
+      </c>
+      <c r="F43" s="8" t="n"/>
+      <c r="G43" s="8" t="n"/>
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="8" t="n"/>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K43" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M43" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1933,22 +2205,29 @@
       <c r="D44" s="6" t="n">
         <v>2.961</v>
       </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr">
+      <c r="E44" s="6" t="n">
+        <v>1.221</v>
+      </c>
+      <c r="F44" s="6" t="n"/>
+      <c r="G44" s="6" t="n"/>
+      <c r="H44" s="6" t="n"/>
+      <c r="I44" s="6" t="n"/>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M44" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1969,22 +2248,29 @@
       <c r="D45" s="8" t="n">
         <v>2.18</v>
       </c>
-      <c r="E45" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F45" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G45" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H45" s="9" t="inlineStr">
+      <c r="E45" s="8" t="n">
+        <v>11.648</v>
+      </c>
+      <c r="F45" s="8" t="n"/>
+      <c r="G45" s="8" t="n"/>
+      <c r="H45" s="8" t="n"/>
+      <c r="I45" s="8" t="n"/>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K45" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M45" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2005,22 +2291,29 @@
       <c r="D46" s="6" t="n">
         <v>1.762</v>
       </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr">
+      <c r="E46" s="6" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="F46" s="6" t="n"/>
+      <c r="G46" s="6" t="n"/>
+      <c r="H46" s="6" t="n"/>
+      <c r="I46" s="6" t="n"/>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M46" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2041,22 +2334,29 @@
       <c r="D47" s="8" t="n">
         <v>2.173</v>
       </c>
-      <c r="E47" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F47" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G47" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H47" s="9" t="inlineStr">
+      <c r="E47" s="8" t="n">
+        <v>14.834</v>
+      </c>
+      <c r="F47" s="8" t="n"/>
+      <c r="G47" s="8" t="n"/>
+      <c r="H47" s="8" t="n"/>
+      <c r="I47" s="8" t="n"/>
+      <c r="J47" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K47" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L47" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M47" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2077,22 +2377,29 @@
       <c r="D48" s="6" t="n">
         <v>-0.083</v>
       </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H48" s="7" t="inlineStr">
+      <c r="E48" s="6" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="F48" s="6" t="n"/>
+      <c r="G48" s="6" t="n"/>
+      <c r="H48" s="6" t="n"/>
+      <c r="I48" s="6" t="n"/>
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M48" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2113,22 +2420,29 @@
       <c r="D49" s="8" t="n">
         <v>-1.394</v>
       </c>
-      <c r="E49" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F49" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G49" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H49" s="9" t="inlineStr">
+      <c r="E49" s="8" t="n">
+        <v>11.843</v>
+      </c>
+      <c r="F49" s="8" t="n"/>
+      <c r="G49" s="8" t="n"/>
+      <c r="H49" s="8" t="n"/>
+      <c r="I49" s="8" t="n"/>
+      <c r="J49" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K49" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L49" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M49" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2149,22 +2463,29 @@
       <c r="D50" s="6" t="n">
         <v>1.429</v>
       </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="inlineStr">
+      <c r="E50" s="6" t="n">
+        <v>12.374</v>
+      </c>
+      <c r="F50" s="6" t="n"/>
+      <c r="G50" s="6" t="n"/>
+      <c r="H50" s="6" t="n"/>
+      <c r="I50" s="6" t="n"/>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L50" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M50" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2185,22 +2506,29 @@
       <c r="D51" s="8" t="n">
         <v>0.828</v>
       </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G51" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H51" s="9" t="inlineStr">
+      <c r="E51" s="8" t="n">
+        <v>11.957</v>
+      </c>
+      <c r="F51" s="8" t="n"/>
+      <c r="G51" s="8" t="n"/>
+      <c r="H51" s="8" t="n"/>
+      <c r="I51" s="8" t="n"/>
+      <c r="J51" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K51" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L51" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M51" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2221,22 +2549,29 @@
       <c r="D52" s="6" t="n">
         <v>1.446</v>
       </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G52" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H52" s="7" t="inlineStr">
+      <c r="E52" s="6" t="n">
+        <v>13.567</v>
+      </c>
+      <c r="F52" s="6" t="n"/>
+      <c r="G52" s="6" t="n"/>
+      <c r="H52" s="6" t="n"/>
+      <c r="I52" s="6" t="n"/>
+      <c r="J52" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K52" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M52" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2257,22 +2592,29 @@
       <c r="D53" s="8" t="n">
         <v>1.434</v>
       </c>
-      <c r="E53" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F53" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G53" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H53" s="9" t="inlineStr">
+      <c r="E53" s="8" t="n">
+        <v>13.829</v>
+      </c>
+      <c r="F53" s="8" t="n"/>
+      <c r="G53" s="8" t="n"/>
+      <c r="H53" s="8" t="n"/>
+      <c r="I53" s="8" t="n"/>
+      <c r="J53" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K53" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L53" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M53" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2293,22 +2635,29 @@
       <c r="D54" s="6" t="n">
         <v>-3.44</v>
       </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G54" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H54" s="7" t="inlineStr">
+      <c r="E54" s="6" t="n">
+        <v>10.497</v>
+      </c>
+      <c r="F54" s="6" t="n"/>
+      <c r="G54" s="6" t="n"/>
+      <c r="H54" s="6" t="n"/>
+      <c r="I54" s="6" t="n"/>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K54" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M54" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2329,22 +2678,29 @@
       <c r="D55" s="8" t="n">
         <v>0.579</v>
       </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F55" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G55" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H55" s="9" t="inlineStr">
+      <c r="E55" s="8" t="n">
+        <v>9.875</v>
+      </c>
+      <c r="F55" s="8" t="n"/>
+      <c r="G55" s="8" t="n"/>
+      <c r="H55" s="8" t="n"/>
+      <c r="I55" s="8" t="n"/>
+      <c r="J55" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K55" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L55" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M55" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2365,22 +2721,29 @@
       <c r="D56" s="6" t="n">
         <v>-0.08400000000000001</v>
       </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F56" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H56" s="7" t="inlineStr">
+      <c r="E56" s="6" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="F56" s="6" t="n"/>
+      <c r="G56" s="6" t="n"/>
+      <c r="H56" s="6" t="n"/>
+      <c r="I56" s="6" t="n"/>
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K56" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M56" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2401,22 +2764,29 @@
       <c r="D57" s="8" t="n">
         <v>1.585</v>
       </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F57" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G57" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H57" s="9" t="inlineStr">
+      <c r="E57" s="8" t="n">
+        <v>6.235</v>
+      </c>
+      <c r="F57" s="8" t="n"/>
+      <c r="G57" s="8" t="n"/>
+      <c r="H57" s="8" t="n"/>
+      <c r="I57" s="8" t="n"/>
+      <c r="J57" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K57" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L57" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M57" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2437,22 +2807,29 @@
       <c r="D58" s="6" t="n">
         <v>-0.602</v>
       </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G58" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H58" s="7" t="inlineStr">
+      <c r="E58" s="6" t="n">
+        <v>3.871</v>
+      </c>
+      <c r="F58" s="6" t="n"/>
+      <c r="G58" s="6" t="n"/>
+      <c r="H58" s="6" t="n"/>
+      <c r="I58" s="6" t="n"/>
+      <c r="J58" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K58" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M58" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2473,22 +2850,29 @@
       <c r="D59" s="8" t="n">
         <v>-1.432</v>
       </c>
-      <c r="E59" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F59" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G59" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H59" s="9" t="inlineStr">
+      <c r="E59" s="8" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="F59" s="8" t="n"/>
+      <c r="G59" s="8" t="n"/>
+      <c r="H59" s="8" t="n"/>
+      <c r="I59" s="8" t="n"/>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K59" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L59" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M59" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2509,22 +2893,29 @@
       <c r="D60" s="6" t="n">
         <v>-1.056</v>
       </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr">
+      <c r="E60" s="6" t="n">
+        <v>-0.707</v>
+      </c>
+      <c r="F60" s="6" t="n"/>
+      <c r="G60" s="6" t="n"/>
+      <c r="H60" s="6" t="n"/>
+      <c r="I60" s="6" t="n"/>
+      <c r="J60" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K60" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M60" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2545,22 +2936,29 @@
       <c r="D61" s="8" t="n">
         <v>-2.001</v>
       </c>
-      <c r="E61" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F61" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G61" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H61" s="9" t="inlineStr">
+      <c r="E61" s="8" t="n">
+        <v>-1.314</v>
+      </c>
+      <c r="F61" s="8" t="n"/>
+      <c r="G61" s="8" t="n"/>
+      <c r="H61" s="8" t="n"/>
+      <c r="I61" s="8" t="n"/>
+      <c r="J61" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K61" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L61" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M61" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2581,22 +2979,29 @@
       <c r="D62" s="6" t="n">
         <v>-0.488</v>
       </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F62" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H62" s="7" t="inlineStr">
+      <c r="E62" s="6" t="n">
+        <v>-3.231</v>
+      </c>
+      <c r="F62" s="6" t="n"/>
+      <c r="G62" s="6" t="n"/>
+      <c r="H62" s="6" t="n"/>
+      <c r="I62" s="6" t="n"/>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M62" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2617,22 +3022,29 @@
       <c r="D63" s="8" t="n">
         <v>1.884</v>
       </c>
-      <c r="E63" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F63" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G63" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H63" s="9" t="inlineStr">
+      <c r="E63" s="8" t="n">
+        <v>-2.175</v>
+      </c>
+      <c r="F63" s="8" t="n"/>
+      <c r="G63" s="8" t="n"/>
+      <c r="H63" s="8" t="n"/>
+      <c r="I63" s="8" t="n"/>
+      <c r="J63" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K63" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L63" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M63" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2653,22 +3065,29 @@
       <c r="D64" s="6" t="n">
         <v>-0.245</v>
       </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G64" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H64" s="7" t="inlineStr">
+      <c r="E64" s="6" t="n">
+        <v>-3.866</v>
+      </c>
+      <c r="F64" s="6" t="n"/>
+      <c r="G64" s="6" t="n"/>
+      <c r="H64" s="6" t="n"/>
+      <c r="I64" s="6" t="n"/>
+      <c r="J64" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M64" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2689,22 +3108,29 @@
       <c r="D65" s="8" t="n">
         <v>-2.201</v>
       </c>
-      <c r="E65" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F65" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G65" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H65" s="9" t="inlineStr">
+      <c r="E65" s="8" t="n">
+        <v>-7.501</v>
+      </c>
+      <c r="F65" s="8" t="n"/>
+      <c r="G65" s="8" t="n"/>
+      <c r="H65" s="8" t="n"/>
+      <c r="I65" s="8" t="n"/>
+      <c r="J65" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K65" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L65" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M65" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2725,22 +3151,29 @@
       <c r="D66" s="6" t="n">
         <v>1.148</v>
       </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F66" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G66" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H66" s="7" t="inlineStr">
+      <c r="E66" s="6" t="n">
+        <v>-2.913</v>
+      </c>
+      <c r="F66" s="6" t="n"/>
+      <c r="G66" s="6" t="n"/>
+      <c r="H66" s="6" t="n"/>
+      <c r="I66" s="6" t="n"/>
+      <c r="J66" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K66" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M66" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2761,22 +3194,29 @@
       <c r="D67" s="8" t="n">
         <v>3.225</v>
       </c>
-      <c r="E67" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F67" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G67" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H67" s="9" t="inlineStr">
+      <c r="E67" s="8" t="n">
+        <v>-0.267</v>
+      </c>
+      <c r="F67" s="8" t="n"/>
+      <c r="G67" s="8" t="n"/>
+      <c r="H67" s="8" t="n"/>
+      <c r="I67" s="8" t="n"/>
+      <c r="J67" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K67" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L67" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M67" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2797,22 +3237,29 @@
       <c r="D68" s="6" t="n">
         <v>1.836</v>
       </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F68" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H68" s="7" t="inlineStr">
+      <c r="E68" s="6" t="n">
+        <v>1.653</v>
+      </c>
+      <c r="F68" s="6" t="n"/>
+      <c r="G68" s="6" t="n"/>
+      <c r="H68" s="6" t="n"/>
+      <c r="I68" s="6" t="n"/>
+      <c r="J68" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K68" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M68" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2833,22 +3280,29 @@
       <c r="D69" s="8" t="n">
         <v>1.165</v>
       </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F69" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G69" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H69" s="9" t="inlineStr">
+      <c r="E69" s="8" t="n">
+        <v>1.233</v>
+      </c>
+      <c r="F69" s="8" t="n"/>
+      <c r="G69" s="8" t="n"/>
+      <c r="H69" s="8" t="n"/>
+      <c r="I69" s="8" t="n"/>
+      <c r="J69" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K69" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L69" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M69" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2869,22 +3323,29 @@
       <c r="D70" s="6" t="n">
         <v>0.904</v>
       </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F70" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G70" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H70" s="7" t="inlineStr">
+      <c r="E70" s="6" t="n">
+        <v>2.739</v>
+      </c>
+      <c r="F70" s="6" t="n"/>
+      <c r="G70" s="6" t="n"/>
+      <c r="H70" s="6" t="n"/>
+      <c r="I70" s="6" t="n"/>
+      <c r="J70" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M70" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2905,22 +3366,29 @@
       <c r="D71" s="8" t="n">
         <v>-0.725</v>
       </c>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F71" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G71" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H71" s="9" t="inlineStr">
+      <c r="E71" s="8" t="n">
+        <v>3.446</v>
+      </c>
+      <c r="F71" s="8" t="n"/>
+      <c r="G71" s="8" t="n"/>
+      <c r="H71" s="8" t="n"/>
+      <c r="I71" s="8" t="n"/>
+      <c r="J71" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K71" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L71" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M71" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2941,22 +3409,29 @@
       <c r="D72" s="6" t="n">
         <v>1.581</v>
       </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G72" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H72" s="7" t="inlineStr">
+      <c r="E72" s="6" t="n">
+        <v>6.083</v>
+      </c>
+      <c r="F72" s="6" t="n"/>
+      <c r="G72" s="6" t="n"/>
+      <c r="H72" s="6" t="n"/>
+      <c r="I72" s="6" t="n"/>
+      <c r="J72" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K72" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M72" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2977,22 +3452,29 @@
       <c r="D73" s="8" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F73" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H73" s="9" t="inlineStr">
+      <c r="E73" s="8" t="n">
+        <v>7.984</v>
+      </c>
+      <c r="F73" s="8" t="n"/>
+      <c r="G73" s="8" t="n"/>
+      <c r="H73" s="8" t="n"/>
+      <c r="I73" s="8" t="n"/>
+      <c r="J73" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K73" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L73" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M73" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3013,22 +3495,29 @@
       <c r="D74" s="6" t="n">
         <v>-0.075</v>
       </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F74" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G74" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H74" s="7" t="inlineStr">
+      <c r="E74" s="6" t="n">
+        <v>8.397</v>
+      </c>
+      <c r="F74" s="6" t="n"/>
+      <c r="G74" s="6" t="n"/>
+      <c r="H74" s="6" t="n"/>
+      <c r="I74" s="6" t="n"/>
+      <c r="J74" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K74" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M74" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3049,22 +3538,29 @@
       <c r="D75" s="8" t="n">
         <v>-0.912</v>
       </c>
-      <c r="E75" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F75" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H75" s="9" t="inlineStr">
+      <c r="E75" s="8" t="n">
+        <v>5.601</v>
+      </c>
+      <c r="F75" s="8" t="n"/>
+      <c r="G75" s="8" t="n"/>
+      <c r="H75" s="8" t="n"/>
+      <c r="I75" s="8" t="n"/>
+      <c r="J75" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K75" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L75" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M75" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3085,22 +3581,29 @@
       <c r="D76" s="6" t="n">
         <v>0.599</v>
       </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F76" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H76" s="7" t="inlineStr">
+      <c r="E76" s="6" t="n">
+        <v>6.445</v>
+      </c>
+      <c r="F76" s="6" t="n"/>
+      <c r="G76" s="6" t="n"/>
+      <c r="H76" s="6" t="n"/>
+      <c r="I76" s="6" t="n"/>
+      <c r="J76" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K76" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L76" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M76" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3121,22 +3624,29 @@
       <c r="D77" s="8" t="n">
         <v>0.12</v>
       </c>
-      <c r="E77" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F77" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H77" s="9" t="inlineStr">
+      <c r="E77" s="8" t="n">
+        <v>8.766</v>
+      </c>
+      <c r="F77" s="8" t="n"/>
+      <c r="G77" s="8" t="n"/>
+      <c r="H77" s="8" t="n"/>
+      <c r="I77" s="8" t="n"/>
+      <c r="J77" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K77" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L77" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M77" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3157,22 +3667,29 @@
       <c r="D78" s="6" t="n">
         <v>-0.197</v>
       </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G78" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H78" s="7" t="inlineStr">
+      <c r="E78" s="6" t="n">
+        <v>7.421</v>
+      </c>
+      <c r="F78" s="6" t="n"/>
+      <c r="G78" s="6" t="n"/>
+      <c r="H78" s="6" t="n"/>
+      <c r="I78" s="6" t="n"/>
+      <c r="J78" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K78" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M78" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3193,22 +3710,29 @@
       <c r="D79" s="8" t="n">
         <v>-0.996</v>
       </c>
-      <c r="E79" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F79" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G79" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H79" s="9" t="inlineStr">
+      <c r="E79" s="8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F79" s="8" t="n"/>
+      <c r="G79" s="8" t="n"/>
+      <c r="H79" s="8" t="n"/>
+      <c r="I79" s="8" t="n"/>
+      <c r="J79" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K79" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L79" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M79" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3229,22 +3753,29 @@
       <c r="D80" s="6" t="n">
         <v>-0.218</v>
       </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G80" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H80" s="7" t="inlineStr">
+      <c r="E80" s="6" t="n">
+        <v>1.146</v>
+      </c>
+      <c r="F80" s="6" t="n"/>
+      <c r="G80" s="6" t="n"/>
+      <c r="H80" s="6" t="n"/>
+      <c r="I80" s="6" t="n"/>
+      <c r="J80" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K80" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L80" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M80" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3265,22 +3796,29 @@
       <c r="D81" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="E81" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F81" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G81" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H81" s="9" t="inlineStr">
+      <c r="E81" s="8" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="F81" s="8" t="n"/>
+      <c r="G81" s="8" t="n"/>
+      <c r="H81" s="8" t="n"/>
+      <c r="I81" s="8" t="n"/>
+      <c r="J81" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K81" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L81" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M81" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3301,22 +3839,29 @@
       <c r="D82" s="6" t="n">
         <v>-0.320114</v>
       </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F82" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G82" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H82" s="7" t="inlineStr">
+      <c r="E82" s="6" t="n">
+        <v>-1.043114</v>
+      </c>
+      <c r="F82" s="6" t="n"/>
+      <c r="G82" s="6" t="n"/>
+      <c r="H82" s="6" t="n"/>
+      <c r="I82" s="6" t="n"/>
+      <c r="J82" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K82" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L82" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M82" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3337,22 +3882,29 @@
       <c r="D83" s="8" t="n">
         <v>-1.486992</v>
       </c>
-      <c r="E83" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F83" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G83" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H83" s="9" t="inlineStr">
+      <c r="E83" s="8" t="n">
+        <v>-1.805107</v>
+      </c>
+      <c r="F83" s="8" t="n"/>
+      <c r="G83" s="8" t="n"/>
+      <c r="H83" s="8" t="n"/>
+      <c r="I83" s="8" t="n"/>
+      <c r="J83" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K83" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L83" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M83" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3373,22 +3925,29 @@
       <c r="D84" s="6" t="n">
         <v>0.342203</v>
       </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F84" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G84" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H84" s="7" t="inlineStr">
+      <c r="E84" s="6" t="n">
+        <v>-3.043904</v>
+      </c>
+      <c r="F84" s="6" t="n"/>
+      <c r="G84" s="6" t="n"/>
+      <c r="H84" s="6" t="n"/>
+      <c r="I84" s="6" t="n"/>
+      <c r="J84" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K84" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L84" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M84" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3409,22 +3968,29 @@
       <c r="D85" s="8" t="n">
         <v>-0.75157</v>
       </c>
-      <c r="E85" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F85" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G85" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H85" s="9" t="inlineStr">
+      <c r="E85" s="8" t="n">
+        <v>-3.695474</v>
+      </c>
+      <c r="F85" s="8" t="n"/>
+      <c r="G85" s="8" t="n"/>
+      <c r="H85" s="8" t="n"/>
+      <c r="I85" s="8" t="n"/>
+      <c r="J85" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K85" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L85" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M85" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3445,22 +4011,29 @@
       <c r="D86" s="6" t="n">
         <v>-1.755021</v>
       </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F86" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G86" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H86" s="7" t="inlineStr">
+      <c r="E86" s="6" t="n">
+        <v>-5.375495</v>
+      </c>
+      <c r="F86" s="6" t="n"/>
+      <c r="G86" s="6" t="n"/>
+      <c r="H86" s="6" t="n"/>
+      <c r="I86" s="6" t="n"/>
+      <c r="J86" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K86" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M86" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3481,22 +4054,29 @@
       <c r="D87" s="8" t="n">
         <v>0.920679</v>
       </c>
-      <c r="E87" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F87" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G87" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H87" s="9" t="inlineStr">
+      <c r="E87" s="8" t="n">
+        <v>-3.542817</v>
+      </c>
+      <c r="F87" s="8" t="n"/>
+      <c r="G87" s="8" t="n"/>
+      <c r="H87" s="8" t="n"/>
+      <c r="I87" s="8" t="n"/>
+      <c r="J87" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K87" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L87" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M87" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3517,22 +4097,29 @@
       <c r="D88" s="6" t="n">
         <v>-0.421547</v>
       </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F88" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G88" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H88" s="7" t="inlineStr">
+      <c r="E88" s="6" t="n">
+        <v>-4.563364</v>
+      </c>
+      <c r="F88" s="6" t="n"/>
+      <c r="G88" s="6" t="n"/>
+      <c r="H88" s="6" t="n"/>
+      <c r="I88" s="6" t="n"/>
+      <c r="J88" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K88" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L88" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M88" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3553,22 +4140,29 @@
       <c r="D89" s="8" t="n">
         <v>0.411983</v>
       </c>
-      <c r="E89" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F89" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G89" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H89" s="9" t="inlineStr">
+      <c r="E89" s="8" t="n">
+        <v>-4.27138</v>
+      </c>
+      <c r="F89" s="8" t="n"/>
+      <c r="G89" s="8" t="n"/>
+      <c r="H89" s="8" t="n"/>
+      <c r="I89" s="8" t="n"/>
+      <c r="J89" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K89" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L89" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M89" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3589,22 +4183,29 @@
       <c r="D90" s="6" t="n">
         <v>-0.521713</v>
       </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G90" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H90" s="7" t="inlineStr">
+      <c r="E90" s="6" t="n">
+        <v>-4.596093</v>
+      </c>
+      <c r="F90" s="6" t="n"/>
+      <c r="G90" s="6" t="n"/>
+      <c r="H90" s="6" t="n"/>
+      <c r="I90" s="6" t="n"/>
+      <c r="J90" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K90" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L90" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M90" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3625,22 +4226,29 @@
       <c r="D91" s="8" t="n">
         <v>-1.257464</v>
       </c>
-      <c r="E91" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F91" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G91" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H91" s="9" t="inlineStr">
+      <c r="E91" s="8" t="n">
+        <v>-4.857557</v>
+      </c>
+      <c r="F91" s="8" t="n"/>
+      <c r="G91" s="8" t="n"/>
+      <c r="H91" s="8" t="n"/>
+      <c r="I91" s="8" t="n"/>
+      <c r="J91" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K91" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L91" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M91" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3661,22 +4269,29 @@
       <c r="D92" s="6" t="n">
         <v>-0.779626</v>
       </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F92" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G92" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H92" s="7" t="inlineStr">
+      <c r="E92" s="6" t="n">
+        <v>-5.419183</v>
+      </c>
+      <c r="F92" s="6" t="n"/>
+      <c r="G92" s="6" t="n"/>
+      <c r="H92" s="6" t="n"/>
+      <c r="I92" s="6" t="n"/>
+      <c r="J92" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K92" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M92" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3697,22 +4312,29 @@
       <c r="D93" s="8" t="n">
         <v>-0.648362</v>
       </c>
-      <c r="E93" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F93" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G93" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H93" s="9" t="inlineStr">
+      <c r="E93" s="8" t="n">
+        <v>-6.267545</v>
+      </c>
+      <c r="F93" s="8" t="n"/>
+      <c r="G93" s="8" t="n"/>
+      <c r="H93" s="8" t="n"/>
+      <c r="I93" s="8" t="n"/>
+      <c r="J93" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K93" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L93" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M93" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3733,22 +4355,29 @@
       <c r="D94" s="6" t="n">
         <v>0.032747</v>
       </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G94" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H94" s="7" t="inlineStr">
+      <c r="E94" s="6" t="n">
+        <v>-5.914683</v>
+      </c>
+      <c r="F94" s="6" t="n"/>
+      <c r="G94" s="6" t="n"/>
+      <c r="H94" s="6" t="n"/>
+      <c r="I94" s="6" t="n"/>
+      <c r="J94" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K94" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L94" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M94" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3769,22 +4398,29 @@
       <c r="D95" s="8" t="n">
         <v>-0.098581</v>
       </c>
-      <c r="E95" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F95" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G95" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H95" s="9" t="inlineStr">
+      <c r="E95" s="8" t="n">
+        <v>-4.526271</v>
+      </c>
+      <c r="F95" s="8" t="n"/>
+      <c r="G95" s="8" t="n"/>
+      <c r="H95" s="8" t="n"/>
+      <c r="I95" s="8" t="n"/>
+      <c r="J95" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K95" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L95" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M95" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3805,22 +4441,29 @@
       <c r="D96" s="6" t="n">
         <v>0.344711</v>
       </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F96" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G96" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H96" s="7" t="inlineStr">
+      <c r="E96" s="6" t="n">
+        <v>-4.523763</v>
+      </c>
+      <c r="F96" s="6" t="n"/>
+      <c r="G96" s="6" t="n"/>
+      <c r="H96" s="6" t="n"/>
+      <c r="I96" s="6" t="n"/>
+      <c r="J96" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K96" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L96" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M96" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3841,22 +4484,29 @@
       <c r="D97" s="8" t="n">
         <v>0.334323</v>
       </c>
-      <c r="E97" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F97" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G97" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H97" s="9" t="inlineStr">
+      <c r="E97" s="8" t="n">
+        <v>-3.437869</v>
+      </c>
+      <c r="F97" s="8" t="n"/>
+      <c r="G97" s="8" t="n"/>
+      <c r="H97" s="8" t="n"/>
+      <c r="I97" s="8" t="n"/>
+      <c r="J97" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K97" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L97" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M97" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3877,22 +4527,29 @@
       <c r="D98" s="6" t="n">
         <v>0.016742</v>
       </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F98" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G98" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H98" s="7" t="inlineStr">
+      <c r="E98" s="6" t="n">
+        <v>-1.666106</v>
+      </c>
+      <c r="F98" s="6" t="n"/>
+      <c r="G98" s="6" t="n"/>
+      <c r="H98" s="6" t="n"/>
+      <c r="I98" s="6" t="n"/>
+      <c r="J98" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K98" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L98" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M98" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3913,22 +4570,29 @@
       <c r="D99" s="8" t="n">
         <v>-0.807123</v>
       </c>
-      <c r="E99" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F99" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G99" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H99" s="9" t="inlineStr">
+      <c r="E99" s="8" t="n">
+        <v>-3.393907</v>
+      </c>
+      <c r="F99" s="8" t="n"/>
+      <c r="G99" s="8" t="n"/>
+      <c r="H99" s="8" t="n"/>
+      <c r="I99" s="8" t="n"/>
+      <c r="J99" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K99" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L99" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M99" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3949,22 +4613,29 @@
       <c r="D100" s="6" t="n">
         <v>-0.209162</v>
       </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F100" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G100" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H100" s="7" t="inlineStr">
+      <c r="E100" s="6" t="n">
+        <v>-3.181522</v>
+      </c>
+      <c r="F100" s="6" t="n"/>
+      <c r="G100" s="6" t="n"/>
+      <c r="H100" s="6" t="n"/>
+      <c r="I100" s="6" t="n"/>
+      <c r="J100" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K100" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M100" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3985,22 +4656,29 @@
       <c r="D101" s="8" t="n">
         <v>-0.154983</v>
       </c>
-      <c r="E101" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F101" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G101" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H101" s="9" t="inlineStr">
+      <c r="E101" s="8" t="n">
+        <v>-3.74849</v>
+      </c>
+      <c r="F101" s="8" t="n"/>
+      <c r="G101" s="8" t="n"/>
+      <c r="H101" s="8" t="n"/>
+      <c r="I101" s="8" t="n"/>
+      <c r="J101" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K101" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L101" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M101" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4021,22 +4699,29 @@
       <c r="D102" s="6" t="n">
         <v>-0.14389</v>
       </c>
-      <c r="E102" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F102" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G102" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H102" s="7" t="inlineStr">
+      <c r="E102" s="6" t="n">
+        <v>-3.370667</v>
+      </c>
+      <c r="F102" s="6" t="n"/>
+      <c r="G102" s="6" t="n"/>
+      <c r="H102" s="6" t="n"/>
+      <c r="I102" s="6" t="n"/>
+      <c r="J102" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K102" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L102" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M102" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4057,22 +4742,29 @@
       <c r="D103" s="8" t="n">
         <v>0.791872</v>
       </c>
-      <c r="E103" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F103" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G103" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H103" s="9" t="inlineStr">
+      <c r="E103" s="8" t="n">
+        <v>-1.321332</v>
+      </c>
+      <c r="F103" s="8" t="n"/>
+      <c r="G103" s="8" t="n"/>
+      <c r="H103" s="8" t="n"/>
+      <c r="I103" s="8" t="n"/>
+      <c r="J103" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K103" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L103" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M103" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4093,22 +4785,29 @@
       <c r="D104" s="6" t="n">
         <v>-0.353837</v>
       </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F104" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G104" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H104" s="7" t="inlineStr">
+      <c r="E104" s="6" t="n">
+        <v>-0.895543</v>
+      </c>
+      <c r="F104" s="6" t="n"/>
+      <c r="G104" s="6" t="n"/>
+      <c r="H104" s="6" t="n"/>
+      <c r="I104" s="6" t="n"/>
+      <c r="J104" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K104" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L104" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M104" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4129,22 +4828,29 @@
       <c r="D105" s="8" t="n">
         <v>-0.085068</v>
       </c>
-      <c r="E105" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F105" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G105" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H105" s="9" t="inlineStr">
+      <c r="E105" s="8" t="n">
+        <v>-0.332249</v>
+      </c>
+      <c r="F105" s="8" t="n"/>
+      <c r="G105" s="8" t="n"/>
+      <c r="H105" s="8" t="n"/>
+      <c r="I105" s="8" t="n"/>
+      <c r="J105" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K105" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L105" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M105" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4165,22 +4871,29 @@
       <c r="D106" s="6" t="n">
         <v>-0.131213</v>
       </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F106" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G106" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H106" s="7" t="inlineStr">
+      <c r="E106" s="6" t="n">
+        <v>-0.496211</v>
+      </c>
+      <c r="F106" s="6" t="n"/>
+      <c r="G106" s="6" t="n"/>
+      <c r="H106" s="6" t="n"/>
+      <c r="I106" s="6" t="n"/>
+      <c r="J106" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K106" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L106" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M106" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4201,22 +4914,29 @@
       <c r="D107" s="8" t="n">
         <v>-0.069019</v>
       </c>
-      <c r="E107" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F107" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G107" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H107" s="9" t="inlineStr">
+      <c r="E107" s="8" t="n">
+        <v>-0.466649</v>
+      </c>
+      <c r="F107" s="8" t="n"/>
+      <c r="G107" s="8" t="n"/>
+      <c r="H107" s="8" t="n"/>
+      <c r="I107" s="8" t="n"/>
+      <c r="J107" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K107" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L107" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M107" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4237,22 +4957,29 @@
       <c r="D108" s="6" t="n">
         <v>0.046638</v>
       </c>
-      <c r="E108" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F108" s="7" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G108" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H108" s="7" t="inlineStr">
+      <c r="E108" s="6" t="n">
+        <v>-0.764721</v>
+      </c>
+      <c r="F108" s="6" t="n"/>
+      <c r="G108" s="6" t="n"/>
+      <c r="H108" s="6" t="n"/>
+      <c r="I108" s="6" t="n"/>
+      <c r="J108" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K108" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M108" s="7" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4273,22 +5000,29 @@
       <c r="D109" s="8" t="n">
         <v>0.029301</v>
       </c>
-      <c r="E109" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="F109" s="9" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="G109" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ee/ee2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="H109" s="9" t="inlineStr">
+      <c r="E109" s="8" t="n">
+        <v>-1.069745</v>
+      </c>
+      <c r="F109" s="8" t="n"/>
+      <c r="G109" s="8" t="n"/>
+      <c r="H109" s="8" t="n"/>
+      <c r="I109" s="8" t="n"/>
+      <c r="J109" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K109" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L109" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M109" s="9" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4296,9 +5030,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/downloads/indicadores/EMOE/EMOE_datos.xlsx
+++ b/downloads/indicadores/EMOE/EMOE_datos.xlsx
@@ -1131,7 +1131,7 @@
         <v>0.504</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>3.668</v>
+        <v>0.76415</v>
       </c>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
@@ -1174,7 +1174,7 @@
         <v>0.171</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>2.919</v>
+        <v>-1.641393</v>
       </c>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
@@ -1217,7 +1217,7 @@
         <v>0.02</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>2.936</v>
+        <v>0.033758</v>
       </c>
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
@@ -1260,7 +1260,7 @@
         <v>-1.413</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>2.378</v>
+        <v>-1.036342</v>
       </c>
       <c r="F22" s="6" t="n"/>
       <c r="G22" s="6" t="n"/>
@@ -1303,7 +1303,7 @@
         <v>-0.892</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>2.264</v>
+        <v>-0.158137</v>
       </c>
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
@@ -1346,7 +1346,7 @@
         <v>-0.993</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>-3.083</v>
+        <v>-10.562397</v>
       </c>
       <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n"/>
@@ -1389,7 +1389,7 @@
         <v>-0.524</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>-4.261</v>
+        <v>-2.141653</v>
       </c>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
@@ -1432,7 +1432,7 @@
         <v>0.842</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>-2.278</v>
+        <v>3.63273</v>
       </c>
       <c r="F26" s="6" t="n"/>
       <c r="G26" s="6" t="n"/>
@@ -1475,7 +1475,7 @@
         <v>-1.299</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>-3.081</v>
+        <v>-1.598997</v>
       </c>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
@@ -1518,7 +1518,7 @@
         <v>-0.759</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>-2.376</v>
+        <v>1.232329</v>
       </c>
       <c r="F28" s="6" t="n"/>
       <c r="G28" s="6" t="n"/>
@@ -1561,7 +1561,7 @@
         <v>0.424</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>-2.507</v>
+        <v>-0.206614</v>
       </c>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
@@ -1604,7 +1604,7 @@
         <v>-0.9399999999999999</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>-4.859</v>
+        <v>-4.382062</v>
       </c>
       <c r="F30" s="6" t="n"/>
       <c r="G30" s="6" t="n"/>
@@ -1647,7 +1647,7 @@
         <v>1.071</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>-4.292</v>
+        <v>1.167722</v>
       </c>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
@@ -1690,7 +1690,7 @@
         <v>-4.384</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>-8.847</v>
+        <v>-8.607958</v>
       </c>
       <c r="F32" s="6" t="n"/>
       <c r="G32" s="6" t="n"/>
@@ -1733,7 +1733,7 @@
         <v>-8.247</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>-17.114</v>
+        <v>-15.658555</v>
       </c>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
@@ -1776,7 +1776,7 @@
         <v>-1.76</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>-17.461</v>
+        <v>-1.567765</v>
       </c>
       <c r="F34" s="6" t="n"/>
       <c r="G34" s="6" t="n"/>
@@ -1819,7 +1819,7 @@
         <v>2.509</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>-14.06</v>
+        <v>6.137927</v>
       </c>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
@@ -1862,7 +1862,7 @@
         <v>2.131</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>-10.936</v>
+        <v>5.755039</v>
       </c>
       <c r="F36" s="6" t="n"/>
       <c r="G36" s="6" t="n"/>
@@ -1905,7 +1905,7 @@
         <v>-0.617</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>-11.029</v>
+        <v>-0.426587</v>
       </c>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
@@ -1948,7 +1948,7 @@
         <v>0.898</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>-10.973</v>
+        <v>0.493442</v>
       </c>
       <c r="F38" s="6" t="n"/>
       <c r="G38" s="6" t="n"/>
@@ -1991,7 +1991,7 @@
         <v>1.245</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>-8.429</v>
+        <v>4.655618</v>
       </c>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
@@ -2034,7 +2034,7 @@
         <v>-0.164</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>-7.834</v>
+        <v>0.970079</v>
       </c>
       <c r="F40" s="6" t="n"/>
       <c r="G40" s="6" t="n"/>
@@ -2077,7 +2077,7 @@
         <v>1.172</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>-7.086</v>
+        <v>1.697639</v>
       </c>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
@@ -2120,7 +2120,7 @@
         <v>-0.108</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>-6.254</v>
+        <v>1.469067</v>
       </c>
       <c r="F42" s="6" t="n"/>
       <c r="G42" s="6" t="n"/>
@@ -2163,7 +2163,7 @@
         <v>1.201</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>-6.124</v>
+        <v>0.562936</v>
       </c>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
@@ -2206,7 +2206,7 @@
         <v>2.961</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>1.221</v>
+        <v>15.46233</v>
       </c>
       <c r="F44" s="6" t="n"/>
       <c r="G44" s="6" t="n"/>
@@ -2249,7 +2249,7 @@
         <v>2.18</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>11.648</v>
+        <v>29.883172</v>
       </c>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
@@ -2292,7 +2292,7 @@
         <v>1.762</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>15.17</v>
+        <v>12.085213</v>
       </c>
       <c r="F46" s="6" t="n"/>
       <c r="G46" s="6" t="n"/>
@@ -2335,7 +2335,7 @@
         <v>2.173</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>14.834</v>
+        <v>-4.006589</v>
       </c>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
@@ -2378,7 +2378,7 @@
         <v>-0.083</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>12.62</v>
+        <v>-7.997474</v>
       </c>
       <c r="F48" s="6" t="n"/>
       <c r="G48" s="6" t="n"/>
@@ -2421,7 +2421,7 @@
         <v>-1.394</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>11.843</v>
+        <v>-1.51613</v>
       </c>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
@@ -2464,7 +2464,7 @@
         <v>1.429</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>12.374</v>
+        <v>0.645431</v>
       </c>
       <c r="F50" s="6" t="n"/>
       <c r="G50" s="6" t="n"/>
@@ -2507,7 +2507,7 @@
         <v>0.828</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>11.957</v>
+        <v>-2.031242</v>
       </c>
       <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="n"/>
@@ -2550,7 +2550,7 @@
         <v>1.446</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>13.567</v>
+        <v>4.157543</v>
       </c>
       <c r="F52" s="6" t="n"/>
       <c r="G52" s="6" t="n"/>
@@ -2593,7 +2593,7 @@
         <v>1.434</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>13.829</v>
+        <v>-0.332301</v>
       </c>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
@@ -2636,7 +2636,7 @@
         <v>-3.44</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>10.497</v>
+        <v>-8.044813</v>
       </c>
       <c r="F54" s="6" t="n"/>
       <c r="G54" s="6" t="n"/>
@@ -2679,7 +2679,7 @@
         <v>0.579</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>9.875</v>
+        <v>-2.204901</v>
       </c>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
@@ -2722,7 +2722,7 @@
         <v>-0.08400000000000001</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>6.83</v>
+        <v>-8.284058999999999</v>
       </c>
       <c r="F56" s="6" t="n"/>
       <c r="G56" s="6" t="n"/>
@@ -2765,7 +2765,7 @@
         <v>1.585</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>6.235</v>
+        <v>-1.955139</v>
       </c>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
@@ -2808,7 +2808,7 @@
         <v>-0.602</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>3.871</v>
+        <v>-5.290859</v>
       </c>
       <c r="F58" s="6" t="n"/>
       <c r="G58" s="6" t="n"/>
@@ -2851,7 +2851,7 @@
         <v>-1.432</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>0.266</v>
+        <v>-7.369635</v>
       </c>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
@@ -2894,7 +2894,7 @@
         <v>-1.056</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>-0.707</v>
+        <v>-1.901034</v>
       </c>
       <c r="F60" s="6" t="n"/>
       <c r="G60" s="6" t="n"/>
@@ -2937,7 +2937,7 @@
         <v>-2.001</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>-1.314</v>
+        <v>-1.258418</v>
       </c>
       <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="n"/>
@@ -2980,7 +2980,7 @@
         <v>-0.488</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>-3.231</v>
+        <v>-3.670806</v>
       </c>
       <c r="F62" s="6" t="n"/>
       <c r="G62" s="6" t="n"/>
@@ -3023,7 +3023,7 @@
         <v>1.884</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>-2.175</v>
+        <v>2.13032</v>
       </c>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
@@ -3066,7 +3066,7 @@
         <v>-0.245</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>-3.866</v>
+        <v>-3.049515</v>
       </c>
       <c r="F64" s="6" t="n"/>
       <c r="G64" s="6" t="n"/>
@@ -3109,7 +3109,7 @@
         <v>-2.201</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>-7.501</v>
+        <v>-6.431919</v>
       </c>
       <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
@@ -3152,7 +3152,7 @@
         <v>1.148</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>-2.913</v>
+        <v>8.001899999999999</v>
       </c>
       <c r="F66" s="6" t="n"/>
       <c r="G66" s="6" t="n"/>
@@ -3195,7 +3195,7 @@
         <v>3.225</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>-0.267</v>
+        <v>5.14733</v>
       </c>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
@@ -3238,7 +3238,7 @@
         <v>1.836</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>1.653</v>
+        <v>3.694463</v>
       </c>
       <c r="F68" s="6" t="n"/>
       <c r="G68" s="6" t="n"/>
@@ -3281,7 +3281,7 @@
         <v>1.165</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>1.233</v>
+        <v>-0.878594</v>
       </c>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
@@ -3324,7 +3324,7 @@
         <v>0.904</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>2.739</v>
+        <v>2.870862</v>
       </c>
       <c r="F70" s="6" t="n"/>
       <c r="G70" s="6" t="n"/>
@@ -3367,7 +3367,7 @@
         <v>-0.725</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>3.446</v>
+        <v>1.516409</v>
       </c>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
@@ -3410,7 +3410,7 @@
         <v>1.581</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>6.083</v>
+        <v>5.366673</v>
       </c>
       <c r="F72" s="6" t="n"/>
       <c r="G72" s="6" t="n"/>
@@ -3453,7 +3453,7 @@
         <v>-0.1</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>7.984</v>
+        <v>4.421398</v>
       </c>
       <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
@@ -3496,7 +3496,7 @@
         <v>-0.075</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>8.397</v>
+        <v>1.028716</v>
       </c>
       <c r="F74" s="6" t="n"/>
       <c r="G74" s="6" t="n"/>
@@ -3539,7 +3539,7 @@
         <v>-0.912</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>5.601</v>
+        <v>-6.270722</v>
       </c>
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
@@ -3582,7 +3582,7 @@
         <v>0.599</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>6.445</v>
+        <v>1.757008</v>
       </c>
       <c r="F76" s="6" t="n"/>
       <c r="G76" s="6" t="n"/>
@@ -3625,7 +3625,7 @@
         <v>0.12</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>8.766</v>
+        <v>5.499725</v>
       </c>
       <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="n"/>
@@ -3668,7 +3668,7 @@
         <v>-0.197</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>7.421</v>
+        <v>-3.207618</v>
       </c>
       <c r="F78" s="6" t="n"/>
       <c r="G78" s="6" t="n"/>
@@ -3711,7 +3711,7 @@
         <v>-0.996</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>3.2</v>
+        <v>-9.104684000000001</v>
       </c>
       <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="n"/>
@@ -3754,7 +3754,7 @@
         <v>-0.218</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>1.146</v>
+        <v>-4.042968</v>
       </c>
       <c r="F80" s="6" t="n"/>
       <c r="G80" s="6" t="n"/>
@@ -3797,7 +3797,7 @@
         <v>0.2</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>0.181</v>
+        <v>-1.807184</v>
       </c>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
@@ -3840,7 +3840,7 @@
         <v>-0.320114</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>-1.043114</v>
+        <v>-2.203846</v>
       </c>
       <c r="F82" s="6" t="n"/>
       <c r="G82" s="6" t="n"/>
@@ -3883,7 +3883,7 @@
         <v>-1.486992</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>-1.805107</v>
+        <v>-1.41129</v>
       </c>
       <c r="F83" s="8" t="n"/>
       <c r="G83" s="8" t="n"/>
@@ -3926,7 +3926,7 @@
         <v>0.342203</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>-3.043904</v>
+        <v>-2.099311</v>
       </c>
       <c r="F84" s="6" t="n"/>
       <c r="G84" s="6" t="n"/>
@@ -3969,7 +3969,7 @@
         <v>-0.75157</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>-3.695474</v>
+        <v>-1.16407</v>
       </c>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
@@ -4012,7 +4012,7 @@
         <v>-1.755021</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>-5.375495</v>
+        <v>-2.989536</v>
       </c>
       <c r="F86" s="6" t="n"/>
       <c r="G86" s="6" t="n"/>
@@ -4055,7 +4055,7 @@
         <v>0.920679</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>-3.542817</v>
+        <v>3.14829</v>
       </c>
       <c r="F87" s="8" t="n"/>
       <c r="G87" s="8" t="n"/>
@@ -4098,7 +4098,7 @@
         <v>-0.421547</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>-4.563364</v>
+        <v>-1.75256</v>
       </c>
       <c r="F88" s="6" t="n"/>
       <c r="G88" s="6" t="n"/>
@@ -4141,7 +4141,7 @@
         <v>0.411983</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>-4.27138</v>
+        <v>0.537234</v>
       </c>
       <c r="F89" s="8" t="n"/>
       <c r="G89" s="8" t="n"/>
@@ -4184,7 +4184,7 @@
         <v>-0.521713</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>-4.596093</v>
+        <v>-0.606911</v>
       </c>
       <c r="F90" s="6" t="n"/>
       <c r="G90" s="6" t="n"/>
@@ -4227,7 +4227,7 @@
         <v>-1.257464</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>-4.857557</v>
+        <v>-0.624376</v>
       </c>
       <c r="F91" s="8" t="n"/>
       <c r="G91" s="8" t="n"/>
@@ -4270,7 +4270,7 @@
         <v>-0.779626</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>-5.419183</v>
+        <v>-1.060847</v>
       </c>
       <c r="F92" s="6" t="n"/>
       <c r="G92" s="6" t="n"/>
@@ -4313,7 +4313,7 @@
         <v>-0.648362</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>-6.267545</v>
+        <v>-1.507667</v>
       </c>
       <c r="F93" s="8" t="n"/>
       <c r="G93" s="8" t="n"/>
@@ -4356,7 +4356,7 @@
         <v>0.032747</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>-5.914683</v>
+        <v>0.579012</v>
       </c>
       <c r="F94" s="6" t="n"/>
       <c r="G94" s="6" t="n"/>
@@ -4399,7 +4399,7 @@
         <v>-0.098581</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>-4.526271</v>
+        <v>2.30939</v>
       </c>
       <c r="F95" s="8" t="n"/>
       <c r="G95" s="8" t="n"/>
@@ -4442,7 +4442,7 @@
         <v>0.344711</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>-4.523763</v>
+        <v>0.059169</v>
       </c>
       <c r="F96" s="6" t="n"/>
       <c r="G96" s="6" t="n"/>
@@ -4485,7 +4485,7 @@
         <v>0.334323</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>-3.437869</v>
+        <v>1.938422</v>
       </c>
       <c r="F97" s="8" t="n"/>
       <c r="G97" s="8" t="n"/>
@@ -4528,7 +4528,7 @@
         <v>0.016742</v>
       </c>
       <c r="E98" s="6" t="n">
-        <v>-1.666106</v>
+        <v>3.250656</v>
       </c>
       <c r="F98" s="6" t="n"/>
       <c r="G98" s="6" t="n"/>
@@ -4571,7 +4571,7 @@
         <v>-0.807123</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>-3.393907</v>
+        <v>-3.270739</v>
       </c>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="8" t="n"/>
@@ -4614,7 +4614,7 @@
         <v>-0.209162</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>-3.181522</v>
+        <v>0.358984</v>
       </c>
       <c r="F100" s="6" t="n"/>
       <c r="G100" s="6" t="n"/>
@@ -4657,7 +4657,7 @@
         <v>-0.154983</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>-3.74849</v>
+        <v>-1.043436</v>
       </c>
       <c r="F101" s="8" t="n"/>
       <c r="G101" s="8" t="n"/>
@@ -4700,7 +4700,7 @@
         <v>-0.14389</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>-3.370667</v>
+        <v>0.662073</v>
       </c>
       <c r="F102" s="6" t="n"/>
       <c r="G102" s="6" t="n"/>
@@ -4743,7 +4743,7 @@
         <v>0.791872</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>-1.321332</v>
+        <v>3.92445</v>
       </c>
       <c r="F103" s="8" t="n"/>
       <c r="G103" s="8" t="n"/>
@@ -4786,7 +4786,7 @@
         <v>-0.353837</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>-0.895543</v>
+        <v>0.821345</v>
       </c>
       <c r="F104" s="6" t="n"/>
       <c r="G104" s="6" t="n"/>
@@ -4829,7 +4829,7 @@
         <v>-0.085068</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>-0.332249</v>
+        <v>1.13274</v>
       </c>
       <c r="F105" s="8" t="n"/>
       <c r="G105" s="8" t="n"/>
@@ -4872,7 +4872,7 @@
         <v>-0.131213</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>-0.496211</v>
+        <v>-0.336063</v>
       </c>
       <c r="F106" s="6" t="n"/>
       <c r="G106" s="6" t="n"/>
@@ -4915,7 +4915,7 @@
         <v>-0.069019</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>-0.466649</v>
+        <v>0.058732</v>
       </c>
       <c r="F107" s="8" t="n"/>
       <c r="G107" s="8" t="n"/>
@@ -4958,7 +4958,7 @@
         <v>0.046638</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>-0.764721</v>
+        <v>-0.60195</v>
       </c>
       <c r="F108" s="6" t="n"/>
       <c r="G108" s="6" t="n"/>
@@ -5001,7 +5001,7 @@
         <v>0.029301</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>-1.069745</v>
+        <v>-0.608084</v>
       </c>
       <c r="F109" s="8" t="n"/>
       <c r="G109" s="8" t="n"/>

--- a/downloads/indicadores/EMOE/EMOE_datos.xlsx
+++ b/downloads/indicadores/EMOE/EMOE_datos.xlsx
@@ -596,10 +596,18 @@
         <v>-0.848</v>
       </c>
       <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
+      <c r="F6" s="6" t="n">
+        <v>50.144</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>44.558</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>53.414</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>46.668</v>
+      </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -637,10 +645,18 @@
         <v>0.122</v>
       </c>
       <c r="E7" s="8" t="n"/>
-      <c r="F7" s="8" t="n"/>
-      <c r="G7" s="8" t="n"/>
-      <c r="H7" s="8" t="n"/>
-      <c r="I7" s="8" t="n"/>
+      <c r="F7" s="8" t="n">
+        <v>51.009</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>45.309</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>52.681</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>46.759</v>
+      </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -678,10 +694,18 @@
         <v>0.92</v>
       </c>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
+      <c r="F8" s="6" t="n">
+        <v>51.97</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>46.026</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>54.572</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>47.205</v>
+      </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -719,10 +743,18 @@
         <v>0.003</v>
       </c>
       <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="8" t="n"/>
+      <c r="F9" s="8" t="n">
+        <v>52.008</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>46.648</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>53.229</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>47.753</v>
+      </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -760,10 +792,18 @@
         <v>-0.855</v>
       </c>
       <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
+      <c r="F10" s="6" t="n">
+        <v>50.967</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>46.858</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>52.22</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>46.847</v>
+      </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -801,10 +841,18 @@
         <v>-0.778</v>
       </c>
       <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="8" t="n"/>
+      <c r="F11" s="8" t="n">
+        <v>49.936</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>45.746</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>52.573</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>45.677</v>
+      </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -842,10 +890,18 @@
         <v>4.354</v>
       </c>
       <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
+      <c r="F12" s="6" t="n">
+        <v>53.001</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>50.325</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>56.46</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>50.816</v>
+      </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -883,10 +939,18 @@
         <v>0.654</v>
       </c>
       <c r="E13" s="8" t="n"/>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="n"/>
-      <c r="H13" s="8" t="n"/>
-      <c r="I13" s="8" t="n"/>
+      <c r="F13" s="8" t="n">
+        <v>53.226</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>51.509</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>56.865</v>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>51.688</v>
+      </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -924,10 +988,18 @@
         <v>-1.141</v>
       </c>
       <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
+      <c r="F14" s="6" t="n">
+        <v>52.794</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>50.06</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>55.91</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>50.189</v>
+      </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -965,10 +1037,18 @@
         <v>-0.496</v>
       </c>
       <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="8" t="n"/>
+      <c r="F15" s="8" t="n">
+        <v>52.278</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>49.549</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>54.93</v>
+      </c>
+      <c r="I15" s="8" t="n">
+        <v>49.952</v>
+      </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1006,10 +1086,18 @@
         <v>-1.464</v>
       </c>
       <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
+      <c r="F16" s="6" t="n">
+        <v>50.975</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>47.584</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>53.675</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>48.407</v>
+      </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1047,10 +1135,18 @@
         <v>0.555</v>
       </c>
       <c r="E17" s="8" t="n"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="8" t="n"/>
+      <c r="F17" s="8" t="n">
+        <v>51.004</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>48.358</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>54.717</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>48.912</v>
+      </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1090,10 +1186,18 @@
       <c r="E18" s="6" t="n">
         <v>3.286</v>
       </c>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n"/>
+      <c r="F18" s="6" t="n">
+        <v>52.962</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>47.435</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>54.194</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>51.53</v>
+      </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1131,12 +1235,20 @@
         <v>0.504</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>3.668</v>
-      </c>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
+        <v>0.76415</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>53.415</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>47.927</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>54.982</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>51.916</v>
+      </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1174,12 +1286,20 @@
         <v>0.171</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>2.919</v>
-      </c>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
+        <v>-1.641393</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>53.622</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>48.044</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>55.745</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>51.779</v>
+      </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1217,12 +1337,20 @@
         <v>0.02</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>2.936</v>
-      </c>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="8" t="n"/>
+        <v>0.033758</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>53.358</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>48.506</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>56.078</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>51.682</v>
+      </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1260,12 +1388,20 @@
         <v>-1.413</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>2.378</v>
-      </c>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
+        <v>-1.036342</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>53.181</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>48.395</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>53.562</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>49.999</v>
+      </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1303,12 +1439,20 @@
         <v>-0.892</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>2.264</v>
-      </c>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="8" t="n"/>
+        <v>-0.158137</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>51.709</v>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>47.852</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>53.495</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>48.883</v>
+      </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1346,12 +1490,20 @@
         <v>-0.993</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>-3.083</v>
-      </c>
-      <c r="F24" s="6" t="n"/>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
-      <c r="I24" s="6" t="n"/>
+        <v>-10.562397</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>50.653</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>47.003</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>51.916</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>48.188</v>
+      </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1389,12 +1541,20 @@
         <v>-0.524</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>-4.261</v>
-      </c>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="8" t="n"/>
+        <v>-2.141653</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>50.317</v>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>46.905</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>51.029</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>47.677</v>
+      </c>
       <c r="J25" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1432,12 +1592,20 @@
         <v>0.842</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>-2.278</v>
-      </c>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n"/>
+        <v>3.63273</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>51.014</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>47.828</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>52.502</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>48.248</v>
+      </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1475,12 +1643,20 @@
         <v>-1.299</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>-3.081</v>
-      </c>
-      <c r="F27" s="8" t="n"/>
-      <c r="G27" s="8" t="n"/>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="8" t="n"/>
+        <v>-1.598997</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>50.226</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>47.166</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>51.411</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>46.48</v>
+      </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1518,12 +1694,20 @@
         <v>-0.759</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>-2.376</v>
-      </c>
-      <c r="F28" s="6" t="n"/>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
-      <c r="I28" s="6" t="n"/>
+        <v>1.232329</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>49.526</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>45.704</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>49.687</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>46.328</v>
+      </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1561,12 +1745,20 @@
         <v>0.424</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>-2.507</v>
-      </c>
-      <c r="F29" s="8" t="n"/>
-      <c r="G29" s="8" t="n"/>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="8" t="n"/>
+        <v>-0.206614</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>49.079</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>47.312</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>51.16</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>46.377</v>
+      </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1604,12 +1796,20 @@
         <v>-0.9399999999999999</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>-4.859</v>
-      </c>
-      <c r="F30" s="6" t="n"/>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
-      <c r="I30" s="6" t="n"/>
+        <v>-4.382062</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>48.445</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>45.917</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>51.535</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>44.718</v>
+      </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1647,12 +1847,20 @@
         <v>1.071</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>-4.292</v>
-      </c>
-      <c r="F31" s="8" t="n"/>
-      <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="n"/>
-      <c r="I31" s="8" t="n"/>
+        <v>1.167722</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>47.757</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>44.829</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>51.263</v>
+      </c>
+      <c r="I31" s="8" t="n">
+        <v>47.721</v>
+      </c>
       <c r="J31" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1690,12 +1898,20 @@
         <v>-4.384</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>-8.847</v>
-      </c>
-      <c r="F32" s="6" t="n"/>
-      <c r="G32" s="6" t="n"/>
-      <c r="H32" s="6" t="n"/>
-      <c r="I32" s="6" t="n"/>
+        <v>-8.607958</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>44.397</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>43.45</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>46.475</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>42.463</v>
+      </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1733,12 +1949,20 @@
         <v>-8.247</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>-17.114</v>
-      </c>
-      <c r="F33" s="8" t="n"/>
-      <c r="G33" s="8" t="n"/>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
+        <v>-15.658555</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>36.578</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>37.197</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>39.131</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>33.157</v>
+      </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1776,12 +2000,20 @@
         <v>-1.76</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>-17.461</v>
-      </c>
-      <c r="F34" s="6" t="n"/>
-      <c r="G34" s="6" t="n"/>
-      <c r="H34" s="6" t="n"/>
-      <c r="I34" s="6" t="n"/>
+        <v>-1.567765</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>34.285</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>34.752</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>37.898</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>31.511</v>
+      </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1819,12 +2051,20 @@
         <v>2.509</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>-14.06</v>
-      </c>
-      <c r="F35" s="8" t="n"/>
-      <c r="G35" s="8" t="n"/>
-      <c r="H35" s="8" t="n"/>
-      <c r="I35" s="8" t="n"/>
+        <v>6.137927</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>37.29</v>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>35.051</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>38.35</v>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>35.287</v>
+      </c>
       <c r="J35" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1862,12 +2102,20 @@
         <v>2.131</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>-10.936</v>
-      </c>
-      <c r="F36" s="6" t="n"/>
-      <c r="G36" s="6" t="n"/>
-      <c r="H36" s="6" t="n"/>
-      <c r="I36" s="6" t="n"/>
+        <v>5.755039</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>39.015</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>39.375</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>41.349</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>36.719</v>
+      </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1905,12 +2153,20 @@
         <v>-0.617</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>-11.029</v>
-      </c>
-      <c r="F37" s="8" t="n"/>
-      <c r="G37" s="8" t="n"/>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="8" t="n"/>
+        <v>-0.426587</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>38.629</v>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>38.464</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>42.073</v>
+      </c>
+      <c r="I37" s="8" t="n">
+        <v>35.371</v>
+      </c>
       <c r="J37" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1948,12 +2204,20 @@
         <v>0.898</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>-10.973</v>
-      </c>
-      <c r="F38" s="6" t="n"/>
-      <c r="G38" s="6" t="n"/>
-      <c r="H38" s="6" t="n"/>
-      <c r="I38" s="6" t="n"/>
+        <v>0.493442</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>41.042</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>40.081</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>41.799</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>36.025</v>
+      </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -1991,12 +2255,20 @@
         <v>1.245</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>-8.429</v>
-      </c>
-      <c r="F39" s="8" t="n"/>
-      <c r="G39" s="8" t="n"/>
-      <c r="H39" s="8" t="n"/>
-      <c r="I39" s="8" t="n"/>
+        <v>4.655618</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>41.767</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>40.883</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>42.921</v>
+      </c>
+      <c r="I39" s="8" t="n">
+        <v>37.661</v>
+      </c>
       <c r="J39" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -2034,12 +2306,20 @@
         <v>-0.164</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>-7.834</v>
-      </c>
-      <c r="F40" s="6" t="n"/>
-      <c r="G40" s="6" t="n"/>
-      <c r="H40" s="6" t="n"/>
-      <c r="I40" s="6" t="n"/>
+        <v>0.970079</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>42.139</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>41.367</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>43.59</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>36.695</v>
+      </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -2077,12 +2357,20 @@
         <v>1.172</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>-7.086</v>
-      </c>
-      <c r="F41" s="8" t="n"/>
-      <c r="G41" s="8" t="n"/>
-      <c r="H41" s="8" t="n"/>
-      <c r="I41" s="8" t="n"/>
+        <v>1.697639</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>42.998</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>41.97</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>44.841</v>
+      </c>
+      <c r="I41" s="8" t="n">
+        <v>38.086</v>
+      </c>
       <c r="J41" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -2120,12 +2408,20 @@
         <v>-0.108</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>-6.254</v>
-      </c>
-      <c r="F42" s="6" t="n"/>
-      <c r="G42" s="6" t="n"/>
-      <c r="H42" s="6" t="n"/>
-      <c r="I42" s="6" t="n"/>
+        <v>1.469067</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>43.668</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>42.347</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>45.468</v>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>37.146</v>
+      </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -2163,12 +2459,20 @@
         <v>1.201</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>-6.124</v>
-      </c>
-      <c r="F43" s="8" t="n"/>
-      <c r="G43" s="8" t="n"/>
-      <c r="H43" s="8" t="n"/>
-      <c r="I43" s="8" t="n"/>
+        <v>0.562936</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>44.653</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>43.085</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>45.675</v>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>39.049</v>
+      </c>
       <c r="J43" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -2206,12 +2510,20 @@
         <v>2.961</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>1.221</v>
-      </c>
-      <c r="F44" s="6" t="n"/>
-      <c r="G44" s="6" t="n"/>
-      <c r="H44" s="6" t="n"/>
-      <c r="I44" s="6" t="n"/>
+        <v>15.46233</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>46.021</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>43.884</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>49.164</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>42.91</v>
+      </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -2249,12 +2561,20 @@
         <v>2.18</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>11.648</v>
-      </c>
-      <c r="F45" s="8" t="n"/>
-      <c r="G45" s="8" t="n"/>
-      <c r="H45" s="8" t="n"/>
-      <c r="I45" s="8" t="n"/>
+        <v>29.883172</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>48.687</v>
+      </c>
+      <c r="G45" s="8" t="n">
+        <v>44.61</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>51.056</v>
+      </c>
+      <c r="I45" s="8" t="n">
+        <v>45.307</v>
+      </c>
       <c r="J45" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -2292,12 +2612,20 @@
         <v>1.762</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>15.17</v>
-      </c>
-      <c r="F46" s="6" t="n"/>
-      <c r="G46" s="6" t="n"/>
-      <c r="H46" s="6" t="n"/>
-      <c r="I46" s="6" t="n"/>
+        <v>12.085213</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>49.692</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>45.781</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>52.246</v>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>47.827</v>
+      </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -2335,12 +2663,20 @@
         <v>2.173</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>14.834</v>
-      </c>
-      <c r="F47" s="8" t="n"/>
-      <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="n"/>
-      <c r="I47" s="8" t="n"/>
+        <v>-4.006589</v>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>51.361</v>
+      </c>
+      <c r="G47" s="8" t="n">
+        <v>47.838</v>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>54.196</v>
+      </c>
+      <c r="I47" s="8" t="n">
+        <v>50.371</v>
+      </c>
       <c r="J47" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -2378,12 +2714,20 @@
         <v>-0.083</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>12.62</v>
-      </c>
-      <c r="F48" s="6" t="n"/>
-      <c r="G48" s="6" t="n"/>
-      <c r="H48" s="6" t="n"/>
-      <c r="I48" s="6" t="n"/>
+        <v>-7.997474</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>51.881</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>49.015</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>54.558</v>
+      </c>
+      <c r="I48" s="6" t="n">
+        <v>49.528</v>
+      </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -2421,12 +2765,20 @@
         <v>-1.394</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>11.843</v>
-      </c>
-      <c r="F49" s="8" t="n"/>
-      <c r="G49" s="8" t="n"/>
-      <c r="H49" s="8" t="n"/>
-      <c r="I49" s="8" t="n"/>
+        <v>-1.51613</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>50.804</v>
+      </c>
+      <c r="G49" s="8" t="n">
+        <v>46.393</v>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>53.506</v>
+      </c>
+      <c r="I49" s="8" t="n">
+        <v>48.062</v>
+      </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -2464,12 +2816,20 @@
         <v>1.429</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>12.374</v>
-      </c>
-      <c r="F50" s="6" t="n"/>
-      <c r="G50" s="6" t="n"/>
-      <c r="H50" s="6" t="n"/>
-      <c r="I50" s="6" t="n"/>
+        <v>0.645431</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>51.636</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>48.16</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>54.933</v>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>49.698</v>
+      </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -2507,12 +2867,20 @@
         <v>0.828</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>11.957</v>
-      </c>
-      <c r="F51" s="8" t="n"/>
-      <c r="G51" s="8" t="n"/>
-      <c r="H51" s="8" t="n"/>
-      <c r="I51" s="8" t="n"/>
+        <v>-2.031242</v>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>52.061</v>
+      </c>
+      <c r="G51" s="8" t="n">
+        <v>48.992</v>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>54.825</v>
+      </c>
+      <c r="I51" s="8" t="n">
+        <v>51.189</v>
+      </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -2550,12 +2918,20 @@
         <v>1.446</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>13.567</v>
-      </c>
-      <c r="F52" s="6" t="n"/>
-      <c r="G52" s="6" t="n"/>
-      <c r="H52" s="6" t="n"/>
-      <c r="I52" s="6" t="n"/>
+        <v>4.157543</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>52.722</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>50.477</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>56.56</v>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>52.84</v>
+      </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -2593,12 +2969,20 @@
         <v>1.434</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>13.829</v>
-      </c>
-      <c r="F53" s="8" t="n"/>
-      <c r="G53" s="8" t="n"/>
-      <c r="H53" s="8" t="n"/>
-      <c r="I53" s="8" t="n"/>
+        <v>-0.332301</v>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>52.703</v>
+      </c>
+      <c r="G53" s="8" t="n">
+        <v>50.895</v>
+      </c>
+      <c r="H53" s="8" t="n">
+        <v>57.434</v>
+      </c>
+      <c r="I53" s="8" t="n">
+        <v>55.435</v>
+      </c>
       <c r="J53" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -2636,12 +3020,20 @@
         <v>-3.44</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>10.497</v>
-      </c>
-      <c r="F54" s="6" t="n"/>
-      <c r="G54" s="6" t="n"/>
-      <c r="H54" s="6" t="n"/>
-      <c r="I54" s="6" t="n"/>
+        <v>-8.044813</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>51.167</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>50.177</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>55.999</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>49.546</v>
+      </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -2679,12 +3071,20 @@
         <v>0.579</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>9.875</v>
-      </c>
-      <c r="F55" s="8" t="n"/>
-      <c r="G55" s="8" t="n"/>
-      <c r="H55" s="8" t="n"/>
-      <c r="I55" s="8" t="n"/>
+        <v>-2.204901</v>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>52.914</v>
+      </c>
+      <c r="G55" s="8" t="n">
+        <v>51.157</v>
+      </c>
+      <c r="H55" s="8" t="n">
+        <v>54.711</v>
+      </c>
+      <c r="I55" s="8" t="n">
+        <v>50.459</v>
+      </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -2722,12 +3122,20 @@
         <v>-0.08400000000000001</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="F56" s="6" t="n"/>
-      <c r="G56" s="6" t="n"/>
-      <c r="H56" s="6" t="n"/>
-      <c r="I56" s="6" t="n"/>
+        <v>-8.284058999999999</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>51.825</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>51.798</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>53.956</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>51.032</v>
+      </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -2765,12 +3173,20 @@
         <v>1.585</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>6.235</v>
-      </c>
-      <c r="F57" s="8" t="n"/>
-      <c r="G57" s="8" t="n"/>
-      <c r="H57" s="8" t="n"/>
-      <c r="I57" s="8" t="n"/>
+        <v>-1.955139</v>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>52.608</v>
+      </c>
+      <c r="G57" s="8" t="n">
+        <v>51.088</v>
+      </c>
+      <c r="H57" s="8" t="n">
+        <v>55.453</v>
+      </c>
+      <c r="I57" s="8" t="n">
+        <v>53.496</v>
+      </c>
       <c r="J57" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -2808,12 +3224,20 @@
         <v>-0.602</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>3.871</v>
-      </c>
-      <c r="F58" s="6" t="n"/>
-      <c r="G58" s="6" t="n"/>
-      <c r="H58" s="6" t="n"/>
-      <c r="I58" s="6" t="n"/>
+        <v>-5.290859</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>52.497</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>49.749</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>54.683</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>52.901</v>
+      </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -2851,12 +3275,20 @@
         <v>-1.432</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="F59" s="8" t="n"/>
-      <c r="G59" s="8" t="n"/>
-      <c r="H59" s="8" t="n"/>
-      <c r="I59" s="8" t="n"/>
+        <v>-7.369635</v>
+      </c>
+      <c r="F59" s="8" t="n">
+        <v>52.168</v>
+      </c>
+      <c r="G59" s="8" t="n">
+        <v>51.099</v>
+      </c>
+      <c r="H59" s="8" t="n">
+        <v>55.841</v>
+      </c>
+      <c r="I59" s="8" t="n">
+        <v>49.078</v>
+      </c>
       <c r="J59" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -2894,12 +3326,20 @@
         <v>-1.056</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>-0.707</v>
-      </c>
-      <c r="F60" s="6" t="n"/>
-      <c r="G60" s="6" t="n"/>
-      <c r="H60" s="6" t="n"/>
-      <c r="I60" s="6" t="n"/>
+        <v>-1.901034</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>51.219</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>55.175</v>
+      </c>
+      <c r="I60" s="6" t="n">
+        <v>47.815</v>
+      </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -2937,12 +3377,20 @@
         <v>-2.001</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>-1.314</v>
-      </c>
-      <c r="F61" s="8" t="n"/>
-      <c r="G61" s="8" t="n"/>
-      <c r="H61" s="8" t="n"/>
-      <c r="I61" s="8" t="n"/>
+        <v>-1.258418</v>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>51.297</v>
+      </c>
+      <c r="G61" s="8" t="n">
+        <v>48.541</v>
+      </c>
+      <c r="H61" s="8" t="n">
+        <v>53.822</v>
+      </c>
+      <c r="I61" s="8" t="n">
+        <v>44.386</v>
+      </c>
       <c r="J61" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -2980,12 +3428,20 @@
         <v>-0.488</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>-3.231</v>
-      </c>
-      <c r="F62" s="6" t="n"/>
-      <c r="G62" s="6" t="n"/>
-      <c r="H62" s="6" t="n"/>
-      <c r="I62" s="6" t="n"/>
+        <v>-3.670806</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>50.889</v>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>50.977</v>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>53.657</v>
+      </c>
+      <c r="I62" s="6" t="n">
+        <v>43.105</v>
+      </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -3023,12 +3479,20 @@
         <v>1.884</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>-2.175</v>
-      </c>
-      <c r="F63" s="8" t="n"/>
-      <c r="G63" s="8" t="n"/>
-      <c r="H63" s="8" t="n"/>
-      <c r="I63" s="8" t="n"/>
+        <v>2.13032</v>
+      </c>
+      <c r="F63" s="8" t="n">
+        <v>50.728</v>
+      </c>
+      <c r="G63" s="8" t="n">
+        <v>51.357</v>
+      </c>
+      <c r="H63" s="8" t="n">
+        <v>52.789</v>
+      </c>
+      <c r="I63" s="8" t="n">
+        <v>47.638</v>
+      </c>
       <c r="J63" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -3066,12 +3530,20 @@
         <v>-0.245</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>-3.866</v>
-      </c>
-      <c r="F64" s="6" t="n"/>
-      <c r="G64" s="6" t="n"/>
-      <c r="H64" s="6" t="n"/>
-      <c r="I64" s="6" t="n"/>
+        <v>-3.049515</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>50.111</v>
+      </c>
+      <c r="G64" s="6" t="n">
+        <v>50.505</v>
+      </c>
+      <c r="H64" s="6" t="n">
+        <v>52.743</v>
+      </c>
+      <c r="I64" s="6" t="n">
+        <v>47.585</v>
+      </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -3109,12 +3581,20 @@
         <v>-2.201</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>-7.501</v>
-      </c>
-      <c r="F65" s="8" t="n"/>
-      <c r="G65" s="8" t="n"/>
-      <c r="H65" s="8" t="n"/>
-      <c r="I65" s="8" t="n"/>
+        <v>-6.431919</v>
+      </c>
+      <c r="F65" s="8" t="n">
+        <v>50.36</v>
+      </c>
+      <c r="G65" s="8" t="n">
+        <v>48.227</v>
+      </c>
+      <c r="H65" s="8" t="n">
+        <v>52.498</v>
+      </c>
+      <c r="I65" s="8" t="n">
+        <v>43.275</v>
+      </c>
       <c r="J65" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -3152,12 +3632,20 @@
         <v>1.148</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>-2.913</v>
-      </c>
-      <c r="F66" s="6" t="n"/>
-      <c r="G66" s="6" t="n"/>
-      <c r="H66" s="6" t="n"/>
-      <c r="I66" s="6" t="n"/>
+        <v>8.001899999999999</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>50.966</v>
+      </c>
+      <c r="G66" s="6" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="H66" s="6" t="n">
+        <v>53.615</v>
+      </c>
+      <c r="I66" s="6" t="n">
+        <v>43.894</v>
+      </c>
       <c r="J66" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -3195,12 +3683,20 @@
         <v>3.225</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>-0.267</v>
-      </c>
-      <c r="F67" s="8" t="n"/>
-      <c r="G67" s="8" t="n"/>
-      <c r="H67" s="8" t="n"/>
-      <c r="I67" s="8" t="n"/>
+        <v>5.14733</v>
+      </c>
+      <c r="F67" s="8" t="n">
+        <v>53.506</v>
+      </c>
+      <c r="G67" s="8" t="n">
+        <v>52.528</v>
+      </c>
+      <c r="H67" s="8" t="n">
+        <v>54.346</v>
+      </c>
+      <c r="I67" s="8" t="n">
+        <v>49.515</v>
+      </c>
       <c r="J67" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -3238,12 +3734,20 @@
         <v>1.836</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>1.653</v>
-      </c>
-      <c r="F68" s="6" t="n"/>
-      <c r="G68" s="6" t="n"/>
-      <c r="H68" s="6" t="n"/>
-      <c r="I68" s="6" t="n"/>
+        <v>3.694463</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>53.419</v>
+      </c>
+      <c r="G68" s="6" t="n">
+        <v>51.35</v>
+      </c>
+      <c r="H68" s="6" t="n">
+        <v>53.577</v>
+      </c>
+      <c r="I68" s="6" t="n">
+        <v>54.174</v>
+      </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -3281,12 +3785,20 @@
         <v>1.165</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>1.233</v>
-      </c>
-      <c r="F69" s="8" t="n"/>
-      <c r="G69" s="8" t="n"/>
-      <c r="H69" s="8" t="n"/>
-      <c r="I69" s="8" t="n"/>
+        <v>-0.878594</v>
+      </c>
+      <c r="F69" s="8" t="n">
+        <v>53.44</v>
+      </c>
+      <c r="G69" s="8" t="n">
+        <v>54.818</v>
+      </c>
+      <c r="H69" s="8" t="n">
+        <v>55.548</v>
+      </c>
+      <c r="I69" s="8" t="n">
+        <v>54.989</v>
+      </c>
       <c r="J69" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -3324,12 +3836,20 @@
         <v>0.904</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>2.739</v>
-      </c>
-      <c r="F70" s="6" t="n"/>
-      <c r="G70" s="6" t="n"/>
-      <c r="H70" s="6" t="n"/>
-      <c r="I70" s="6" t="n"/>
+        <v>2.870862</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>53.61</v>
+      </c>
+      <c r="G70" s="6" t="n">
+        <v>53.334</v>
+      </c>
+      <c r="H70" s="6" t="n">
+        <v>56.038</v>
+      </c>
+      <c r="I70" s="6" t="n">
+        <v>56.923</v>
+      </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -3367,12 +3887,20 @@
         <v>-0.725</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>3.446</v>
-      </c>
-      <c r="F71" s="8" t="n"/>
-      <c r="G71" s="8" t="n"/>
-      <c r="H71" s="8" t="n"/>
-      <c r="I71" s="8" t="n"/>
+        <v>1.516409</v>
+      </c>
+      <c r="F71" s="8" t="n">
+        <v>53.599</v>
+      </c>
+      <c r="G71" s="8" t="n">
+        <v>52.418</v>
+      </c>
+      <c r="H71" s="8" t="n">
+        <v>56.453</v>
+      </c>
+      <c r="I71" s="8" t="n">
+        <v>55.327</v>
+      </c>
       <c r="J71" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -3410,12 +3938,20 @@
         <v>1.581</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>6.083</v>
-      </c>
-      <c r="F72" s="6" t="n"/>
-      <c r="G72" s="6" t="n"/>
-      <c r="H72" s="6" t="n"/>
-      <c r="I72" s="6" t="n"/>
+        <v>5.366673</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>53.657</v>
+      </c>
+      <c r="G72" s="6" t="n">
+        <v>53.188</v>
+      </c>
+      <c r="H72" s="6" t="n">
+        <v>56.343</v>
+      </c>
+      <c r="I72" s="6" t="n">
+        <v>58.635</v>
+      </c>
       <c r="J72" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -3453,12 +3989,20 @@
         <v>-0.1</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>7.984</v>
-      </c>
-      <c r="F73" s="8" t="n"/>
-      <c r="G73" s="8" t="n"/>
-      <c r="H73" s="8" t="n"/>
-      <c r="I73" s="8" t="n"/>
+        <v>4.421398</v>
+      </c>
+      <c r="F73" s="8" t="n">
+        <v>53.275</v>
+      </c>
+      <c r="G73" s="8" t="n">
+        <v>52.503</v>
+      </c>
+      <c r="H73" s="8" t="n">
+        <v>56.542</v>
+      </c>
+      <c r="I73" s="8" t="n">
+        <v>58.631</v>
+      </c>
       <c r="J73" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -3496,12 +4040,20 @@
         <v>-0.075</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>8.397</v>
-      </c>
-      <c r="F74" s="6" t="n"/>
-      <c r="G74" s="6" t="n"/>
-      <c r="H74" s="6" t="n"/>
-      <c r="I74" s="6" t="n"/>
+        <v>1.028716</v>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v>53.66</v>
+      </c>
+      <c r="G74" s="6" t="n">
+        <v>53.171</v>
+      </c>
+      <c r="H74" s="6" t="n">
+        <v>55.637</v>
+      </c>
+      <c r="I74" s="6" t="n">
+        <v>58.618</v>
+      </c>
       <c r="J74" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -3539,12 +4091,20 @@
         <v>-0.912</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>5.601</v>
-      </c>
-      <c r="F75" s="8" t="n"/>
-      <c r="G75" s="8" t="n"/>
-      <c r="H75" s="8" t="n"/>
-      <c r="I75" s="8" t="n"/>
+        <v>-6.270722</v>
+      </c>
+      <c r="F75" s="8" t="n">
+        <v>53.919</v>
+      </c>
+      <c r="G75" s="8" t="n">
+        <v>52.305</v>
+      </c>
+      <c r="H75" s="8" t="n">
+        <v>55.171</v>
+      </c>
+      <c r="I75" s="8" t="n">
+        <v>56.93</v>
+      </c>
       <c r="J75" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -3582,12 +4142,20 @@
         <v>0.599</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>6.445</v>
-      </c>
-      <c r="F76" s="6" t="n"/>
-      <c r="G76" s="6" t="n"/>
-      <c r="H76" s="6" t="n"/>
-      <c r="I76" s="6" t="n"/>
+        <v>1.757008</v>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v>53.748</v>
+      </c>
+      <c r="G76" s="6" t="n">
+        <v>51.766</v>
+      </c>
+      <c r="H76" s="6" t="n">
+        <v>56.308</v>
+      </c>
+      <c r="I76" s="6" t="n">
+        <v>57.838</v>
+      </c>
       <c r="J76" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -3625,12 +4193,20 @@
         <v>0.12</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>8.766</v>
-      </c>
-      <c r="F77" s="8" t="n"/>
-      <c r="G77" s="8" t="n"/>
-      <c r="H77" s="8" t="n"/>
-      <c r="I77" s="8" t="n"/>
+        <v>5.499725</v>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>54.197</v>
+      </c>
+      <c r="G77" s="8" t="n">
+        <v>51.267</v>
+      </c>
+      <c r="H77" s="8" t="n">
+        <v>56.346</v>
+      </c>
+      <c r="I77" s="8" t="n">
+        <v>57.973</v>
+      </c>
       <c r="J77" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -3668,12 +4244,20 @@
         <v>-0.197</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>7.421</v>
-      </c>
-      <c r="F78" s="6" t="n"/>
-      <c r="G78" s="6" t="n"/>
-      <c r="H78" s="6" t="n"/>
-      <c r="I78" s="6" t="n"/>
+        <v>-3.207618</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>54.113</v>
+      </c>
+      <c r="G78" s="6" t="n">
+        <v>52.849</v>
+      </c>
+      <c r="H78" s="6" t="n">
+        <v>54.242</v>
+      </c>
+      <c r="I78" s="6" t="n">
+        <v>58.339</v>
+      </c>
       <c r="J78" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -3711,12 +4295,20 @@
         <v>-0.996</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F79" s="8" t="n"/>
-      <c r="G79" s="8" t="n"/>
-      <c r="H79" s="8" t="n"/>
-      <c r="I79" s="8" t="n"/>
+        <v>-9.104684000000001</v>
+      </c>
+      <c r="F79" s="8" t="n">
+        <v>54.517</v>
+      </c>
+      <c r="G79" s="8" t="n">
+        <v>49.958</v>
+      </c>
+      <c r="H79" s="8" t="n">
+        <v>53.966</v>
+      </c>
+      <c r="I79" s="8" t="n">
+        <v>56.714</v>
+      </c>
       <c r="J79" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -3754,12 +4346,20 @@
         <v>-0.218</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>1.146</v>
-      </c>
-      <c r="F80" s="6" t="n"/>
-      <c r="G80" s="6" t="n"/>
-      <c r="H80" s="6" t="n"/>
-      <c r="I80" s="6" t="n"/>
+        <v>-4.042968</v>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>54.585</v>
+      </c>
+      <c r="G80" s="6" t="n">
+        <v>52.076</v>
+      </c>
+      <c r="H80" s="6" t="n">
+        <v>54.104</v>
+      </c>
+      <c r="I80" s="6" t="n">
+        <v>55.71</v>
+      </c>
       <c r="J80" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -3797,12 +4397,20 @@
         <v>0.2</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>0.181</v>
-      </c>
-      <c r="F81" s="8" t="n"/>
-      <c r="G81" s="8" t="n"/>
-      <c r="H81" s="8" t="n"/>
-      <c r="I81" s="8" t="n"/>
+        <v>-1.807184</v>
+      </c>
+      <c r="F81" s="8" t="n">
+        <v>54.542</v>
+      </c>
+      <c r="G81" s="8" t="n">
+        <v>52.821</v>
+      </c>
+      <c r="H81" s="8" t="n">
+        <v>54.206</v>
+      </c>
+      <c r="I81" s="8" t="n">
+        <v>55.962</v>
+      </c>
       <c r="J81" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -3840,12 +4448,20 @@
         <v>-0.320114</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>-1.043114</v>
-      </c>
-      <c r="F82" s="6" t="n"/>
-      <c r="G82" s="6" t="n"/>
-      <c r="H82" s="6" t="n"/>
-      <c r="I82" s="6" t="n"/>
+        <v>-2.203846</v>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>54.179614</v>
+      </c>
+      <c r="G82" s="6" t="n">
+        <v>50.676569</v>
+      </c>
+      <c r="H82" s="6" t="n">
+        <v>53.474536</v>
+      </c>
+      <c r="I82" s="6" t="n">
+        <v>56.239812</v>
+      </c>
       <c r="J82" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -3883,12 +4499,20 @@
         <v>-1.486992</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>-1.805107</v>
-      </c>
-      <c r="F83" s="8" t="n"/>
-      <c r="G83" s="8" t="n"/>
-      <c r="H83" s="8" t="n"/>
-      <c r="I83" s="8" t="n"/>
+        <v>-1.41129</v>
+      </c>
+      <c r="F83" s="8" t="n">
+        <v>53.132812</v>
+      </c>
+      <c r="G83" s="8" t="n">
+        <v>50.317052</v>
+      </c>
+      <c r="H83" s="8" t="n">
+        <v>53.449466</v>
+      </c>
+      <c r="I83" s="8" t="n">
+        <v>53.576937</v>
+      </c>
       <c r="J83" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -3926,12 +4550,20 @@
         <v>0.342203</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>-3.043904</v>
-      </c>
-      <c r="F84" s="6" t="n"/>
-      <c r="G84" s="6" t="n"/>
-      <c r="H84" s="6" t="n"/>
-      <c r="I84" s="6" t="n"/>
+        <v>-2.099311</v>
+      </c>
+      <c r="F84" s="6" t="n">
+        <v>52.989241</v>
+      </c>
+      <c r="G84" s="6" t="n">
+        <v>50.622791</v>
+      </c>
+      <c r="H84" s="6" t="n">
+        <v>53.085435</v>
+      </c>
+      <c r="I84" s="6" t="n">
+        <v>54.510294</v>
+      </c>
       <c r="J84" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -3969,12 +4601,20 @@
         <v>-0.75157</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>-3.695474</v>
-      </c>
-      <c r="F85" s="8" t="n"/>
-      <c r="G85" s="8" t="n"/>
-      <c r="H85" s="8" t="n"/>
-      <c r="I85" s="8" t="n"/>
+        <v>-1.16407</v>
+      </c>
+      <c r="F85" s="8" t="n">
+        <v>52.885945</v>
+      </c>
+      <c r="G85" s="8" t="n">
+        <v>51.122903</v>
+      </c>
+      <c r="H85" s="8" t="n">
+        <v>52.604894</v>
+      </c>
+      <c r="I85" s="8" t="n">
+        <v>53.06938</v>
+      </c>
       <c r="J85" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -4012,12 +4652,20 @@
         <v>-1.755021</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>-5.375495</v>
-      </c>
-      <c r="F86" s="6" t="n"/>
-      <c r="G86" s="6" t="n"/>
-      <c r="H86" s="6" t="n"/>
-      <c r="I86" s="6" t="n"/>
+        <v>-2.989536</v>
+      </c>
+      <c r="F86" s="6" t="n">
+        <v>51.576526</v>
+      </c>
+      <c r="G86" s="6" t="n">
+        <v>47.887594</v>
+      </c>
+      <c r="H86" s="6" t="n">
+        <v>51.522499</v>
+      </c>
+      <c r="I86" s="6" t="n">
+        <v>51.06508</v>
+      </c>
       <c r="J86" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -4055,12 +4703,20 @@
         <v>0.920679</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>-3.542817</v>
-      </c>
-      <c r="F87" s="8" t="n"/>
-      <c r="G87" s="8" t="n"/>
-      <c r="H87" s="8" t="n"/>
-      <c r="I87" s="8" t="n"/>
+        <v>3.14829</v>
+      </c>
+      <c r="F87" s="8" t="n">
+        <v>51.978727</v>
+      </c>
+      <c r="G87" s="8" t="n">
+        <v>48.998174</v>
+      </c>
+      <c r="H87" s="8" t="n">
+        <v>52.32137</v>
+      </c>
+      <c r="I87" s="8" t="n">
+        <v>52.248185</v>
+      </c>
       <c r="J87" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -4098,12 +4754,20 @@
         <v>-0.421547</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>-4.563364</v>
-      </c>
-      <c r="F88" s="6" t="n"/>
-      <c r="G88" s="6" t="n"/>
-      <c r="H88" s="6" t="n"/>
-      <c r="I88" s="6" t="n"/>
+        <v>-1.75256</v>
+      </c>
+      <c r="F88" s="6" t="n">
+        <v>51.622676</v>
+      </c>
+      <c r="G88" s="6" t="n">
+        <v>49.201964</v>
+      </c>
+      <c r="H88" s="6" t="n">
+        <v>51.863878</v>
+      </c>
+      <c r="I88" s="6" t="n">
+        <v>51.688565</v>
+      </c>
       <c r="J88" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -4141,12 +4805,20 @@
         <v>0.411983</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>-4.27138</v>
-      </c>
-      <c r="F89" s="8" t="n"/>
-      <c r="G89" s="8" t="n"/>
-      <c r="H89" s="8" t="n"/>
-      <c r="I89" s="8" t="n"/>
+        <v>0.537234</v>
+      </c>
+      <c r="F89" s="8" t="n">
+        <v>50.91615</v>
+      </c>
+      <c r="G89" s="8" t="n">
+        <v>48.748217</v>
+      </c>
+      <c r="H89" s="8" t="n">
+        <v>52.017722</v>
+      </c>
+      <c r="I89" s="8" t="n">
+        <v>52.92183</v>
+      </c>
       <c r="J89" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -4184,12 +4856,20 @@
         <v>-0.521713</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>-4.596093</v>
-      </c>
-      <c r="F90" s="6" t="n"/>
-      <c r="G90" s="6" t="n"/>
-      <c r="H90" s="6" t="n"/>
-      <c r="I90" s="6" t="n"/>
+        <v>-0.606911</v>
+      </c>
+      <c r="F90" s="6" t="n">
+        <v>51.362162</v>
+      </c>
+      <c r="G90" s="6" t="n">
+        <v>48.098086</v>
+      </c>
+      <c r="H90" s="6" t="n">
+        <v>52.463376</v>
+      </c>
+      <c r="I90" s="6" t="n">
+        <v>51.487236</v>
+      </c>
       <c r="J90" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -4227,12 +4907,20 @@
         <v>-1.257464</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>-4.857557</v>
-      </c>
-      <c r="F91" s="8" t="n"/>
-      <c r="G91" s="8" t="n"/>
-      <c r="H91" s="8" t="n"/>
-      <c r="I91" s="8" t="n"/>
+        <v>-0.624376</v>
+      </c>
+      <c r="F91" s="8" t="n">
+        <v>50.547437</v>
+      </c>
+      <c r="G91" s="8" t="n">
+        <v>46.76653</v>
+      </c>
+      <c r="H91" s="8" t="n">
+        <v>50.564832</v>
+      </c>
+      <c r="I91" s="8" t="n">
+        <v>50.36792</v>
+      </c>
       <c r="J91" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -4270,12 +4958,20 @@
         <v>-0.779626</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>-5.419183</v>
-      </c>
-      <c r="F92" s="6" t="n"/>
-      <c r="G92" s="6" t="n"/>
-      <c r="H92" s="6" t="n"/>
-      <c r="I92" s="6" t="n"/>
+        <v>-1.060847</v>
+      </c>
+      <c r="F92" s="6" t="n">
+        <v>50.202057</v>
+      </c>
+      <c r="G92" s="6" t="n">
+        <v>46.853136</v>
+      </c>
+      <c r="H92" s="6" t="n">
+        <v>49.188614</v>
+      </c>
+      <c r="I92" s="6" t="n">
+        <v>49.517803</v>
+      </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -4313,12 +5009,20 @@
         <v>-0.648362</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>-6.267545</v>
-      </c>
-      <c r="F93" s="8" t="n"/>
-      <c r="G93" s="8" t="n"/>
-      <c r="H93" s="8" t="n"/>
-      <c r="I93" s="8" t="n"/>
+        <v>-1.507667</v>
+      </c>
+      <c r="F93" s="8" t="n">
+        <v>48.690879</v>
+      </c>
+      <c r="G93" s="8" t="n">
+        <v>46.683058</v>
+      </c>
+      <c r="H93" s="8" t="n">
+        <v>47.264022</v>
+      </c>
+      <c r="I93" s="8" t="n">
+        <v>49.820923</v>
+      </c>
       <c r="J93" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -4356,12 +5060,20 @@
         <v>0.032747</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>-5.914683</v>
-      </c>
-      <c r="F94" s="6" t="n"/>
-      <c r="G94" s="6" t="n"/>
-      <c r="H94" s="6" t="n"/>
-      <c r="I94" s="6" t="n"/>
+        <v>0.579012</v>
+      </c>
+      <c r="F94" s="6" t="n">
+        <v>49.843553</v>
+      </c>
+      <c r="G94" s="6" t="n">
+        <v>46.355094</v>
+      </c>
+      <c r="H94" s="6" t="n">
+        <v>46.755586</v>
+      </c>
+      <c r="I94" s="6" t="n">
+        <v>49.687044</v>
+      </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -4399,12 +5111,20 @@
         <v>-0.098581</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>-4.526271</v>
-      </c>
-      <c r="F95" s="8" t="n"/>
-      <c r="G95" s="8" t="n"/>
-      <c r="H95" s="8" t="n"/>
-      <c r="I95" s="8" t="n"/>
+        <v>2.30939</v>
+      </c>
+      <c r="F95" s="8" t="n">
+        <v>49.228847</v>
+      </c>
+      <c r="G95" s="8" t="n">
+        <v>47.481149</v>
+      </c>
+      <c r="H95" s="8" t="n">
+        <v>47.550991</v>
+      </c>
+      <c r="I95" s="8" t="n">
+        <v>49.1228</v>
+      </c>
       <c r="J95" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -4442,12 +5162,20 @@
         <v>0.344711</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>-4.523763</v>
-      </c>
-      <c r="F96" s="6" t="n"/>
-      <c r="G96" s="6" t="n"/>
-      <c r="H96" s="6" t="n"/>
-      <c r="I96" s="6" t="n"/>
+        <v>0.059169</v>
+      </c>
+      <c r="F96" s="6" t="n">
+        <v>49.341468</v>
+      </c>
+      <c r="G96" s="6" t="n">
+        <v>47.049596</v>
+      </c>
+      <c r="H96" s="6" t="n">
+        <v>47.151559</v>
+      </c>
+      <c r="I96" s="6" t="n">
+        <v>50.110607</v>
+      </c>
       <c r="J96" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -4485,12 +5213,20 @@
         <v>0.334323</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>-3.437869</v>
-      </c>
-      <c r="F97" s="8" t="n"/>
-      <c r="G97" s="8" t="n"/>
-      <c r="H97" s="8" t="n"/>
-      <c r="I97" s="8" t="n"/>
+        <v>1.938422</v>
+      </c>
+      <c r="F97" s="8" t="n">
+        <v>49.210834</v>
+      </c>
+      <c r="G97" s="8" t="n">
+        <v>46.197266</v>
+      </c>
+      <c r="H97" s="8" t="n">
+        <v>48.49971</v>
+      </c>
+      <c r="I97" s="8" t="n">
+        <v>50.381451</v>
+      </c>
       <c r="J97" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -4528,12 +5264,20 @@
         <v>0.016742</v>
       </c>
       <c r="E98" s="6" t="n">
-        <v>-1.666106</v>
-      </c>
-      <c r="F98" s="6" t="n"/>
-      <c r="G98" s="6" t="n"/>
-      <c r="H98" s="6" t="n"/>
-      <c r="I98" s="6" t="n"/>
+        <v>3.250656</v>
+      </c>
+      <c r="F98" s="6" t="n">
+        <v>49.155734</v>
+      </c>
+      <c r="G98" s="6" t="n">
+        <v>46.493502</v>
+      </c>
+      <c r="H98" s="6" t="n">
+        <v>48.186482</v>
+      </c>
+      <c r="I98" s="6" t="n">
+        <v>50.543125</v>
+      </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -4571,12 +5315,20 @@
         <v>-0.807123</v>
       </c>
       <c r="E99" s="8" t="n">
-        <v>-3.393907</v>
-      </c>
-      <c r="F99" s="8" t="n"/>
-      <c r="G99" s="8" t="n"/>
-      <c r="H99" s="8" t="n"/>
-      <c r="I99" s="8" t="n"/>
+        <v>-3.270739</v>
+      </c>
+      <c r="F99" s="8" t="n">
+        <v>48.83249</v>
+      </c>
+      <c r="G99" s="8" t="n">
+        <v>45.847665</v>
+      </c>
+      <c r="H99" s="8" t="n">
+        <v>47.870006</v>
+      </c>
+      <c r="I99" s="8" t="n">
+        <v>49.230472</v>
+      </c>
       <c r="J99" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -4614,12 +5366,20 @@
         <v>-0.209162</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>-3.181522</v>
-      </c>
-      <c r="F100" s="6" t="n"/>
-      <c r="G100" s="6" t="n"/>
-      <c r="H100" s="6" t="n"/>
-      <c r="I100" s="6" t="n"/>
+        <v>0.358984</v>
+      </c>
+      <c r="F100" s="6" t="n">
+        <v>48.233571</v>
+      </c>
+      <c r="G100" s="6" t="n">
+        <v>46.046766</v>
+      </c>
+      <c r="H100" s="6" t="n">
+        <v>47.73379</v>
+      </c>
+      <c r="I100" s="6" t="n">
+        <v>49.08107</v>
+      </c>
       <c r="J100" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -4657,12 +5417,20 @@
         <v>-0.154983</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>-3.74849</v>
-      </c>
-      <c r="F101" s="8" t="n"/>
-      <c r="G101" s="8" t="n"/>
-      <c r="H101" s="8" t="n"/>
-      <c r="I101" s="8" t="n"/>
+        <v>-1.043436</v>
+      </c>
+      <c r="F101" s="8" t="n">
+        <v>48.199845</v>
+      </c>
+      <c r="G101" s="8" t="n">
+        <v>45.064614</v>
+      </c>
+      <c r="H101" s="8" t="n">
+        <v>47.725481</v>
+      </c>
+      <c r="I101" s="8" t="n">
+        <v>48.962478</v>
+      </c>
       <c r="J101" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -4700,12 +5468,20 @@
         <v>-0.14389</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>-3.370667</v>
-      </c>
-      <c r="F102" s="6" t="n"/>
-      <c r="G102" s="6" t="n"/>
-      <c r="H102" s="6" t="n"/>
-      <c r="I102" s="6" t="n"/>
+        <v>0.662073</v>
+      </c>
+      <c r="F102" s="6" t="n">
+        <v>48.032404</v>
+      </c>
+      <c r="G102" s="6" t="n">
+        <v>45.501564</v>
+      </c>
+      <c r="H102" s="6" t="n">
+        <v>47.135756</v>
+      </c>
+      <c r="I102" s="6" t="n">
+        <v>48.93954</v>
+      </c>
       <c r="J102" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -4743,12 +5519,20 @@
         <v>0.791872</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>-1.321332</v>
-      </c>
-      <c r="F103" s="8" t="n"/>
-      <c r="G103" s="8" t="n"/>
-      <c r="H103" s="8" t="n"/>
-      <c r="I103" s="8" t="n"/>
+        <v>3.92445</v>
+      </c>
+      <c r="F103" s="8" t="n">
+        <v>48.432033</v>
+      </c>
+      <c r="G103" s="8" t="n">
+        <v>46.529004</v>
+      </c>
+      <c r="H103" s="8" t="n">
+        <v>48.708475</v>
+      </c>
+      <c r="I103" s="8" t="n">
+        <v>49.466133</v>
+      </c>
       <c r="J103" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -4786,12 +5570,20 @@
         <v>-0.353837</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>-0.895543</v>
-      </c>
-      <c r="F104" s="6" t="n"/>
-      <c r="G104" s="6" t="n"/>
-      <c r="H104" s="6" t="n"/>
-      <c r="I104" s="6" t="n"/>
+        <v>0.821345</v>
+      </c>
+      <c r="F104" s="6" t="n">
+        <v>47.946339</v>
+      </c>
+      <c r="G104" s="6" t="n">
+        <v>47.83974</v>
+      </c>
+      <c r="H104" s="6" t="n">
+        <v>49.009558</v>
+      </c>
+      <c r="I104" s="6" t="n">
+        <v>48.502866</v>
+      </c>
       <c r="J104" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -4829,12 +5621,20 @@
         <v>-0.085068</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>-0.332249</v>
-      </c>
-      <c r="F105" s="8" t="n"/>
-      <c r="G105" s="8" t="n"/>
-      <c r="H105" s="8" t="n"/>
-      <c r="I105" s="8" t="n"/>
+        <v>1.13274</v>
+      </c>
+      <c r="F105" s="8" t="n">
+        <v>48.327254</v>
+      </c>
+      <c r="G105" s="8" t="n">
+        <v>48.111931</v>
+      </c>
+      <c r="H105" s="8" t="n">
+        <v>49.031304</v>
+      </c>
+      <c r="I105" s="8" t="n">
+        <v>48.076703</v>
+      </c>
       <c r="J105" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -4872,12 +5672,20 @@
         <v>-0.131213</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>-0.496211</v>
-      </c>
-      <c r="F106" s="6" t="n"/>
-      <c r="G106" s="6" t="n"/>
-      <c r="H106" s="6" t="n"/>
-      <c r="I106" s="6" t="n"/>
+        <v>-0.336063</v>
+      </c>
+      <c r="F106" s="6" t="n">
+        <v>47.783735</v>
+      </c>
+      <c r="G106" s="6" t="n">
+        <v>47.739796</v>
+      </c>
+      <c r="H106" s="6" t="n">
+        <v>48.310078</v>
+      </c>
+      <c r="I106" s="6" t="n">
+        <v>48.484834</v>
+      </c>
       <c r="J106" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -4915,12 +5723,20 @@
         <v>-0.069019</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>-0.466649</v>
-      </c>
-      <c r="F107" s="8" t="n"/>
-      <c r="G107" s="8" t="n"/>
-      <c r="H107" s="8" t="n"/>
-      <c r="I107" s="8" t="n"/>
+        <v>0.058732</v>
+      </c>
+      <c r="F107" s="8" t="n">
+        <v>48.03239</v>
+      </c>
+      <c r="G107" s="8" t="n">
+        <v>46.252625</v>
+      </c>
+      <c r="H107" s="8" t="n">
+        <v>48.91357</v>
+      </c>
+      <c r="I107" s="8" t="n">
+        <v>48.212931</v>
+      </c>
       <c r="J107" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -4958,12 +5774,20 @@
         <v>0.046638</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>-0.764721</v>
-      </c>
-      <c r="F108" s="6" t="n"/>
-      <c r="G108" s="6" t="n"/>
-      <c r="H108" s="6" t="n"/>
-      <c r="I108" s="6" t="n"/>
+        <v>-0.60195</v>
+      </c>
+      <c r="F108" s="6" t="n">
+        <v>47.907922</v>
+      </c>
+      <c r="G108" s="6" t="n">
+        <v>47.126658</v>
+      </c>
+      <c r="H108" s="6" t="n">
+        <v>48.257084</v>
+      </c>
+      <c r="I108" s="6" t="n">
+        <v>48.529883</v>
+      </c>
       <c r="J108" s="7" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -5001,12 +5825,20 @@
         <v>0.029301</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>-1.069745</v>
-      </c>
-      <c r="F109" s="8" t="n"/>
-      <c r="G109" s="8" t="n"/>
-      <c r="H109" s="8" t="n"/>
-      <c r="I109" s="8" t="n"/>
+        <v>-0.608084</v>
+      </c>
+      <c r="F109" s="8" t="n">
+        <v>47.997733</v>
+      </c>
+      <c r="G109" s="8" t="n">
+        <v>47.498528</v>
+      </c>
+      <c r="H109" s="8" t="n">
+        <v>48.000377</v>
+      </c>
+      <c r="I109" s="8" t="n">
+        <v>48.608038</v>
+      </c>
       <c r="J109" s="9" t="inlineStr">
         <is>
           <t>Definitivo</t>

--- a/downloads/indicadores/EMOE/EMOE_datos.xlsx
+++ b/downloads/indicadores/EMOE/EMOE_datos.xlsx
@@ -96,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,8 +106,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -592,10 +594,10 @@
       <c r="C6" s="6" t="n">
         <v>48.793</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="7" t="n">
         <v>-0.848</v>
       </c>
-      <c r="E6" s="6" t="n"/>
+      <c r="E6" s="7" t="n"/>
       <c r="F6" s="6" t="n">
         <v>50.144</v>
       </c>
@@ -608,22 +610,22 @@
       <c r="I6" s="6" t="n">
         <v>46.668</v>
       </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -638,41 +640,41 @@
       <c r="B7" s="5" t="n">
         <v>43132</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="9" t="n">
         <v>48.915</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="10" t="n">
         <v>0.122</v>
       </c>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="8" t="n">
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="9" t="n">
         <v>51.009</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G7" s="9" t="n">
         <v>45.309</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="9" t="n">
         <v>52.681</v>
       </c>
-      <c r="I7" s="8" t="n">
+      <c r="I7" s="9" t="n">
         <v>46.759</v>
       </c>
-      <c r="J7" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M7" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -690,10 +692,10 @@
       <c r="C8" s="6" t="n">
         <v>49.835</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="7" t="n">
         <v>0.92</v>
       </c>
-      <c r="E8" s="6" t="n"/>
+      <c r="E8" s="7" t="n"/>
       <c r="F8" s="6" t="n">
         <v>51.97</v>
       </c>
@@ -706,22 +708,22 @@
       <c r="I8" s="6" t="n">
         <v>47.205</v>
       </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -736,41 +738,41 @@
       <c r="B9" s="5" t="n">
         <v>43191</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="9" t="n">
         <v>49.838</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="10" t="n">
         <v>0.003</v>
       </c>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="n">
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="9" t="n">
         <v>52.008</v>
       </c>
-      <c r="G9" s="8" t="n">
+      <c r="G9" s="9" t="n">
         <v>46.648</v>
       </c>
-      <c r="H9" s="8" t="n">
+      <c r="H9" s="9" t="n">
         <v>53.229</v>
       </c>
-      <c r="I9" s="8" t="n">
+      <c r="I9" s="9" t="n">
         <v>47.753</v>
       </c>
-      <c r="J9" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M9" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -788,10 +790,10 @@
       <c r="C10" s="6" t="n">
         <v>48.983</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="7" t="n">
         <v>-0.855</v>
       </c>
-      <c r="E10" s="6" t="n"/>
+      <c r="E10" s="7" t="n"/>
       <c r="F10" s="6" t="n">
         <v>50.967</v>
       </c>
@@ -804,22 +806,22 @@
       <c r="I10" s="6" t="n">
         <v>46.847</v>
       </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L10" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M10" s="7" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -834,41 +836,41 @@
       <c r="B11" s="5" t="n">
         <v>43252</v>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="9" t="n">
         <v>48.205</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="10" t="n">
         <v>-0.778</v>
       </c>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n">
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="9" t="n">
         <v>49.936</v>
       </c>
-      <c r="G11" s="8" t="n">
+      <c r="G11" s="9" t="n">
         <v>45.746</v>
       </c>
-      <c r="H11" s="8" t="n">
+      <c r="H11" s="9" t="n">
         <v>52.573</v>
       </c>
-      <c r="I11" s="8" t="n">
+      <c r="I11" s="9" t="n">
         <v>45.677</v>
       </c>
-      <c r="J11" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K11" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M11" s="9" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M11" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -886,10 +888,10 @@
       <c r="C12" s="6" t="n">
         <v>52.559</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="7" t="n">
         <v>4.354</v>
       </c>
-      <c r="E12" s="6" t="n"/>
+      <c r="E12" s="7" t="n"/>
       <c r="F12" s="6" t="n">
         <v>53.001</v>
       </c>
@@ -902,22 +904,22 @@
       <c r="I12" s="6" t="n">
         <v>50.816</v>
       </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="inlineStr">
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -932,41 +934,41 @@
       <c r="B13" s="5" t="n">
         <v>43313</v>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C13" s="9" t="n">
         <v>53.213</v>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="10" t="n">
         <v>0.654</v>
       </c>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="8" t="n">
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="9" t="n">
         <v>53.226</v>
       </c>
-      <c r="G13" s="8" t="n">
+      <c r="G13" s="9" t="n">
         <v>51.509</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="9" t="n">
         <v>56.865</v>
       </c>
-      <c r="I13" s="8" t="n">
+      <c r="I13" s="9" t="n">
         <v>51.688</v>
       </c>
-      <c r="J13" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K13" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L13" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K13" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M13" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -984,10 +986,10 @@
       <c r="C14" s="6" t="n">
         <v>52.072</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="7" t="n">
         <v>-1.141</v>
       </c>
-      <c r="E14" s="6" t="n"/>
+      <c r="E14" s="7" t="n"/>
       <c r="F14" s="6" t="n">
         <v>52.794</v>
       </c>
@@ -1000,22 +1002,22 @@
       <c r="I14" s="6" t="n">
         <v>50.189</v>
       </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M14" s="7" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1030,41 +1032,41 @@
       <c r="B15" s="5" t="n">
         <v>43374</v>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C15" s="9" t="n">
         <v>51.576</v>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D15" s="10" t="n">
         <v>-0.496</v>
       </c>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n">
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="9" t="n">
         <v>52.278</v>
       </c>
-      <c r="G15" s="8" t="n">
+      <c r="G15" s="9" t="n">
         <v>49.549</v>
       </c>
-      <c r="H15" s="8" t="n">
+      <c r="H15" s="9" t="n">
         <v>54.93</v>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="I15" s="9" t="n">
         <v>49.952</v>
       </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M15" s="9" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K15" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M15" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1082,10 +1084,10 @@
       <c r="C16" s="6" t="n">
         <v>50.112</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="7" t="n">
         <v>-1.464</v>
       </c>
-      <c r="E16" s="6" t="n"/>
+      <c r="E16" s="7" t="n"/>
       <c r="F16" s="6" t="n">
         <v>50.975</v>
       </c>
@@ -1098,22 +1100,22 @@
       <c r="I16" s="6" t="n">
         <v>48.407</v>
       </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M16" s="7" t="inlineStr">
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1128,41 +1130,41 @@
       <c r="B17" s="5" t="n">
         <v>43435</v>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C17" s="9" t="n">
         <v>50.667</v>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D17" s="10" t="n">
         <v>0.555</v>
       </c>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="8" t="n">
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="9" t="n">
         <v>51.004</v>
       </c>
-      <c r="G17" s="8" t="n">
+      <c r="G17" s="9" t="n">
         <v>48.358</v>
       </c>
-      <c r="H17" s="8" t="n">
+      <c r="H17" s="9" t="n">
         <v>54.717</v>
       </c>
-      <c r="I17" s="8" t="n">
+      <c r="I17" s="9" t="n">
         <v>48.912</v>
       </c>
-      <c r="J17" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K17" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L17" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M17" s="9" t="inlineStr">
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L17" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M17" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1180,10 +1182,10 @@
       <c r="C18" s="6" t="n">
         <v>52.079</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="7" t="n">
         <v>1.412</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="7" t="n">
         <v>3.286</v>
       </c>
       <c r="F18" s="6" t="n">
@@ -1198,22 +1200,22 @@
       <c r="I18" s="6" t="n">
         <v>51.53</v>
       </c>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M18" s="7" t="inlineStr">
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1228,43 +1230,43 @@
       <c r="B19" s="5" t="n">
         <v>43497</v>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C19" s="9" t="n">
         <v>52.583</v>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="D19" s="10" t="n">
         <v>0.504</v>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="E19" s="10" t="n">
         <v>0.76415</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="9" t="n">
         <v>53.415</v>
       </c>
-      <c r="G19" s="8" t="n">
+      <c r="G19" s="9" t="n">
         <v>47.927</v>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="H19" s="9" t="n">
         <v>54.982</v>
       </c>
-      <c r="I19" s="8" t="n">
+      <c r="I19" s="9" t="n">
         <v>51.916</v>
       </c>
-      <c r="J19" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K19" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L19" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M19" s="9" t="inlineStr">
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K19" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L19" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M19" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1282,10 +1284,10 @@
       <c r="C20" s="6" t="n">
         <v>52.754</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="7" t="n">
         <v>0.171</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="7" t="n">
         <v>-1.641393</v>
       </c>
       <c r="F20" s="6" t="n">
@@ -1300,22 +1302,22 @@
       <c r="I20" s="6" t="n">
         <v>51.779</v>
       </c>
-      <c r="J20" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L20" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M20" s="7" t="inlineStr">
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1330,43 +1332,43 @@
       <c r="B21" s="5" t="n">
         <v>43556</v>
       </c>
-      <c r="C21" s="8" t="n">
+      <c r="C21" s="9" t="n">
         <v>52.774</v>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="10" t="n">
         <v>0.02</v>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="E21" s="10" t="n">
         <v>0.033758</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="9" t="n">
         <v>53.358</v>
       </c>
-      <c r="G21" s="8" t="n">
+      <c r="G21" s="9" t="n">
         <v>48.506</v>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="9" t="n">
         <v>56.078</v>
       </c>
-      <c r="I21" s="8" t="n">
+      <c r="I21" s="9" t="n">
         <v>51.682</v>
       </c>
-      <c r="J21" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K21" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L21" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M21" s="9" t="inlineStr">
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K21" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L21" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M21" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1384,10 +1386,10 @@
       <c r="C22" s="6" t="n">
         <v>51.361</v>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="7" t="n">
         <v>-1.413</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="7" t="n">
         <v>-1.036342</v>
       </c>
       <c r="F22" s="6" t="n">
@@ -1402,22 +1404,22 @@
       <c r="I22" s="6" t="n">
         <v>49.999</v>
       </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L22" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="inlineStr">
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1432,43 +1434,43 @@
       <c r="B23" s="5" t="n">
         <v>43617</v>
       </c>
-      <c r="C23" s="8" t="n">
+      <c r="C23" s="9" t="n">
         <v>50.469</v>
       </c>
-      <c r="D23" s="8" t="n">
+      <c r="D23" s="10" t="n">
         <v>-0.892</v>
       </c>
-      <c r="E23" s="8" t="n">
+      <c r="E23" s="10" t="n">
         <v>-0.158137</v>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="F23" s="9" t="n">
         <v>51.709</v>
       </c>
-      <c r="G23" s="8" t="n">
+      <c r="G23" s="9" t="n">
         <v>47.852</v>
       </c>
-      <c r="H23" s="8" t="n">
+      <c r="H23" s="9" t="n">
         <v>53.495</v>
       </c>
-      <c r="I23" s="8" t="n">
+      <c r="I23" s="9" t="n">
         <v>48.883</v>
       </c>
-      <c r="J23" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K23" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L23" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M23" s="9" t="inlineStr">
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K23" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L23" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M23" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1486,10 +1488,10 @@
       <c r="C24" s="6" t="n">
         <v>49.476</v>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="7" t="n">
         <v>-0.993</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="7" t="n">
         <v>-10.562397</v>
       </c>
       <c r="F24" s="6" t="n">
@@ -1504,22 +1506,22 @@
       <c r="I24" s="6" t="n">
         <v>48.188</v>
       </c>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L24" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M24" s="7" t="inlineStr">
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1534,43 +1536,43 @@
       <c r="B25" s="5" t="n">
         <v>43678</v>
       </c>
-      <c r="C25" s="8" t="n">
+      <c r="C25" s="9" t="n">
         <v>48.952</v>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="D25" s="10" t="n">
         <v>-0.524</v>
       </c>
-      <c r="E25" s="8" t="n">
+      <c r="E25" s="10" t="n">
         <v>-2.141653</v>
       </c>
-      <c r="F25" s="8" t="n">
+      <c r="F25" s="9" t="n">
         <v>50.317</v>
       </c>
-      <c r="G25" s="8" t="n">
+      <c r="G25" s="9" t="n">
         <v>46.905</v>
       </c>
-      <c r="H25" s="8" t="n">
+      <c r="H25" s="9" t="n">
         <v>51.029</v>
       </c>
-      <c r="I25" s="8" t="n">
+      <c r="I25" s="9" t="n">
         <v>47.677</v>
       </c>
-      <c r="J25" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K25" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L25" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M25" s="9" t="inlineStr">
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K25" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L25" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M25" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1588,10 +1590,10 @@
       <c r="C26" s="6" t="n">
         <v>49.794</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="7" t="n">
         <v>0.842</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E26" s="7" t="n">
         <v>3.63273</v>
       </c>
       <c r="F26" s="6" t="n">
@@ -1606,22 +1608,22 @@
       <c r="I26" s="6" t="n">
         <v>48.248</v>
       </c>
-      <c r="J26" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L26" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M26" s="7" t="inlineStr">
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1636,43 +1638,43 @@
       <c r="B27" s="5" t="n">
         <v>43739</v>
       </c>
-      <c r="C27" s="8" t="n">
+      <c r="C27" s="9" t="n">
         <v>48.495</v>
       </c>
-      <c r="D27" s="8" t="n">
+      <c r="D27" s="10" t="n">
         <v>-1.299</v>
       </c>
-      <c r="E27" s="8" t="n">
+      <c r="E27" s="10" t="n">
         <v>-1.598997</v>
       </c>
-      <c r="F27" s="8" t="n">
+      <c r="F27" s="9" t="n">
         <v>50.226</v>
       </c>
-      <c r="G27" s="8" t="n">
+      <c r="G27" s="9" t="n">
         <v>47.166</v>
       </c>
-      <c r="H27" s="8" t="n">
+      <c r="H27" s="9" t="n">
         <v>51.411</v>
       </c>
-      <c r="I27" s="8" t="n">
+      <c r="I27" s="9" t="n">
         <v>46.48</v>
       </c>
-      <c r="J27" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K27" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L27" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M27" s="9" t="inlineStr">
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K27" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L27" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M27" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1690,10 +1692,10 @@
       <c r="C28" s="6" t="n">
         <v>47.736</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="7" t="n">
         <v>-0.759</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E28" s="7" t="n">
         <v>1.232329</v>
       </c>
       <c r="F28" s="6" t="n">
@@ -1708,22 +1710,22 @@
       <c r="I28" s="6" t="n">
         <v>46.328</v>
       </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L28" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M28" s="7" t="inlineStr">
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1738,43 +1740,43 @@
       <c r="B29" s="5" t="n">
         <v>43800</v>
       </c>
-      <c r="C29" s="8" t="n">
+      <c r="C29" s="9" t="n">
         <v>48.16</v>
       </c>
-      <c r="D29" s="8" t="n">
+      <c r="D29" s="10" t="n">
         <v>0.424</v>
       </c>
-      <c r="E29" s="8" t="n">
+      <c r="E29" s="10" t="n">
         <v>-0.206614</v>
       </c>
-      <c r="F29" s="8" t="n">
+      <c r="F29" s="9" t="n">
         <v>49.079</v>
       </c>
-      <c r="G29" s="8" t="n">
+      <c r="G29" s="9" t="n">
         <v>47.312</v>
       </c>
-      <c r="H29" s="8" t="n">
+      <c r="H29" s="9" t="n">
         <v>51.16</v>
       </c>
-      <c r="I29" s="8" t="n">
+      <c r="I29" s="9" t="n">
         <v>46.377</v>
       </c>
-      <c r="J29" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K29" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L29" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M29" s="9" t="inlineStr">
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K29" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L29" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M29" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1792,10 +1794,10 @@
       <c r="C30" s="6" t="n">
         <v>47.22</v>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="7" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E30" s="7" t="n">
         <v>-4.382062</v>
       </c>
       <c r="F30" s="6" t="n">
@@ -1810,22 +1812,22 @@
       <c r="I30" s="6" t="n">
         <v>44.718</v>
       </c>
-      <c r="J30" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L30" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M30" s="7" t="inlineStr">
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1840,43 +1842,43 @@
       <c r="B31" s="5" t="n">
         <v>43862</v>
       </c>
-      <c r="C31" s="8" t="n">
+      <c r="C31" s="9" t="n">
         <v>48.291</v>
       </c>
-      <c r="D31" s="8" t="n">
+      <c r="D31" s="10" t="n">
         <v>1.071</v>
       </c>
-      <c r="E31" s="8" t="n">
+      <c r="E31" s="10" t="n">
         <v>1.167722</v>
       </c>
-      <c r="F31" s="8" t="n">
+      <c r="F31" s="9" t="n">
         <v>47.757</v>
       </c>
-      <c r="G31" s="8" t="n">
+      <c r="G31" s="9" t="n">
         <v>44.829</v>
       </c>
-      <c r="H31" s="8" t="n">
+      <c r="H31" s="9" t="n">
         <v>51.263</v>
       </c>
-      <c r="I31" s="8" t="n">
+      <c r="I31" s="9" t="n">
         <v>47.721</v>
       </c>
-      <c r="J31" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K31" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L31" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M31" s="9" t="inlineStr">
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K31" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L31" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M31" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1894,10 +1896,10 @@
       <c r="C32" s="6" t="n">
         <v>43.907</v>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="7" t="n">
         <v>-4.384</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E32" s="7" t="n">
         <v>-8.607958</v>
       </c>
       <c r="F32" s="6" t="n">
@@ -1912,22 +1914,22 @@
       <c r="I32" s="6" t="n">
         <v>42.463</v>
       </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L32" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M32" s="7" t="inlineStr">
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M32" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1942,43 +1944,43 @@
       <c r="B33" s="5" t="n">
         <v>43922</v>
       </c>
-      <c r="C33" s="8" t="n">
+      <c r="C33" s="9" t="n">
         <v>35.66</v>
       </c>
-      <c r="D33" s="8" t="n">
+      <c r="D33" s="10" t="n">
         <v>-8.247</v>
       </c>
-      <c r="E33" s="8" t="n">
+      <c r="E33" s="10" t="n">
         <v>-15.658555</v>
       </c>
-      <c r="F33" s="8" t="n">
+      <c r="F33" s="9" t="n">
         <v>36.578</v>
       </c>
-      <c r="G33" s="8" t="n">
+      <c r="G33" s="9" t="n">
         <v>37.197</v>
       </c>
-      <c r="H33" s="8" t="n">
+      <c r="H33" s="9" t="n">
         <v>39.131</v>
       </c>
-      <c r="I33" s="8" t="n">
+      <c r="I33" s="9" t="n">
         <v>33.157</v>
       </c>
-      <c r="J33" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K33" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L33" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M33" s="9" t="inlineStr">
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K33" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L33" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M33" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -1996,10 +1998,10 @@
       <c r="C34" s="6" t="n">
         <v>33.9</v>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="7" t="n">
         <v>-1.76</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="E34" s="7" t="n">
         <v>-1.567765</v>
       </c>
       <c r="F34" s="6" t="n">
@@ -2014,22 +2016,22 @@
       <c r="I34" s="6" t="n">
         <v>31.511</v>
       </c>
-      <c r="J34" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L34" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M34" s="7" t="inlineStr">
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M34" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2044,43 +2046,43 @@
       <c r="B35" s="5" t="n">
         <v>43983</v>
       </c>
-      <c r="C35" s="8" t="n">
+      <c r="C35" s="9" t="n">
         <v>36.409</v>
       </c>
-      <c r="D35" s="8" t="n">
+      <c r="D35" s="10" t="n">
         <v>2.509</v>
       </c>
-      <c r="E35" s="8" t="n">
+      <c r="E35" s="10" t="n">
         <v>6.137927</v>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="F35" s="9" t="n">
         <v>37.29</v>
       </c>
-      <c r="G35" s="8" t="n">
+      <c r="G35" s="9" t="n">
         <v>35.051</v>
       </c>
-      <c r="H35" s="8" t="n">
+      <c r="H35" s="9" t="n">
         <v>38.35</v>
       </c>
-      <c r="I35" s="8" t="n">
+      <c r="I35" s="9" t="n">
         <v>35.287</v>
       </c>
-      <c r="J35" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K35" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L35" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M35" s="9" t="inlineStr">
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K35" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L35" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M35" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2098,10 +2100,10 @@
       <c r="C36" s="6" t="n">
         <v>38.54</v>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="7" t="n">
         <v>2.131</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="E36" s="7" t="n">
         <v>5.755039</v>
       </c>
       <c r="F36" s="6" t="n">
@@ -2116,22 +2118,22 @@
       <c r="I36" s="6" t="n">
         <v>36.719</v>
       </c>
-      <c r="J36" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L36" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M36" s="7" t="inlineStr">
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L36" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M36" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2146,43 +2148,43 @@
       <c r="B37" s="5" t="n">
         <v>44044</v>
       </c>
-      <c r="C37" s="8" t="n">
+      <c r="C37" s="9" t="n">
         <v>37.923</v>
       </c>
-      <c r="D37" s="8" t="n">
+      <c r="D37" s="10" t="n">
         <v>-0.617</v>
       </c>
-      <c r="E37" s="8" t="n">
+      <c r="E37" s="10" t="n">
         <v>-0.426587</v>
       </c>
-      <c r="F37" s="8" t="n">
+      <c r="F37" s="9" t="n">
         <v>38.629</v>
       </c>
-      <c r="G37" s="8" t="n">
+      <c r="G37" s="9" t="n">
         <v>38.464</v>
       </c>
-      <c r="H37" s="8" t="n">
+      <c r="H37" s="9" t="n">
         <v>42.073</v>
       </c>
-      <c r="I37" s="8" t="n">
+      <c r="I37" s="9" t="n">
         <v>35.371</v>
       </c>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K37" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L37" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M37" s="9" t="inlineStr">
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L37" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M37" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2200,10 +2202,10 @@
       <c r="C38" s="6" t="n">
         <v>38.821</v>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="7" t="n">
         <v>0.898</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="E38" s="7" t="n">
         <v>0.493442</v>
       </c>
       <c r="F38" s="6" t="n">
@@ -2218,22 +2220,22 @@
       <c r="I38" s="6" t="n">
         <v>36.025</v>
       </c>
-      <c r="J38" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L38" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M38" s="7" t="inlineStr">
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L38" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M38" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2248,43 +2250,43 @@
       <c r="B39" s="5" t="n">
         <v>44105</v>
       </c>
-      <c r="C39" s="8" t="n">
+      <c r="C39" s="9" t="n">
         <v>40.066</v>
       </c>
-      <c r="D39" s="8" t="n">
+      <c r="D39" s="10" t="n">
         <v>1.245</v>
       </c>
-      <c r="E39" s="8" t="n">
+      <c r="E39" s="10" t="n">
         <v>4.655618</v>
       </c>
-      <c r="F39" s="8" t="n">
+      <c r="F39" s="9" t="n">
         <v>41.767</v>
       </c>
-      <c r="G39" s="8" t="n">
+      <c r="G39" s="9" t="n">
         <v>40.883</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H39" s="9" t="n">
         <v>42.921</v>
       </c>
-      <c r="I39" s="8" t="n">
+      <c r="I39" s="9" t="n">
         <v>37.661</v>
       </c>
-      <c r="J39" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K39" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L39" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M39" s="9" t="inlineStr">
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K39" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L39" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M39" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2302,10 +2304,10 @@
       <c r="C40" s="6" t="n">
         <v>39.902</v>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="7" t="n">
         <v>-0.164</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="E40" s="7" t="n">
         <v>0.970079</v>
       </c>
       <c r="F40" s="6" t="n">
@@ -2320,22 +2322,22 @@
       <c r="I40" s="6" t="n">
         <v>36.695</v>
       </c>
-      <c r="J40" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L40" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M40" s="7" t="inlineStr">
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L40" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M40" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2350,43 +2352,43 @@
       <c r="B41" s="5" t="n">
         <v>44166</v>
       </c>
-      <c r="C41" s="8" t="n">
+      <c r="C41" s="9" t="n">
         <v>41.074</v>
       </c>
-      <c r="D41" s="8" t="n">
+      <c r="D41" s="10" t="n">
         <v>1.172</v>
       </c>
-      <c r="E41" s="8" t="n">
+      <c r="E41" s="10" t="n">
         <v>1.697639</v>
       </c>
-      <c r="F41" s="8" t="n">
+      <c r="F41" s="9" t="n">
         <v>42.998</v>
       </c>
-      <c r="G41" s="8" t="n">
+      <c r="G41" s="9" t="n">
         <v>41.97</v>
       </c>
-      <c r="H41" s="8" t="n">
+      <c r="H41" s="9" t="n">
         <v>44.841</v>
       </c>
-      <c r="I41" s="8" t="n">
+      <c r="I41" s="9" t="n">
         <v>38.086</v>
       </c>
-      <c r="J41" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K41" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L41" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M41" s="9" t="inlineStr">
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K41" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L41" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M41" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2404,10 +2406,10 @@
       <c r="C42" s="6" t="n">
         <v>40.966</v>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="7" t="n">
         <v>-0.108</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="E42" s="7" t="n">
         <v>1.469067</v>
       </c>
       <c r="F42" s="6" t="n">
@@ -2422,22 +2424,22 @@
       <c r="I42" s="6" t="n">
         <v>37.146</v>
       </c>
-      <c r="J42" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L42" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M42" s="7" t="inlineStr">
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L42" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M42" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2452,43 +2454,43 @@
       <c r="B43" s="5" t="n">
         <v>44228</v>
       </c>
-      <c r="C43" s="8" t="n">
+      <c r="C43" s="9" t="n">
         <v>42.167</v>
       </c>
-      <c r="D43" s="8" t="n">
+      <c r="D43" s="10" t="n">
         <v>1.201</v>
       </c>
-      <c r="E43" s="8" t="n">
+      <c r="E43" s="10" t="n">
         <v>0.562936</v>
       </c>
-      <c r="F43" s="8" t="n">
+      <c r="F43" s="9" t="n">
         <v>44.653</v>
       </c>
-      <c r="G43" s="8" t="n">
+      <c r="G43" s="9" t="n">
         <v>43.085</v>
       </c>
-      <c r="H43" s="8" t="n">
+      <c r="H43" s="9" t="n">
         <v>45.675</v>
       </c>
-      <c r="I43" s="8" t="n">
+      <c r="I43" s="9" t="n">
         <v>39.049</v>
       </c>
-      <c r="J43" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K43" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L43" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M43" s="9" t="inlineStr">
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K43" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L43" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M43" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2506,10 +2508,10 @@
       <c r="C44" s="6" t="n">
         <v>45.128</v>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="7" t="n">
         <v>2.961</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="E44" s="7" t="n">
         <v>15.46233</v>
       </c>
       <c r="F44" s="6" t="n">
@@ -2524,22 +2526,22 @@
       <c r="I44" s="6" t="n">
         <v>42.91</v>
       </c>
-      <c r="J44" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L44" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M44" s="7" t="inlineStr">
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K44" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L44" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M44" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2554,43 +2556,43 @@
       <c r="B45" s="5" t="n">
         <v>44287</v>
       </c>
-      <c r="C45" s="8" t="n">
+      <c r="C45" s="9" t="n">
         <v>47.308</v>
       </c>
-      <c r="D45" s="8" t="n">
+      <c r="D45" s="10" t="n">
         <v>2.18</v>
       </c>
-      <c r="E45" s="8" t="n">
+      <c r="E45" s="10" t="n">
         <v>29.883172</v>
       </c>
-      <c r="F45" s="8" t="n">
+      <c r="F45" s="9" t="n">
         <v>48.687</v>
       </c>
-      <c r="G45" s="8" t="n">
+      <c r="G45" s="9" t="n">
         <v>44.61</v>
       </c>
-      <c r="H45" s="8" t="n">
+      <c r="H45" s="9" t="n">
         <v>51.056</v>
       </c>
-      <c r="I45" s="8" t="n">
+      <c r="I45" s="9" t="n">
         <v>45.307</v>
       </c>
-      <c r="J45" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K45" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L45" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M45" s="9" t="inlineStr">
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K45" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L45" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M45" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2608,10 +2610,10 @@
       <c r="C46" s="6" t="n">
         <v>49.07</v>
       </c>
-      <c r="D46" s="6" t="n">
+      <c r="D46" s="7" t="n">
         <v>1.762</v>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="E46" s="7" t="n">
         <v>12.085213</v>
       </c>
       <c r="F46" s="6" t="n">
@@ -2626,22 +2628,22 @@
       <c r="I46" s="6" t="n">
         <v>47.827</v>
       </c>
-      <c r="J46" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L46" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M46" s="7" t="inlineStr">
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M46" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2656,43 +2658,43 @@
       <c r="B47" s="5" t="n">
         <v>44348</v>
       </c>
-      <c r="C47" s="8" t="n">
+      <c r="C47" s="9" t="n">
         <v>51.243</v>
       </c>
-      <c r="D47" s="8" t="n">
+      <c r="D47" s="10" t="n">
         <v>2.173</v>
       </c>
-      <c r="E47" s="8" t="n">
+      <c r="E47" s="10" t="n">
         <v>-4.006589</v>
       </c>
-      <c r="F47" s="8" t="n">
+      <c r="F47" s="9" t="n">
         <v>51.361</v>
       </c>
-      <c r="G47" s="8" t="n">
+      <c r="G47" s="9" t="n">
         <v>47.838</v>
       </c>
-      <c r="H47" s="8" t="n">
+      <c r="H47" s="9" t="n">
         <v>54.196</v>
       </c>
-      <c r="I47" s="8" t="n">
+      <c r="I47" s="9" t="n">
         <v>50.371</v>
       </c>
-      <c r="J47" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K47" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L47" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M47" s="9" t="inlineStr">
+      <c r="J47" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K47" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L47" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M47" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2710,10 +2712,10 @@
       <c r="C48" s="6" t="n">
         <v>51.16</v>
       </c>
-      <c r="D48" s="6" t="n">
+      <c r="D48" s="7" t="n">
         <v>-0.083</v>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="E48" s="7" t="n">
         <v>-7.997474</v>
       </c>
       <c r="F48" s="6" t="n">
@@ -2728,22 +2730,22 @@
       <c r="I48" s="6" t="n">
         <v>49.528</v>
       </c>
-      <c r="J48" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L48" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M48" s="7" t="inlineStr">
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K48" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L48" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M48" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2758,43 +2760,43 @@
       <c r="B49" s="5" t="n">
         <v>44409</v>
       </c>
-      <c r="C49" s="8" t="n">
+      <c r="C49" s="9" t="n">
         <v>49.766</v>
       </c>
-      <c r="D49" s="8" t="n">
+      <c r="D49" s="10" t="n">
         <v>-1.394</v>
       </c>
-      <c r="E49" s="8" t="n">
+      <c r="E49" s="10" t="n">
         <v>-1.51613</v>
       </c>
-      <c r="F49" s="8" t="n">
+      <c r="F49" s="9" t="n">
         <v>50.804</v>
       </c>
-      <c r="G49" s="8" t="n">
+      <c r="G49" s="9" t="n">
         <v>46.393</v>
       </c>
-      <c r="H49" s="8" t="n">
+      <c r="H49" s="9" t="n">
         <v>53.506</v>
       </c>
-      <c r="I49" s="8" t="n">
+      <c r="I49" s="9" t="n">
         <v>48.062</v>
       </c>
-      <c r="J49" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K49" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L49" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M49" s="9" t="inlineStr">
+      <c r="J49" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K49" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L49" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M49" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2812,10 +2814,10 @@
       <c r="C50" s="6" t="n">
         <v>51.195</v>
       </c>
-      <c r="D50" s="6" t="n">
+      <c r="D50" s="7" t="n">
         <v>1.429</v>
       </c>
-      <c r="E50" s="6" t="n">
+      <c r="E50" s="7" t="n">
         <v>0.645431</v>
       </c>
       <c r="F50" s="6" t="n">
@@ -2830,22 +2832,22 @@
       <c r="I50" s="6" t="n">
         <v>49.698</v>
       </c>
-      <c r="J50" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L50" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M50" s="7" t="inlineStr">
+      <c r="J50" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K50" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L50" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M50" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2860,43 +2862,43 @@
       <c r="B51" s="5" t="n">
         <v>44470</v>
       </c>
-      <c r="C51" s="8" t="n">
+      <c r="C51" s="9" t="n">
         <v>52.023</v>
       </c>
-      <c r="D51" s="8" t="n">
+      <c r="D51" s="10" t="n">
         <v>0.828</v>
       </c>
-      <c r="E51" s="8" t="n">
+      <c r="E51" s="10" t="n">
         <v>-2.031242</v>
       </c>
-      <c r="F51" s="8" t="n">
+      <c r="F51" s="9" t="n">
         <v>52.061</v>
       </c>
-      <c r="G51" s="8" t="n">
+      <c r="G51" s="9" t="n">
         <v>48.992</v>
       </c>
-      <c r="H51" s="8" t="n">
+      <c r="H51" s="9" t="n">
         <v>54.825</v>
       </c>
-      <c r="I51" s="8" t="n">
+      <c r="I51" s="9" t="n">
         <v>51.189</v>
       </c>
-      <c r="J51" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K51" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L51" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M51" s="9" t="inlineStr">
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K51" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L51" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M51" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2914,10 +2916,10 @@
       <c r="C52" s="6" t="n">
         <v>53.469</v>
       </c>
-      <c r="D52" s="6" t="n">
+      <c r="D52" s="7" t="n">
         <v>1.446</v>
       </c>
-      <c r="E52" s="6" t="n">
+      <c r="E52" s="7" t="n">
         <v>4.157543</v>
       </c>
       <c r="F52" s="6" t="n">
@@ -2932,22 +2934,22 @@
       <c r="I52" s="6" t="n">
         <v>52.84</v>
       </c>
-      <c r="J52" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L52" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M52" s="7" t="inlineStr">
+      <c r="J52" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K52" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L52" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M52" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -2962,43 +2964,43 @@
       <c r="B53" s="5" t="n">
         <v>44531</v>
       </c>
-      <c r="C53" s="8" t="n">
+      <c r="C53" s="9" t="n">
         <v>54.903</v>
       </c>
-      <c r="D53" s="8" t="n">
+      <c r="D53" s="10" t="n">
         <v>1.434</v>
       </c>
-      <c r="E53" s="8" t="n">
+      <c r="E53" s="10" t="n">
         <v>-0.332301</v>
       </c>
-      <c r="F53" s="8" t="n">
+      <c r="F53" s="9" t="n">
         <v>52.703</v>
       </c>
-      <c r="G53" s="8" t="n">
+      <c r="G53" s="9" t="n">
         <v>50.895</v>
       </c>
-      <c r="H53" s="8" t="n">
+      <c r="H53" s="9" t="n">
         <v>57.434</v>
       </c>
-      <c r="I53" s="8" t="n">
+      <c r="I53" s="9" t="n">
         <v>55.435</v>
       </c>
-      <c r="J53" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K53" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L53" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M53" s="9" t="inlineStr">
+      <c r="J53" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K53" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L53" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M53" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3016,10 +3018,10 @@
       <c r="C54" s="6" t="n">
         <v>51.463</v>
       </c>
-      <c r="D54" s="6" t="n">
+      <c r="D54" s="7" t="n">
         <v>-3.44</v>
       </c>
-      <c r="E54" s="6" t="n">
+      <c r="E54" s="7" t="n">
         <v>-8.044813</v>
       </c>
       <c r="F54" s="6" t="n">
@@ -3034,22 +3036,22 @@
       <c r="I54" s="6" t="n">
         <v>49.546</v>
       </c>
-      <c r="J54" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K54" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L54" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M54" s="7" t="inlineStr">
+      <c r="J54" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K54" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L54" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M54" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3064,43 +3066,43 @@
       <c r="B55" s="5" t="n">
         <v>44593</v>
       </c>
-      <c r="C55" s="8" t="n">
+      <c r="C55" s="9" t="n">
         <v>52.042</v>
       </c>
-      <c r="D55" s="8" t="n">
+      <c r="D55" s="10" t="n">
         <v>0.579</v>
       </c>
-      <c r="E55" s="8" t="n">
+      <c r="E55" s="10" t="n">
         <v>-2.204901</v>
       </c>
-      <c r="F55" s="8" t="n">
+      <c r="F55" s="9" t="n">
         <v>52.914</v>
       </c>
-      <c r="G55" s="8" t="n">
+      <c r="G55" s="9" t="n">
         <v>51.157</v>
       </c>
-      <c r="H55" s="8" t="n">
+      <c r="H55" s="9" t="n">
         <v>54.711</v>
       </c>
-      <c r="I55" s="8" t="n">
+      <c r="I55" s="9" t="n">
         <v>50.459</v>
       </c>
-      <c r="J55" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K55" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L55" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M55" s="9" t="inlineStr">
+      <c r="J55" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K55" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L55" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M55" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3118,10 +3120,10 @@
       <c r="C56" s="6" t="n">
         <v>51.958</v>
       </c>
-      <c r="D56" s="6" t="n">
+      <c r="D56" s="7" t="n">
         <v>-0.08400000000000001</v>
       </c>
-      <c r="E56" s="6" t="n">
+      <c r="E56" s="7" t="n">
         <v>-8.284058999999999</v>
       </c>
       <c r="F56" s="6" t="n">
@@ -3136,22 +3138,22 @@
       <c r="I56" s="6" t="n">
         <v>51.032</v>
       </c>
-      <c r="J56" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K56" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L56" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M56" s="7" t="inlineStr">
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K56" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L56" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M56" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3166,43 +3168,43 @@
       <c r="B57" s="5" t="n">
         <v>44652</v>
       </c>
-      <c r="C57" s="8" t="n">
+      <c r="C57" s="9" t="n">
         <v>53.543</v>
       </c>
-      <c r="D57" s="8" t="n">
+      <c r="D57" s="10" t="n">
         <v>1.585</v>
       </c>
-      <c r="E57" s="8" t="n">
+      <c r="E57" s="10" t="n">
         <v>-1.955139</v>
       </c>
-      <c r="F57" s="8" t="n">
+      <c r="F57" s="9" t="n">
         <v>52.608</v>
       </c>
-      <c r="G57" s="8" t="n">
+      <c r="G57" s="9" t="n">
         <v>51.088</v>
       </c>
-      <c r="H57" s="8" t="n">
+      <c r="H57" s="9" t="n">
         <v>55.453</v>
       </c>
-      <c r="I57" s="8" t="n">
+      <c r="I57" s="9" t="n">
         <v>53.496</v>
       </c>
-      <c r="J57" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K57" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L57" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M57" s="9" t="inlineStr">
+      <c r="J57" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K57" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L57" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M57" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3220,10 +3222,10 @@
       <c r="C58" s="6" t="n">
         <v>52.941</v>
       </c>
-      <c r="D58" s="6" t="n">
+      <c r="D58" s="7" t="n">
         <v>-0.602</v>
       </c>
-      <c r="E58" s="6" t="n">
+      <c r="E58" s="7" t="n">
         <v>-5.290859</v>
       </c>
       <c r="F58" s="6" t="n">
@@ -3238,22 +3240,22 @@
       <c r="I58" s="6" t="n">
         <v>52.901</v>
       </c>
-      <c r="J58" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K58" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L58" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M58" s="7" t="inlineStr">
+      <c r="J58" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K58" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L58" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M58" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3268,43 +3270,43 @@
       <c r="B59" s="5" t="n">
         <v>44713</v>
       </c>
-      <c r="C59" s="8" t="n">
+      <c r="C59" s="9" t="n">
         <v>51.509</v>
       </c>
-      <c r="D59" s="8" t="n">
+      <c r="D59" s="10" t="n">
         <v>-1.432</v>
       </c>
-      <c r="E59" s="8" t="n">
+      <c r="E59" s="10" t="n">
         <v>-7.369635</v>
       </c>
-      <c r="F59" s="8" t="n">
+      <c r="F59" s="9" t="n">
         <v>52.168</v>
       </c>
-      <c r="G59" s="8" t="n">
+      <c r="G59" s="9" t="n">
         <v>51.099</v>
       </c>
-      <c r="H59" s="8" t="n">
+      <c r="H59" s="9" t="n">
         <v>55.841</v>
       </c>
-      <c r="I59" s="8" t="n">
+      <c r="I59" s="9" t="n">
         <v>49.078</v>
       </c>
-      <c r="J59" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K59" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L59" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M59" s="9" t="inlineStr">
+      <c r="J59" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K59" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L59" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M59" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3322,10 +3324,10 @@
       <c r="C60" s="6" t="n">
         <v>50.453</v>
       </c>
-      <c r="D60" s="6" t="n">
+      <c r="D60" s="7" t="n">
         <v>-1.056</v>
       </c>
-      <c r="E60" s="6" t="n">
+      <c r="E60" s="7" t="n">
         <v>-1.901034</v>
       </c>
       <c r="F60" s="6" t="n">
@@ -3340,22 +3342,22 @@
       <c r="I60" s="6" t="n">
         <v>47.815</v>
       </c>
-      <c r="J60" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K60" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L60" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M60" s="7" t="inlineStr">
+      <c r="J60" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K60" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L60" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M60" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3370,43 +3372,43 @@
       <c r="B61" s="5" t="n">
         <v>44774</v>
       </c>
-      <c r="C61" s="8" t="n">
+      <c r="C61" s="9" t="n">
         <v>48.452</v>
       </c>
-      <c r="D61" s="8" t="n">
+      <c r="D61" s="10" t="n">
         <v>-2.001</v>
       </c>
-      <c r="E61" s="8" t="n">
+      <c r="E61" s="10" t="n">
         <v>-1.258418</v>
       </c>
-      <c r="F61" s="8" t="n">
+      <c r="F61" s="9" t="n">
         <v>51.297</v>
       </c>
-      <c r="G61" s="8" t="n">
+      <c r="G61" s="9" t="n">
         <v>48.541</v>
       </c>
-      <c r="H61" s="8" t="n">
+      <c r="H61" s="9" t="n">
         <v>53.822</v>
       </c>
-      <c r="I61" s="8" t="n">
+      <c r="I61" s="9" t="n">
         <v>44.386</v>
       </c>
-      <c r="J61" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K61" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L61" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M61" s="9" t="inlineStr">
+      <c r="J61" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K61" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L61" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M61" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3424,10 +3426,10 @@
       <c r="C62" s="6" t="n">
         <v>47.964</v>
       </c>
-      <c r="D62" s="6" t="n">
+      <c r="D62" s="7" t="n">
         <v>-0.488</v>
       </c>
-      <c r="E62" s="6" t="n">
+      <c r="E62" s="7" t="n">
         <v>-3.670806</v>
       </c>
       <c r="F62" s="6" t="n">
@@ -3442,22 +3444,22 @@
       <c r="I62" s="6" t="n">
         <v>43.105</v>
       </c>
-      <c r="J62" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K62" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L62" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M62" s="7" t="inlineStr">
+      <c r="J62" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K62" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L62" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M62" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3472,43 +3474,43 @@
       <c r="B63" s="5" t="n">
         <v>44835</v>
       </c>
-      <c r="C63" s="8" t="n">
+      <c r="C63" s="9" t="n">
         <v>49.848</v>
       </c>
-      <c r="D63" s="8" t="n">
+      <c r="D63" s="10" t="n">
         <v>1.884</v>
       </c>
-      <c r="E63" s="8" t="n">
+      <c r="E63" s="10" t="n">
         <v>2.13032</v>
       </c>
-      <c r="F63" s="8" t="n">
+      <c r="F63" s="9" t="n">
         <v>50.728</v>
       </c>
-      <c r="G63" s="8" t="n">
+      <c r="G63" s="9" t="n">
         <v>51.357</v>
       </c>
-      <c r="H63" s="8" t="n">
+      <c r="H63" s="9" t="n">
         <v>52.789</v>
       </c>
-      <c r="I63" s="8" t="n">
+      <c r="I63" s="9" t="n">
         <v>47.638</v>
       </c>
-      <c r="J63" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K63" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L63" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M63" s="9" t="inlineStr">
+      <c r="J63" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K63" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L63" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M63" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3526,10 +3528,10 @@
       <c r="C64" s="6" t="n">
         <v>49.603</v>
       </c>
-      <c r="D64" s="6" t="n">
+      <c r="D64" s="7" t="n">
         <v>-0.245</v>
       </c>
-      <c r="E64" s="6" t="n">
+      <c r="E64" s="7" t="n">
         <v>-3.049515</v>
       </c>
       <c r="F64" s="6" t="n">
@@ -3544,22 +3546,22 @@
       <c r="I64" s="6" t="n">
         <v>47.585</v>
       </c>
-      <c r="J64" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K64" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L64" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M64" s="7" t="inlineStr">
+      <c r="J64" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K64" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L64" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M64" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3574,43 +3576,43 @@
       <c r="B65" s="5" t="n">
         <v>44896</v>
       </c>
-      <c r="C65" s="8" t="n">
+      <c r="C65" s="9" t="n">
         <v>47.402</v>
       </c>
-      <c r="D65" s="8" t="n">
+      <c r="D65" s="10" t="n">
         <v>-2.201</v>
       </c>
-      <c r="E65" s="8" t="n">
+      <c r="E65" s="10" t="n">
         <v>-6.431919</v>
       </c>
-      <c r="F65" s="8" t="n">
+      <c r="F65" s="9" t="n">
         <v>50.36</v>
       </c>
-      <c r="G65" s="8" t="n">
+      <c r="G65" s="9" t="n">
         <v>48.227</v>
       </c>
-      <c r="H65" s="8" t="n">
+      <c r="H65" s="9" t="n">
         <v>52.498</v>
       </c>
-      <c r="I65" s="8" t="n">
+      <c r="I65" s="9" t="n">
         <v>43.275</v>
       </c>
-      <c r="J65" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K65" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L65" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M65" s="9" t="inlineStr">
+      <c r="J65" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K65" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L65" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M65" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3628,10 +3630,10 @@
       <c r="C66" s="6" t="n">
         <v>48.55</v>
       </c>
-      <c r="D66" s="6" t="n">
+      <c r="D66" s="7" t="n">
         <v>1.148</v>
       </c>
-      <c r="E66" s="6" t="n">
+      <c r="E66" s="7" t="n">
         <v>8.001899999999999</v>
       </c>
       <c r="F66" s="6" t="n">
@@ -3646,22 +3648,22 @@
       <c r="I66" s="6" t="n">
         <v>43.894</v>
       </c>
-      <c r="J66" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K66" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L66" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M66" s="7" t="inlineStr">
+      <c r="J66" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K66" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L66" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M66" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3676,43 +3678,43 @@
       <c r="B67" s="5" t="n">
         <v>44958</v>
       </c>
-      <c r="C67" s="8" t="n">
+      <c r="C67" s="9" t="n">
         <v>51.775</v>
       </c>
-      <c r="D67" s="8" t="n">
+      <c r="D67" s="10" t="n">
         <v>3.225</v>
       </c>
-      <c r="E67" s="8" t="n">
+      <c r="E67" s="10" t="n">
         <v>5.14733</v>
       </c>
-      <c r="F67" s="8" t="n">
+      <c r="F67" s="9" t="n">
         <v>53.506</v>
       </c>
-      <c r="G67" s="8" t="n">
+      <c r="G67" s="9" t="n">
         <v>52.528</v>
       </c>
-      <c r="H67" s="8" t="n">
+      <c r="H67" s="9" t="n">
         <v>54.346</v>
       </c>
-      <c r="I67" s="8" t="n">
+      <c r="I67" s="9" t="n">
         <v>49.515</v>
       </c>
-      <c r="J67" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K67" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L67" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M67" s="9" t="inlineStr">
+      <c r="J67" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K67" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L67" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M67" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3730,10 +3732,10 @@
       <c r="C68" s="6" t="n">
         <v>53.611</v>
       </c>
-      <c r="D68" s="6" t="n">
+      <c r="D68" s="7" t="n">
         <v>1.836</v>
       </c>
-      <c r="E68" s="6" t="n">
+      <c r="E68" s="7" t="n">
         <v>3.694463</v>
       </c>
       <c r="F68" s="6" t="n">
@@ -3748,22 +3750,22 @@
       <c r="I68" s="6" t="n">
         <v>54.174</v>
       </c>
-      <c r="J68" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K68" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L68" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M68" s="7" t="inlineStr">
+      <c r="J68" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K68" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L68" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M68" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3778,43 +3780,43 @@
       <c r="B69" s="5" t="n">
         <v>45017</v>
       </c>
-      <c r="C69" s="8" t="n">
+      <c r="C69" s="9" t="n">
         <v>54.776</v>
       </c>
-      <c r="D69" s="8" t="n">
+      <c r="D69" s="10" t="n">
         <v>1.165</v>
       </c>
-      <c r="E69" s="8" t="n">
+      <c r="E69" s="10" t="n">
         <v>-0.878594</v>
       </c>
-      <c r="F69" s="8" t="n">
+      <c r="F69" s="9" t="n">
         <v>53.44</v>
       </c>
-      <c r="G69" s="8" t="n">
+      <c r="G69" s="9" t="n">
         <v>54.818</v>
       </c>
-      <c r="H69" s="8" t="n">
+      <c r="H69" s="9" t="n">
         <v>55.548</v>
       </c>
-      <c r="I69" s="8" t="n">
+      <c r="I69" s="9" t="n">
         <v>54.989</v>
       </c>
-      <c r="J69" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K69" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L69" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M69" s="9" t="inlineStr">
+      <c r="J69" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K69" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L69" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M69" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3832,10 +3834,10 @@
       <c r="C70" s="6" t="n">
         <v>55.68</v>
       </c>
-      <c r="D70" s="6" t="n">
+      <c r="D70" s="7" t="n">
         <v>0.904</v>
       </c>
-      <c r="E70" s="6" t="n">
+      <c r="E70" s="7" t="n">
         <v>2.870862</v>
       </c>
       <c r="F70" s="6" t="n">
@@ -3850,22 +3852,22 @@
       <c r="I70" s="6" t="n">
         <v>56.923</v>
       </c>
-      <c r="J70" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K70" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L70" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M70" s="7" t="inlineStr">
+      <c r="J70" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K70" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L70" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M70" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3880,43 +3882,43 @@
       <c r="B71" s="5" t="n">
         <v>45078</v>
       </c>
-      <c r="C71" s="8" t="n">
+      <c r="C71" s="9" t="n">
         <v>54.955</v>
       </c>
-      <c r="D71" s="8" t="n">
+      <c r="D71" s="10" t="n">
         <v>-0.725</v>
       </c>
-      <c r="E71" s="8" t="n">
+      <c r="E71" s="10" t="n">
         <v>1.516409</v>
       </c>
-      <c r="F71" s="8" t="n">
+      <c r="F71" s="9" t="n">
         <v>53.599</v>
       </c>
-      <c r="G71" s="8" t="n">
+      <c r="G71" s="9" t="n">
         <v>52.418</v>
       </c>
-      <c r="H71" s="8" t="n">
+      <c r="H71" s="9" t="n">
         <v>56.453</v>
       </c>
-      <c r="I71" s="8" t="n">
+      <c r="I71" s="9" t="n">
         <v>55.327</v>
       </c>
-      <c r="J71" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K71" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L71" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M71" s="9" t="inlineStr">
+      <c r="J71" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K71" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L71" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M71" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3934,10 +3936,10 @@
       <c r="C72" s="6" t="n">
         <v>56.536</v>
       </c>
-      <c r="D72" s="6" t="n">
+      <c r="D72" s="7" t="n">
         <v>1.581</v>
       </c>
-      <c r="E72" s="6" t="n">
+      <c r="E72" s="7" t="n">
         <v>5.366673</v>
       </c>
       <c r="F72" s="6" t="n">
@@ -3952,22 +3954,22 @@
       <c r="I72" s="6" t="n">
         <v>58.635</v>
       </c>
-      <c r="J72" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K72" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L72" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M72" s="7" t="inlineStr">
+      <c r="J72" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K72" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L72" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M72" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -3982,43 +3984,43 @@
       <c r="B73" s="5" t="n">
         <v>45139</v>
       </c>
-      <c r="C73" s="8" t="n">
+      <c r="C73" s="9" t="n">
         <v>56.436</v>
       </c>
-      <c r="D73" s="8" t="n">
+      <c r="D73" s="10" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E73" s="8" t="n">
+      <c r="E73" s="10" t="n">
         <v>4.421398</v>
       </c>
-      <c r="F73" s="8" t="n">
+      <c r="F73" s="9" t="n">
         <v>53.275</v>
       </c>
-      <c r="G73" s="8" t="n">
+      <c r="G73" s="9" t="n">
         <v>52.503</v>
       </c>
-      <c r="H73" s="8" t="n">
+      <c r="H73" s="9" t="n">
         <v>56.542</v>
       </c>
-      <c r="I73" s="8" t="n">
+      <c r="I73" s="9" t="n">
         <v>58.631</v>
       </c>
-      <c r="J73" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K73" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L73" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M73" s="9" t="inlineStr">
+      <c r="J73" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K73" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L73" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M73" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4036,10 +4038,10 @@
       <c r="C74" s="6" t="n">
         <v>56.361</v>
       </c>
-      <c r="D74" s="6" t="n">
+      <c r="D74" s="7" t="n">
         <v>-0.075</v>
       </c>
-      <c r="E74" s="6" t="n">
+      <c r="E74" s="7" t="n">
         <v>1.028716</v>
       </c>
       <c r="F74" s="6" t="n">
@@ -4054,22 +4056,22 @@
       <c r="I74" s="6" t="n">
         <v>58.618</v>
       </c>
-      <c r="J74" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K74" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L74" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M74" s="7" t="inlineStr">
+      <c r="J74" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K74" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L74" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M74" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4084,43 +4086,43 @@
       <c r="B75" s="5" t="n">
         <v>45200</v>
       </c>
-      <c r="C75" s="8" t="n">
+      <c r="C75" s="9" t="n">
         <v>55.449</v>
       </c>
-      <c r="D75" s="8" t="n">
+      <c r="D75" s="10" t="n">
         <v>-0.912</v>
       </c>
-      <c r="E75" s="8" t="n">
+      <c r="E75" s="10" t="n">
         <v>-6.270722</v>
       </c>
-      <c r="F75" s="8" t="n">
+      <c r="F75" s="9" t="n">
         <v>53.919</v>
       </c>
-      <c r="G75" s="8" t="n">
+      <c r="G75" s="9" t="n">
         <v>52.305</v>
       </c>
-      <c r="H75" s="8" t="n">
+      <c r="H75" s="9" t="n">
         <v>55.171</v>
       </c>
-      <c r="I75" s="8" t="n">
+      <c r="I75" s="9" t="n">
         <v>56.93</v>
       </c>
-      <c r="J75" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K75" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L75" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M75" s="9" t="inlineStr">
+      <c r="J75" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K75" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L75" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M75" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4138,10 +4140,10 @@
       <c r="C76" s="6" t="n">
         <v>56.048</v>
       </c>
-      <c r="D76" s="6" t="n">
+      <c r="D76" s="7" t="n">
         <v>0.599</v>
       </c>
-      <c r="E76" s="6" t="n">
+      <c r="E76" s="7" t="n">
         <v>1.757008</v>
       </c>
       <c r="F76" s="6" t="n">
@@ -4156,22 +4158,22 @@
       <c r="I76" s="6" t="n">
         <v>57.838</v>
       </c>
-      <c r="J76" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K76" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L76" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M76" s="7" t="inlineStr">
+      <c r="J76" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K76" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L76" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M76" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4186,43 +4188,43 @@
       <c r="B77" s="5" t="n">
         <v>45261</v>
       </c>
-      <c r="C77" s="8" t="n">
+      <c r="C77" s="9" t="n">
         <v>56.168</v>
       </c>
-      <c r="D77" s="8" t="n">
+      <c r="D77" s="10" t="n">
         <v>0.12</v>
       </c>
-      <c r="E77" s="8" t="n">
+      <c r="E77" s="10" t="n">
         <v>5.499725</v>
       </c>
-      <c r="F77" s="8" t="n">
+      <c r="F77" s="9" t="n">
         <v>54.197</v>
       </c>
-      <c r="G77" s="8" t="n">
+      <c r="G77" s="9" t="n">
         <v>51.267</v>
       </c>
-      <c r="H77" s="8" t="n">
+      <c r="H77" s="9" t="n">
         <v>56.346</v>
       </c>
-      <c r="I77" s="8" t="n">
+      <c r="I77" s="9" t="n">
         <v>57.973</v>
       </c>
-      <c r="J77" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K77" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L77" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M77" s="9" t="inlineStr">
+      <c r="J77" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K77" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L77" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M77" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4240,10 +4242,10 @@
       <c r="C78" s="6" t="n">
         <v>55.971</v>
       </c>
-      <c r="D78" s="6" t="n">
+      <c r="D78" s="7" t="n">
         <v>-0.197</v>
       </c>
-      <c r="E78" s="6" t="n">
+      <c r="E78" s="7" t="n">
         <v>-3.207618</v>
       </c>
       <c r="F78" s="6" t="n">
@@ -4258,22 +4260,22 @@
       <c r="I78" s="6" t="n">
         <v>58.339</v>
       </c>
-      <c r="J78" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K78" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L78" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M78" s="7" t="inlineStr">
+      <c r="J78" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K78" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L78" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M78" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4288,43 +4290,43 @@
       <c r="B79" s="5" t="n">
         <v>45323</v>
       </c>
-      <c r="C79" s="8" t="n">
+      <c r="C79" s="9" t="n">
         <v>54.975</v>
       </c>
-      <c r="D79" s="8" t="n">
+      <c r="D79" s="10" t="n">
         <v>-0.996</v>
       </c>
-      <c r="E79" s="8" t="n">
+      <c r="E79" s="10" t="n">
         <v>-9.104684000000001</v>
       </c>
-      <c r="F79" s="8" t="n">
+      <c r="F79" s="9" t="n">
         <v>54.517</v>
       </c>
-      <c r="G79" s="8" t="n">
+      <c r="G79" s="9" t="n">
         <v>49.958</v>
       </c>
-      <c r="H79" s="8" t="n">
+      <c r="H79" s="9" t="n">
         <v>53.966</v>
       </c>
-      <c r="I79" s="8" t="n">
+      <c r="I79" s="9" t="n">
         <v>56.714</v>
       </c>
-      <c r="J79" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K79" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L79" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M79" s="9" t="inlineStr">
+      <c r="J79" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K79" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L79" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M79" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4342,10 +4344,10 @@
       <c r="C80" s="6" t="n">
         <v>54.757</v>
       </c>
-      <c r="D80" s="6" t="n">
+      <c r="D80" s="7" t="n">
         <v>-0.218</v>
       </c>
-      <c r="E80" s="6" t="n">
+      <c r="E80" s="7" t="n">
         <v>-4.042968</v>
       </c>
       <c r="F80" s="6" t="n">
@@ -4360,22 +4362,22 @@
       <c r="I80" s="6" t="n">
         <v>55.71</v>
       </c>
-      <c r="J80" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K80" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L80" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M80" s="7" t="inlineStr">
+      <c r="J80" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K80" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L80" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M80" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4390,43 +4392,43 @@
       <c r="B81" s="5" t="n">
         <v>45383</v>
       </c>
-      <c r="C81" s="8" t="n">
+      <c r="C81" s="9" t="n">
         <v>54.957</v>
       </c>
-      <c r="D81" s="8" t="n">
+      <c r="D81" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="E81" s="8" t="n">
+      <c r="E81" s="10" t="n">
         <v>-1.807184</v>
       </c>
-      <c r="F81" s="8" t="n">
+      <c r="F81" s="9" t="n">
         <v>54.542</v>
       </c>
-      <c r="G81" s="8" t="n">
+      <c r="G81" s="9" t="n">
         <v>52.821</v>
       </c>
-      <c r="H81" s="8" t="n">
+      <c r="H81" s="9" t="n">
         <v>54.206</v>
       </c>
-      <c r="I81" s="8" t="n">
+      <c r="I81" s="9" t="n">
         <v>55.962</v>
       </c>
-      <c r="J81" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K81" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L81" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M81" s="9" t="inlineStr">
+      <c r="J81" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K81" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L81" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M81" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4444,10 +4446,10 @@
       <c r="C82" s="6" t="n">
         <v>54.636886</v>
       </c>
-      <c r="D82" s="6" t="n">
+      <c r="D82" s="7" t="n">
         <v>-0.320114</v>
       </c>
-      <c r="E82" s="6" t="n">
+      <c r="E82" s="7" t="n">
         <v>-2.203846</v>
       </c>
       <c r="F82" s="6" t="n">
@@ -4462,22 +4464,22 @@
       <c r="I82" s="6" t="n">
         <v>56.239812</v>
       </c>
-      <c r="J82" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K82" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L82" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M82" s="7" t="inlineStr">
+      <c r="J82" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K82" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L82" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M82" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4492,43 +4494,43 @@
       <c r="B83" s="5" t="n">
         <v>45444</v>
       </c>
-      <c r="C83" s="8" t="n">
+      <c r="C83" s="9" t="n">
         <v>53.149893</v>
       </c>
-      <c r="D83" s="8" t="n">
+      <c r="D83" s="10" t="n">
         <v>-1.486992</v>
       </c>
-      <c r="E83" s="8" t="n">
+      <c r="E83" s="10" t="n">
         <v>-1.41129</v>
       </c>
-      <c r="F83" s="8" t="n">
+      <c r="F83" s="9" t="n">
         <v>53.132812</v>
       </c>
-      <c r="G83" s="8" t="n">
+      <c r="G83" s="9" t="n">
         <v>50.317052</v>
       </c>
-      <c r="H83" s="8" t="n">
+      <c r="H83" s="9" t="n">
         <v>53.449466</v>
       </c>
-      <c r="I83" s="8" t="n">
+      <c r="I83" s="9" t="n">
         <v>53.576937</v>
       </c>
-      <c r="J83" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K83" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L83" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M83" s="9" t="inlineStr">
+      <c r="J83" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K83" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L83" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M83" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4546,10 +4548,10 @@
       <c r="C84" s="6" t="n">
         <v>53.492096</v>
       </c>
-      <c r="D84" s="6" t="n">
+      <c r="D84" s="7" t="n">
         <v>0.342203</v>
       </c>
-      <c r="E84" s="6" t="n">
+      <c r="E84" s="7" t="n">
         <v>-2.099311</v>
       </c>
       <c r="F84" s="6" t="n">
@@ -4564,22 +4566,22 @@
       <c r="I84" s="6" t="n">
         <v>54.510294</v>
       </c>
-      <c r="J84" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K84" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L84" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M84" s="7" t="inlineStr">
+      <c r="J84" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K84" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L84" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M84" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4594,43 +4596,43 @@
       <c r="B85" s="5" t="n">
         <v>45505</v>
       </c>
-      <c r="C85" s="8" t="n">
+      <c r="C85" s="9" t="n">
         <v>52.740526</v>
       </c>
-      <c r="D85" s="8" t="n">
+      <c r="D85" s="10" t="n">
         <v>-0.75157</v>
       </c>
-      <c r="E85" s="8" t="n">
+      <c r="E85" s="10" t="n">
         <v>-1.16407</v>
       </c>
-      <c r="F85" s="8" t="n">
+      <c r="F85" s="9" t="n">
         <v>52.885945</v>
       </c>
-      <c r="G85" s="8" t="n">
+      <c r="G85" s="9" t="n">
         <v>51.122903</v>
       </c>
-      <c r="H85" s="8" t="n">
+      <c r="H85" s="9" t="n">
         <v>52.604894</v>
       </c>
-      <c r="I85" s="8" t="n">
+      <c r="I85" s="9" t="n">
         <v>53.06938</v>
       </c>
-      <c r="J85" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K85" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L85" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M85" s="9" t="inlineStr">
+      <c r="J85" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K85" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L85" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M85" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4648,10 +4650,10 @@
       <c r="C86" s="6" t="n">
         <v>50.985505</v>
       </c>
-      <c r="D86" s="6" t="n">
+      <c r="D86" s="7" t="n">
         <v>-1.755021</v>
       </c>
-      <c r="E86" s="6" t="n">
+      <c r="E86" s="7" t="n">
         <v>-2.989536</v>
       </c>
       <c r="F86" s="6" t="n">
@@ -4666,22 +4668,22 @@
       <c r="I86" s="6" t="n">
         <v>51.06508</v>
       </c>
-      <c r="J86" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K86" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L86" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M86" s="7" t="inlineStr">
+      <c r="J86" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K86" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L86" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M86" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4696,43 +4698,43 @@
       <c r="B87" s="5" t="n">
         <v>45566</v>
       </c>
-      <c r="C87" s="8" t="n">
+      <c r="C87" s="9" t="n">
         <v>51.906183</v>
       </c>
-      <c r="D87" s="8" t="n">
+      <c r="D87" s="10" t="n">
         <v>0.920679</v>
       </c>
-      <c r="E87" s="8" t="n">
+      <c r="E87" s="10" t="n">
         <v>3.14829</v>
       </c>
-      <c r="F87" s="8" t="n">
+      <c r="F87" s="9" t="n">
         <v>51.978727</v>
       </c>
-      <c r="G87" s="8" t="n">
+      <c r="G87" s="9" t="n">
         <v>48.998174</v>
       </c>
-      <c r="H87" s="8" t="n">
+      <c r="H87" s="9" t="n">
         <v>52.32137</v>
       </c>
-      <c r="I87" s="8" t="n">
+      <c r="I87" s="9" t="n">
         <v>52.248185</v>
       </c>
-      <c r="J87" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K87" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L87" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M87" s="9" t="inlineStr">
+      <c r="J87" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K87" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L87" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M87" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4750,10 +4752,10 @@
       <c r="C88" s="6" t="n">
         <v>51.484636</v>
       </c>
-      <c r="D88" s="6" t="n">
+      <c r="D88" s="7" t="n">
         <v>-0.421547</v>
       </c>
-      <c r="E88" s="6" t="n">
+      <c r="E88" s="7" t="n">
         <v>-1.75256</v>
       </c>
       <c r="F88" s="6" t="n">
@@ -4768,22 +4770,22 @@
       <c r="I88" s="6" t="n">
         <v>51.688565</v>
       </c>
-      <c r="J88" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K88" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L88" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M88" s="7" t="inlineStr">
+      <c r="J88" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K88" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L88" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M88" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4798,43 +4800,43 @@
       <c r="B89" s="5" t="n">
         <v>45627</v>
       </c>
-      <c r="C89" s="8" t="n">
+      <c r="C89" s="9" t="n">
         <v>51.89662</v>
       </c>
-      <c r="D89" s="8" t="n">
+      <c r="D89" s="10" t="n">
         <v>0.411983</v>
       </c>
-      <c r="E89" s="8" t="n">
+      <c r="E89" s="10" t="n">
         <v>0.537234</v>
       </c>
-      <c r="F89" s="8" t="n">
+      <c r="F89" s="9" t="n">
         <v>50.91615</v>
       </c>
-      <c r="G89" s="8" t="n">
+      <c r="G89" s="9" t="n">
         <v>48.748217</v>
       </c>
-      <c r="H89" s="8" t="n">
+      <c r="H89" s="9" t="n">
         <v>52.017722</v>
       </c>
-      <c r="I89" s="8" t="n">
+      <c r="I89" s="9" t="n">
         <v>52.92183</v>
       </c>
-      <c r="J89" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K89" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L89" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M89" s="9" t="inlineStr">
+      <c r="J89" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K89" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L89" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M89" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4852,10 +4854,10 @@
       <c r="C90" s="6" t="n">
         <v>51.374907</v>
       </c>
-      <c r="D90" s="6" t="n">
+      <c r="D90" s="7" t="n">
         <v>-0.521713</v>
       </c>
-      <c r="E90" s="6" t="n">
+      <c r="E90" s="7" t="n">
         <v>-0.606911</v>
       </c>
       <c r="F90" s="6" t="n">
@@ -4870,22 +4872,22 @@
       <c r="I90" s="6" t="n">
         <v>51.487236</v>
       </c>
-      <c r="J90" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K90" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L90" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M90" s="7" t="inlineStr">
+      <c r="J90" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K90" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L90" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M90" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4900,43 +4902,43 @@
       <c r="B91" s="5" t="n">
         <v>45689</v>
       </c>
-      <c r="C91" s="8" t="n">
+      <c r="C91" s="9" t="n">
         <v>50.117443</v>
       </c>
-      <c r="D91" s="8" t="n">
+      <c r="D91" s="10" t="n">
         <v>-1.257464</v>
       </c>
-      <c r="E91" s="8" t="n">
+      <c r="E91" s="10" t="n">
         <v>-0.624376</v>
       </c>
-      <c r="F91" s="8" t="n">
+      <c r="F91" s="9" t="n">
         <v>50.547437</v>
       </c>
-      <c r="G91" s="8" t="n">
+      <c r="G91" s="9" t="n">
         <v>46.76653</v>
       </c>
-      <c r="H91" s="8" t="n">
+      <c r="H91" s="9" t="n">
         <v>50.564832</v>
       </c>
-      <c r="I91" s="8" t="n">
+      <c r="I91" s="9" t="n">
         <v>50.36792</v>
       </c>
-      <c r="J91" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K91" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L91" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M91" s="9" t="inlineStr">
+      <c r="J91" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K91" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L91" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M91" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -4954,10 +4956,10 @@
       <c r="C92" s="6" t="n">
         <v>49.337817</v>
       </c>
-      <c r="D92" s="6" t="n">
+      <c r="D92" s="7" t="n">
         <v>-0.779626</v>
       </c>
-      <c r="E92" s="6" t="n">
+      <c r="E92" s="7" t="n">
         <v>-1.060847</v>
       </c>
       <c r="F92" s="6" t="n">
@@ -4972,22 +4974,22 @@
       <c r="I92" s="6" t="n">
         <v>49.517803</v>
       </c>
-      <c r="J92" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K92" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L92" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M92" s="7" t="inlineStr">
+      <c r="J92" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K92" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L92" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M92" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -5002,43 +5004,43 @@
       <c r="B93" s="5" t="n">
         <v>45748</v>
       </c>
-      <c r="C93" s="8" t="n">
+      <c r="C93" s="9" t="n">
         <v>48.689455</v>
       </c>
-      <c r="D93" s="8" t="n">
+      <c r="D93" s="10" t="n">
         <v>-0.648362</v>
       </c>
-      <c r="E93" s="8" t="n">
+      <c r="E93" s="10" t="n">
         <v>-1.507667</v>
       </c>
-      <c r="F93" s="8" t="n">
+      <c r="F93" s="9" t="n">
         <v>48.690879</v>
       </c>
-      <c r="G93" s="8" t="n">
+      <c r="G93" s="9" t="n">
         <v>46.683058</v>
       </c>
-      <c r="H93" s="8" t="n">
+      <c r="H93" s="9" t="n">
         <v>47.264022</v>
       </c>
-      <c r="I93" s="8" t="n">
+      <c r="I93" s="9" t="n">
         <v>49.820923</v>
       </c>
-      <c r="J93" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K93" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L93" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M93" s="9" t="inlineStr">
+      <c r="J93" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K93" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L93" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M93" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -5056,10 +5058,10 @@
       <c r="C94" s="6" t="n">
         <v>48.722203</v>
       </c>
-      <c r="D94" s="6" t="n">
+      <c r="D94" s="7" t="n">
         <v>0.032747</v>
       </c>
-      <c r="E94" s="6" t="n">
+      <c r="E94" s="7" t="n">
         <v>0.579012</v>
       </c>
       <c r="F94" s="6" t="n">
@@ -5074,22 +5076,22 @@
       <c r="I94" s="6" t="n">
         <v>49.687044</v>
       </c>
-      <c r="J94" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K94" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L94" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M94" s="7" t="inlineStr">
+      <c r="J94" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K94" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L94" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M94" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -5104,43 +5106,43 @@
       <c r="B95" s="5" t="n">
         <v>45809</v>
       </c>
-      <c r="C95" s="8" t="n">
+      <c r="C95" s="9" t="n">
         <v>48.623622</v>
       </c>
-      <c r="D95" s="8" t="n">
+      <c r="D95" s="10" t="n">
         <v>-0.098581</v>
       </c>
-      <c r="E95" s="8" t="n">
+      <c r="E95" s="10" t="n">
         <v>2.30939</v>
       </c>
-      <c r="F95" s="8" t="n">
+      <c r="F95" s="9" t="n">
         <v>49.228847</v>
       </c>
-      <c r="G95" s="8" t="n">
+      <c r="G95" s="9" t="n">
         <v>47.481149</v>
       </c>
-      <c r="H95" s="8" t="n">
+      <c r="H95" s="9" t="n">
         <v>47.550991</v>
       </c>
-      <c r="I95" s="8" t="n">
+      <c r="I95" s="9" t="n">
         <v>49.1228</v>
       </c>
-      <c r="J95" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K95" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L95" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M95" s="9" t="inlineStr">
+      <c r="J95" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K95" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L95" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M95" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -5158,10 +5160,10 @@
       <c r="C96" s="6" t="n">
         <v>48.968333</v>
       </c>
-      <c r="D96" s="6" t="n">
+      <c r="D96" s="7" t="n">
         <v>0.344711</v>
       </c>
-      <c r="E96" s="6" t="n">
+      <c r="E96" s="7" t="n">
         <v>0.059169</v>
       </c>
       <c r="F96" s="6" t="n">
@@ -5176,22 +5178,22 @@
       <c r="I96" s="6" t="n">
         <v>50.110607</v>
       </c>
-      <c r="J96" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K96" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L96" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M96" s="7" t="inlineStr">
+      <c r="J96" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K96" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L96" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M96" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -5206,43 +5208,43 @@
       <c r="B97" s="5" t="n">
         <v>45870</v>
       </c>
-      <c r="C97" s="8" t="n">
+      <c r="C97" s="9" t="n">
         <v>49.302657</v>
       </c>
-      <c r="D97" s="8" t="n">
+      <c r="D97" s="10" t="n">
         <v>0.334323</v>
       </c>
-      <c r="E97" s="8" t="n">
+      <c r="E97" s="10" t="n">
         <v>1.938422</v>
       </c>
-      <c r="F97" s="8" t="n">
+      <c r="F97" s="9" t="n">
         <v>49.210834</v>
       </c>
-      <c r="G97" s="8" t="n">
+      <c r="G97" s="9" t="n">
         <v>46.197266</v>
       </c>
-      <c r="H97" s="8" t="n">
+      <c r="H97" s="9" t="n">
         <v>48.49971</v>
       </c>
-      <c r="I97" s="8" t="n">
+      <c r="I97" s="9" t="n">
         <v>50.381451</v>
       </c>
-      <c r="J97" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K97" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L97" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M97" s="9" t="inlineStr">
+      <c r="J97" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K97" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L97" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M97" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -5260,10 +5262,10 @@
       <c r="C98" s="6" t="n">
         <v>49.319399</v>
       </c>
-      <c r="D98" s="6" t="n">
+      <c r="D98" s="7" t="n">
         <v>0.016742</v>
       </c>
-      <c r="E98" s="6" t="n">
+      <c r="E98" s="7" t="n">
         <v>3.250656</v>
       </c>
       <c r="F98" s="6" t="n">
@@ -5278,22 +5280,22 @@
       <c r="I98" s="6" t="n">
         <v>50.543125</v>
       </c>
-      <c r="J98" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K98" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L98" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M98" s="7" t="inlineStr">
+      <c r="J98" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K98" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L98" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M98" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -5308,43 +5310,43 @@
       <c r="B99" s="5" t="n">
         <v>45931</v>
       </c>
-      <c r="C99" s="8" t="n">
+      <c r="C99" s="9" t="n">
         <v>48.512276</v>
       </c>
-      <c r="D99" s="8" t="n">
+      <c r="D99" s="10" t="n">
         <v>-0.807123</v>
       </c>
-      <c r="E99" s="8" t="n">
+      <c r="E99" s="10" t="n">
         <v>-3.270739</v>
       </c>
-      <c r="F99" s="8" t="n">
+      <c r="F99" s="9" t="n">
         <v>48.83249</v>
       </c>
-      <c r="G99" s="8" t="n">
+      <c r="G99" s="9" t="n">
         <v>45.847665</v>
       </c>
-      <c r="H99" s="8" t="n">
+      <c r="H99" s="9" t="n">
         <v>47.870006</v>
       </c>
-      <c r="I99" s="8" t="n">
+      <c r="I99" s="9" t="n">
         <v>49.230472</v>
       </c>
-      <c r="J99" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K99" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L99" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M99" s="9" t="inlineStr">
+      <c r="J99" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K99" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L99" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M99" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -5362,10 +5364,10 @@
       <c r="C100" s="6" t="n">
         <v>48.303114</v>
       </c>
-      <c r="D100" s="6" t="n">
+      <c r="D100" s="7" t="n">
         <v>-0.209162</v>
       </c>
-      <c r="E100" s="6" t="n">
+      <c r="E100" s="7" t="n">
         <v>0.358984</v>
       </c>
       <c r="F100" s="6" t="n">
@@ -5380,22 +5382,22 @@
       <c r="I100" s="6" t="n">
         <v>49.08107</v>
       </c>
-      <c r="J100" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K100" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L100" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M100" s="7" t="inlineStr">
+      <c r="J100" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K100" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L100" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M100" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -5410,43 +5412,43 @@
       <c r="B101" s="5" t="n">
         <v>45992</v>
       </c>
-      <c r="C101" s="8" t="n">
+      <c r="C101" s="9" t="n">
         <v>48.14813</v>
       </c>
-      <c r="D101" s="8" t="n">
+      <c r="D101" s="10" t="n">
         <v>-0.154983</v>
       </c>
-      <c r="E101" s="8" t="n">
+      <c r="E101" s="10" t="n">
         <v>-1.043436</v>
       </c>
-      <c r="F101" s="8" t="n">
+      <c r="F101" s="9" t="n">
         <v>48.199845</v>
       </c>
-      <c r="G101" s="8" t="n">
+      <c r="G101" s="9" t="n">
         <v>45.064614</v>
       </c>
-      <c r="H101" s="8" t="n">
+      <c r="H101" s="9" t="n">
         <v>47.725481</v>
       </c>
-      <c r="I101" s="8" t="n">
+      <c r="I101" s="9" t="n">
         <v>48.962478</v>
       </c>
-      <c r="J101" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K101" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L101" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M101" s="9" t="inlineStr">
+      <c r="J101" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K101" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L101" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M101" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -5464,10 +5466,10 @@
       <c r="C102" s="6" t="n">
         <v>48.00424</v>
       </c>
-      <c r="D102" s="6" t="n">
+      <c r="D102" s="7" t="n">
         <v>-0.14389</v>
       </c>
-      <c r="E102" s="6" t="n">
+      <c r="E102" s="7" t="n">
         <v>0.662073</v>
       </c>
       <c r="F102" s="6" t="n">
@@ -5482,22 +5484,22 @@
       <c r="I102" s="6" t="n">
         <v>48.93954</v>
       </c>
-      <c r="J102" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K102" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L102" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M102" s="7" t="inlineStr">
+      <c r="J102" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K102" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L102" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M102" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -5512,43 +5514,43 @@
       <c r="B103" s="5" t="n">
         <v>46054</v>
       </c>
-      <c r="C103" s="8" t="n">
+      <c r="C103" s="9" t="n">
         <v>48.796111</v>
       </c>
-      <c r="D103" s="8" t="n">
+      <c r="D103" s="10" t="n">
         <v>0.791872</v>
       </c>
-      <c r="E103" s="8" t="n">
+      <c r="E103" s="10" t="n">
         <v>3.92445</v>
       </c>
-      <c r="F103" s="8" t="n">
+      <c r="F103" s="9" t="n">
         <v>48.432033</v>
       </c>
-      <c r="G103" s="8" t="n">
+      <c r="G103" s="9" t="n">
         <v>46.529004</v>
       </c>
-      <c r="H103" s="8" t="n">
+      <c r="H103" s="9" t="n">
         <v>48.708475</v>
       </c>
-      <c r="I103" s="8" t="n">
+      <c r="I103" s="9" t="n">
         <v>49.466133</v>
       </c>
-      <c r="J103" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K103" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L103" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M103" s="9" t="inlineStr">
+      <c r="J103" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K103" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L103" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M103" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -5566,10 +5568,10 @@
       <c r="C104" s="6" t="n">
         <v>48.442274</v>
       </c>
-      <c r="D104" s="6" t="n">
+      <c r="D104" s="7" t="n">
         <v>-0.353837</v>
       </c>
-      <c r="E104" s="6" t="n">
+      <c r="E104" s="7" t="n">
         <v>0.821345</v>
       </c>
       <c r="F104" s="6" t="n">
@@ -5584,22 +5586,22 @@
       <c r="I104" s="6" t="n">
         <v>48.502866</v>
       </c>
-      <c r="J104" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K104" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L104" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M104" s="7" t="inlineStr">
+      <c r="J104" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K104" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L104" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M104" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -5614,43 +5616,43 @@
       <c r="B105" s="5" t="n">
         <v>46113</v>
       </c>
-      <c r="C105" s="8" t="n">
+      <c r="C105" s="9" t="n">
         <v>48.357206</v>
       </c>
-      <c r="D105" s="8" t="n">
+      <c r="D105" s="10" t="n">
         <v>-0.085068</v>
       </c>
-      <c r="E105" s="8" t="n">
+      <c r="E105" s="10" t="n">
         <v>1.13274</v>
       </c>
-      <c r="F105" s="8" t="n">
+      <c r="F105" s="9" t="n">
         <v>48.327254</v>
       </c>
-      <c r="G105" s="8" t="n">
+      <c r="G105" s="9" t="n">
         <v>48.111931</v>
       </c>
-      <c r="H105" s="8" t="n">
+      <c r="H105" s="9" t="n">
         <v>49.031304</v>
       </c>
-      <c r="I105" s="8" t="n">
+      <c r="I105" s="9" t="n">
         <v>48.076703</v>
       </c>
-      <c r="J105" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K105" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L105" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M105" s="9" t="inlineStr">
+      <c r="J105" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K105" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L105" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M105" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -5668,10 +5670,10 @@
       <c r="C106" s="6" t="n">
         <v>48.225992</v>
       </c>
-      <c r="D106" s="6" t="n">
+      <c r="D106" s="7" t="n">
         <v>-0.131213</v>
       </c>
-      <c r="E106" s="6" t="n">
+      <c r="E106" s="7" t="n">
         <v>-0.336063</v>
       </c>
       <c r="F106" s="6" t="n">
@@ -5686,22 +5688,22 @@
       <c r="I106" s="6" t="n">
         <v>48.484834</v>
       </c>
-      <c r="J106" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K106" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L106" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M106" s="7" t="inlineStr">
+      <c r="J106" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K106" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L106" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M106" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -5716,43 +5718,43 @@
       <c r="B107" s="5" t="n">
         <v>46174</v>
       </c>
-      <c r="C107" s="8" t="n">
+      <c r="C107" s="9" t="n">
         <v>48.156973</v>
       </c>
-      <c r="D107" s="8" t="n">
+      <c r="D107" s="10" t="n">
         <v>-0.069019</v>
       </c>
-      <c r="E107" s="8" t="n">
+      <c r="E107" s="10" t="n">
         <v>0.058732</v>
       </c>
-      <c r="F107" s="8" t="n">
+      <c r="F107" s="9" t="n">
         <v>48.03239</v>
       </c>
-      <c r="G107" s="8" t="n">
+      <c r="G107" s="9" t="n">
         <v>46.252625</v>
       </c>
-      <c r="H107" s="8" t="n">
+      <c r="H107" s="9" t="n">
         <v>48.91357</v>
       </c>
-      <c r="I107" s="8" t="n">
+      <c r="I107" s="9" t="n">
         <v>48.212931</v>
       </c>
-      <c r="J107" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K107" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L107" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M107" s="9" t="inlineStr">
+      <c r="J107" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K107" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L107" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M107" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -5770,10 +5772,10 @@
       <c r="C108" s="6" t="n">
         <v>48.203612</v>
       </c>
-      <c r="D108" s="6" t="n">
+      <c r="D108" s="7" t="n">
         <v>0.046638</v>
       </c>
-      <c r="E108" s="6" t="n">
+      <c r="E108" s="7" t="n">
         <v>-0.60195</v>
       </c>
       <c r="F108" s="6" t="n">
@@ -5788,22 +5790,22 @@
       <c r="I108" s="6" t="n">
         <v>48.529883</v>
       </c>
-      <c r="J108" s="7" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K108" s="7" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L108" s="7" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M108" s="7" t="inlineStr">
+      <c r="J108" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K108" s="8" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L108" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M108" s="8" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
@@ -5818,43 +5820,43 @@
       <c r="B109" s="5" t="n">
         <v>46235</v>
       </c>
-      <c r="C109" s="8" t="n">
+      <c r="C109" s="9" t="n">
         <v>48.232912</v>
       </c>
-      <c r="D109" s="8" t="n">
+      <c r="D109" s="10" t="n">
         <v>0.029301</v>
       </c>
-      <c r="E109" s="8" t="n">
+      <c r="E109" s="10" t="n">
         <v>-0.608084</v>
       </c>
-      <c r="F109" s="8" t="n">
+      <c r="F109" s="9" t="n">
         <v>47.997733</v>
       </c>
-      <c r="G109" s="8" t="n">
+      <c r="G109" s="9" t="n">
         <v>47.498528</v>
       </c>
-      <c r="H109" s="8" t="n">
+      <c r="H109" s="9" t="n">
         <v>48.000377</v>
       </c>
-      <c r="I109" s="8" t="n">
+      <c r="I109" s="9" t="n">
         <v>48.608038</v>
       </c>
-      <c r="J109" s="9" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="K109" s="9" t="inlineStr">
-        <is>
-          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
-        </is>
-      </c>
-      <c r="L109" s="9" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
-        </is>
-      </c>
-      <c r="M109" s="9" t="inlineStr">
+      <c r="J109" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="K109" s="11" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Mensual de Opinión Empresarial (EMOE) / Indicadores de Confianza Empresarial (ICE)</t>
+        </is>
+      </c>
+      <c r="L109" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ice/ice2026_09.pdf</t>
+        </is>
+      </c>
+      <c r="M109" s="11" t="inlineStr">
         <is>
           <t>1 de septiembre de 2026</t>
         </is>
